--- a/research/traditional_assets/database/data/poland/poland_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_coal_related_energy.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wse_lwb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0268</v>
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-0.192</v>
       </c>
       <c r="G2">
-        <v>0.2244101801969162</v>
+        <v>0.3590548273952372</v>
       </c>
       <c r="H2">
-        <v>0.2244101801969162</v>
+        <v>0.3590548273952372</v>
       </c>
       <c r="I2">
-        <v>0.09232769830949286</v>
+        <v>0.1894795876331263</v>
       </c>
       <c r="J2">
-        <v>0.08302279746423928</v>
+        <v>0.1712672977233135</v>
       </c>
       <c r="K2">
-        <v>37.1</v>
+        <v>85.21600000000001</v>
       </c>
       <c r="L2">
-        <v>0.06892067620286087</v>
+        <v>0.1573121654052058</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04399764663750543</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.2018400300413068</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04399764663750543</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.2018400300413068</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>112.7</v>
+        <v>155.001</v>
       </c>
       <c r="V2">
-        <v>0.417144760706222</v>
+        <v>0.396492978282557</v>
       </c>
       <c r="W2">
-        <v>-0.3747758334083968</v>
+        <v>0.05182727318039908</v>
       </c>
       <c r="X2">
-        <v>0.07075994029369359</v>
+        <v>0.1420898670806235</v>
       </c>
       <c r="Y2">
-        <v>-0.4455357737020904</v>
+        <v>-0.09026259390022441</v>
       </c>
       <c r="Z2">
-        <v>0.690249441248014</v>
+        <v>0.7048002716622224</v>
       </c>
       <c r="AA2">
-        <v>-0.3635427333715324</v>
+        <v>0.05262492226956571</v>
       </c>
       <c r="AB2">
-        <v>0.06822653992234123</v>
+        <v>0.1411363361552839</v>
       </c>
       <c r="AC2">
-        <v>-0.4317692732938737</v>
+        <v>-0.08851141388571815</v>
       </c>
       <c r="AD2">
-        <v>8.312000000000001</v>
+        <v>6.052</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.08453689567723217</v>
       </c>
       <c r="AF2">
-        <v>8.312000000000001</v>
+        <v>6.136536895677231</v>
       </c>
       <c r="AG2">
-        <v>-104.388</v>
+        <v>-148.8644631043228</v>
       </c>
       <c r="AH2">
-        <v>0.02984753054057354</v>
+        <v>0.01545468158473779</v>
       </c>
       <c r="AI2">
-        <v>0.009405885694498826</v>
+        <v>0.007801774707634442</v>
       </c>
       <c r="AJ2">
-        <v>-0.6296702898987827</v>
+        <v>-0.6149758656825186</v>
       </c>
       <c r="AK2">
-        <v>-0.1353926448958628</v>
+        <v>-0.2357108035756367</v>
       </c>
       <c r="AL2">
-        <v>0.022</v>
+        <v>1.15</v>
       </c>
       <c r="AM2">
-        <v>-0.07100000000000001</v>
+        <v>-3.223</v>
       </c>
       <c r="AN2">
-        <v>0.04918343195266273</v>
+        <v>0.03313132640268904</v>
       </c>
       <c r="AO2">
-        <v>2259.090909090909</v>
+        <v>89.2095652173913</v>
       </c>
       <c r="AP2">
-        <v>-0.6176804733727811</v>
+        <v>-0.8149499532171808</v>
       </c>
       <c r="AQ2">
-        <v>-700</v>
+        <v>-31.83090288551039</v>
       </c>
     </row>
     <row r="3">
@@ -716,112 +724,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0268</v>
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.155</v>
       </c>
       <c r="G3">
-        <v>0.2244101801969162</v>
+        <v>0.3590548273952372</v>
       </c>
       <c r="H3">
-        <v>0.2244101801969162</v>
+        <v>0.3590548273952372</v>
       </c>
       <c r="I3">
-        <v>0.1181497306334758</v>
+        <v>0.1894962019953194</v>
       </c>
       <c r="J3">
-        <v>0.09433517555266581</v>
+        <v>0.1530684283162949</v>
       </c>
       <c r="K3">
-        <v>51.2</v>
+        <v>85.2</v>
       </c>
       <c r="L3">
-        <v>0.09511424856028239</v>
+        <v>0.157282628761307</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>17.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0443527591542032</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2018779342723004</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>17.2</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0443527591542032</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2018779342723004</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>112.7</v>
+        <v>155</v>
       </c>
       <c r="V3">
-        <v>0.4195830230826508</v>
+        <v>0.3996905621454358</v>
       </c>
       <c r="W3">
-        <v>0.06079316076941344</v>
+        <v>0.09791977933570854</v>
       </c>
       <c r="X3">
-        <v>0.06920215418612799</v>
+        <v>0.1400948155766387</v>
       </c>
       <c r="Y3">
-        <v>-0.008408993416714548</v>
+        <v>-0.04217503624093012</v>
       </c>
       <c r="Z3">
-        <v>0.7061061192365711</v>
+        <v>0.7075177175214213</v>
       </c>
       <c r="AA3">
-        <v>0.0666106447169935</v>
+        <v>0.1082986250269363</v>
       </c>
       <c r="AB3">
-        <v>0.06800338250100328</v>
+        <v>0.1388275259524534</v>
       </c>
       <c r="AC3">
-        <v>-0.001392737784009779</v>
+        <v>-0.03052890092551712</v>
       </c>
       <c r="AD3">
-        <v>8.15</v>
+        <v>5.85</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.08453689567723217</v>
       </c>
       <c r="AF3">
-        <v>8.15</v>
+        <v>5.934536895677232</v>
       </c>
       <c r="AG3">
-        <v>-104.55</v>
+        <v>-149.0654631043228</v>
       </c>
       <c r="AH3">
-        <v>0.02944896115627823</v>
+        <v>0.01507243165018473</v>
       </c>
       <c r="AI3">
-        <v>0.009253477150156118</v>
+        <v>0.007568263628804777</v>
       </c>
       <c r="AJ3">
-        <v>-0.6373056994818652</v>
+        <v>-0.624398401013347</v>
       </c>
       <c r="AK3">
-        <v>-0.1361239502636547</v>
+        <v>-0.2369373390941987</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM3">
-        <v>-0.093</v>
+        <v>-3.21</v>
       </c>
       <c r="AN3">
-        <v>0.04822485207100592</v>
+        <v>0.0320254890045821</v>
+      </c>
+      <c r="AO3">
+        <v>89.21739130434783</v>
       </c>
       <c r="AP3">
-        <v>-0.6186390532544378</v>
+        <v>-0.8160503161727228</v>
       </c>
       <c r="AQ3">
-        <v>-683.8709677419355</v>
+        <v>-31.9626168224299</v>
       </c>
     </row>
     <row r="4">
@@ -840,8 +857,11 @@
           <t>Coal &amp; Related Energy</t>
         </is>
       </c>
+      <c r="E4">
+        <v>-0.539</v>
+      </c>
       <c r="K4">
-        <v>-14.1</v>
+        <v>0.016</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -850,7 +870,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -859,73 +879,8782 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.0003194888178913738</v>
       </c>
       <c r="W4">
-        <v>-0.810344827586207</v>
+        <v>0.005734767025089606</v>
       </c>
       <c r="X4">
-        <v>0.07231772640125919</v>
+        <v>0.1440849185846083</v>
       </c>
       <c r="Y4">
-        <v>-0.8826625539874662</v>
+        <v>-0.1383501515595187</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.7936961114600584</v>
+        <v>-0.003048780487804878</v>
       </c>
       <c r="AB4">
-        <v>0.06844969734367919</v>
+        <v>0.1434451463581143</v>
       </c>
       <c r="AC4">
-        <v>-0.8621458088037376</v>
+        <v>-0.1464939268459192</v>
       </c>
       <c r="AD4">
-        <v>0.162</v>
+        <v>0.202</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.162</v>
+        <v>0.202</v>
       </c>
       <c r="AG4">
-        <v>0.162</v>
+        <v>0.201</v>
       </c>
       <c r="AH4">
-        <v>0.09353348729792148</v>
+        <v>0.06062424969987996</v>
       </c>
       <c r="AI4">
-        <v>0.05487804878048781</v>
+        <v>0.08340214698596202</v>
       </c>
       <c r="AJ4">
-        <v>0.09353348729792148</v>
+        <v>0.06034223956769739</v>
       </c>
       <c r="AK4">
-        <v>0.05487804878048781</v>
+        <v>0.08302354399008674</v>
       </c>
       <c r="AL4">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.022</v>
-      </c>
-      <c r="AO4">
-        <v>-631.8181818181819</v>
+        <v>-0.013</v>
       </c>
       <c r="AQ4">
-        <v>-631.8181818181819</v>
+        <v>0.6923076923076923</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lubelski Wegiel Bogdanka S.A. (WSE:LWB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WSE:LWB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coal &amp; Related Energy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0150724316501847</v>
+      </c>
+      <c r="F2">
+        <v>0.99</v>
+      </c>
+      <c r="G2">
+        <v>387.8</v>
+      </c>
+      <c r="H2">
+        <v>39.9169286941432</v>
+      </c>
+      <c r="I2">
+        <v>238.734536895677</v>
+      </c>
+      <c r="J2">
+        <v>274.714120220864</v>
+      </c>
+      <c r="K2">
+        <v>5.93453689567723</v>
+      </c>
+      <c r="L2">
+        <v>389.79719152672</v>
+      </c>
+      <c r="M2">
+        <v>0.138827525952453</v>
+      </c>
+      <c r="N2">
+        <v>0.125726820746893</v>
+      </c>
+      <c r="O2">
+        <v>0.0560148440366973</v>
+      </c>
+      <c r="P2">
+        <v>0.04455</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.140094815576639</v>
+      </c>
+      <c r="T2">
+        <v>8.16223207468925</v>
+      </c>
+      <c r="U2">
+        <v>1.37352270837945</v>
+      </c>
+      <c r="V2">
+        <v>110.150932809802</v>
+      </c>
+      <c r="W2">
+        <v>4.788830622307774</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>387.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.06915412844036697</v>
+      </c>
+      <c r="AD2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>182.667</v>
+      </c>
+      <c r="AH2">
+        <v>80</v>
+      </c>
+      <c r="AI2">
+        <v>206.6</v>
+      </c>
+      <c r="AJ2">
+        <v>5.934536895677232</v>
+      </c>
+      <c r="AK2">
+        <v>5.85</v>
+      </c>
+      <c r="AL2">
+        <v>1.15</v>
+      </c>
+      <c r="AM2">
+        <v>5.85</v>
+      </c>
+      <c r="AN2">
+        <v>155</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1388545889233804</v>
+      </c>
+      <c r="C2">
+        <v>393.669963487293</v>
+      </c>
+      <c r="D2">
+        <v>238.669963487293</v>
+      </c>
+      <c r="E2">
+        <v>-5.934536895677232</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>155</v>
+      </c>
+      <c r="H2">
+        <v>387.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>182.667</v>
+      </c>
+      <c r="K2">
+        <v>80</v>
+      </c>
+      <c r="L2">
+        <v>102.667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>102.667</v>
+      </c>
+      <c r="O2">
+        <v>19.50672999999999</v>
+      </c>
+      <c r="P2">
+        <v>83.16027000000001</v>
+      </c>
+      <c r="Q2">
+        <v>163.16027</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1388545889233804</v>
+      </c>
+      <c r="T2">
+        <v>1.356705663379757</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.138646655204426</v>
+      </c>
+      <c r="C3">
+        <v>390.2296556305997</v>
+      </c>
+      <c r="D3">
+        <v>239.1670009995564</v>
+      </c>
+      <c r="E3">
+        <v>-1.997191526720459</v>
+      </c>
+      <c r="F3">
+        <v>3.937345368956773</v>
+      </c>
+      <c r="G3">
+        <v>155</v>
+      </c>
+      <c r="H3">
+        <v>387.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>182.667</v>
+      </c>
+      <c r="K3">
+        <v>80</v>
+      </c>
+      <c r="L3">
+        <v>102.667</v>
+      </c>
+      <c r="M3">
+        <v>0.1799366833613245</v>
+      </c>
+      <c r="N3">
+        <v>102.4870633166387</v>
+      </c>
+      <c r="O3">
+        <v>19.47254203016134</v>
+      </c>
+      <c r="P3">
+        <v>83.01452128647733</v>
+      </c>
+      <c r="Q3">
+        <v>163.0145212864773</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.139673217378208</v>
+      </c>
+      <c r="T3">
+        <v>1.367805982443773</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>570.5729264434535</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1384387214854715</v>
+      </c>
+      <c r="C4">
+        <v>386.7914222858398</v>
+      </c>
+      <c r="D4">
+        <v>239.6661130237534</v>
+      </c>
+      <c r="E4">
+        <v>1.940153842236314</v>
+      </c>
+      <c r="F4">
+        <v>7.874690737913546</v>
+      </c>
+      <c r="G4">
+        <v>155</v>
+      </c>
+      <c r="H4">
+        <v>387.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>182.667</v>
+      </c>
+      <c r="K4">
+        <v>80</v>
+      </c>
+      <c r="L4">
+        <v>102.667</v>
+      </c>
+      <c r="M4">
+        <v>0.3598733667226491</v>
+      </c>
+      <c r="N4">
+        <v>102.3071266332773</v>
+      </c>
+      <c r="O4">
+        <v>19.43835406032269</v>
+      </c>
+      <c r="P4">
+        <v>82.86877257295465</v>
+      </c>
+      <c r="Q4">
+        <v>162.8687725729546</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1405085525361954</v>
+      </c>
+      <c r="T4">
+        <v>1.379132838631545</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>285.2864632217267</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1382307877665171</v>
+      </c>
+      <c r="C5">
+        <v>383.3552764679255</v>
+      </c>
+      <c r="D5">
+        <v>240.1673125747959</v>
+      </c>
+      <c r="E5">
+        <v>5.877499211193086</v>
+      </c>
+      <c r="F5">
+        <v>11.81203610687032</v>
+      </c>
+      <c r="G5">
+        <v>155</v>
+      </c>
+      <c r="H5">
+        <v>387.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>182.667</v>
+      </c>
+      <c r="K5">
+        <v>80</v>
+      </c>
+      <c r="L5">
+        <v>102.667</v>
+      </c>
+      <c r="M5">
+        <v>0.5398100500839735</v>
+      </c>
+      <c r="N5">
+        <v>102.127189949916</v>
+      </c>
+      <c r="O5">
+        <v>19.40416609048404</v>
+      </c>
+      <c r="P5">
+        <v>82.72302385943199</v>
+      </c>
+      <c r="Q5">
+        <v>162.723023859432</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1413611110995022</v>
+      </c>
+      <c r="T5">
+        <v>1.390693238245869</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>190.1909754811512</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1380228540475627</v>
+      </c>
+      <c r="C6">
+        <v>379.9212313008661</v>
+      </c>
+      <c r="D6">
+        <v>240.6706127766932</v>
+      </c>
+      <c r="E6">
+        <v>9.81484458014986</v>
+      </c>
+      <c r="F6">
+        <v>15.74938147582709</v>
+      </c>
+      <c r="G6">
+        <v>155</v>
+      </c>
+      <c r="H6">
+        <v>387.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>182.667</v>
+      </c>
+      <c r="K6">
+        <v>80</v>
+      </c>
+      <c r="L6">
+        <v>102.667</v>
+      </c>
+      <c r="M6">
+        <v>0.7197467334452982</v>
+      </c>
+      <c r="N6">
+        <v>101.9472532665547</v>
+      </c>
+      <c r="O6">
+        <v>19.36997812064539</v>
+      </c>
+      <c r="P6">
+        <v>82.57727514590931</v>
+      </c>
+      <c r="Q6">
+        <v>162.5772751459093</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1422314312995445</v>
+      </c>
+      <c r="T6">
+        <v>1.402494479518824</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>142.6432316108634</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1378149203286082</v>
+      </c>
+      <c r="C7">
+        <v>376.4893000189138</v>
+      </c>
+      <c r="D7">
+        <v>241.1760268636977</v>
+      </c>
+      <c r="E7">
+        <v>13.75218994910663</v>
+      </c>
+      <c r="F7">
+        <v>19.68672684478386</v>
+      </c>
+      <c r="G7">
+        <v>155</v>
+      </c>
+      <c r="H7">
+        <v>387.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>182.667</v>
+      </c>
+      <c r="K7">
+        <v>80</v>
+      </c>
+      <c r="L7">
+        <v>102.667</v>
+      </c>
+      <c r="M7">
+        <v>0.8996834168066226</v>
+      </c>
+      <c r="N7">
+        <v>101.7673165831934</v>
+      </c>
+      <c r="O7">
+        <v>19.33579015080674</v>
+      </c>
+      <c r="P7">
+        <v>82.43152643238665</v>
+      </c>
+      <c r="Q7">
+        <v>162.4315264323866</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.143120074030114</v>
+      </c>
+      <c r="T7">
+        <v>1.414544167976473</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>114.1145852886907</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1376069866096538</v>
+      </c>
+      <c r="C8">
+        <v>373.0594959677237</v>
+      </c>
+      <c r="D8">
+        <v>241.6835681814644</v>
+      </c>
+      <c r="E8">
+        <v>17.68953531806341</v>
+      </c>
+      <c r="F8">
+        <v>23.62407221374064</v>
+      </c>
+      <c r="G8">
+        <v>155</v>
+      </c>
+      <c r="H8">
+        <v>387.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>182.667</v>
+      </c>
+      <c r="K8">
+        <v>80</v>
+      </c>
+      <c r="L8">
+        <v>102.667</v>
+      </c>
+      <c r="M8">
+        <v>1.079620100167947</v>
+      </c>
+      <c r="N8">
+        <v>101.5873798998321</v>
+      </c>
+      <c r="O8">
+        <v>19.30160218096809</v>
+      </c>
+      <c r="P8">
+        <v>82.28577771886397</v>
+      </c>
+      <c r="Q8">
+        <v>162.285777718864</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1440276240528232</v>
+      </c>
+      <c r="T8">
+        <v>1.426850232784285</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>95.09548774057559</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1373990528906994</v>
+      </c>
+      <c r="C9">
+        <v>369.6318326055288</v>
+      </c>
+      <c r="D9">
+        <v>242.1932501882262</v>
+      </c>
+      <c r="E9">
+        <v>21.62688068702018</v>
+      </c>
+      <c r="F9">
+        <v>27.56141758269741</v>
+      </c>
+      <c r="G9">
+        <v>155</v>
+      </c>
+      <c r="H9">
+        <v>387.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>182.667</v>
+      </c>
+      <c r="K9">
+        <v>80</v>
+      </c>
+      <c r="L9">
+        <v>102.667</v>
+      </c>
+      <c r="M9">
+        <v>1.259556783529272</v>
+      </c>
+      <c r="N9">
+        <v>101.4074432164707</v>
+      </c>
+      <c r="O9">
+        <v>19.26741421112943</v>
+      </c>
+      <c r="P9">
+        <v>82.14002900534129</v>
+      </c>
+      <c r="Q9">
+        <v>162.1400290053413</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.144954691280322</v>
+      </c>
+      <c r="T9">
+        <v>1.439420944147104</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>81.51041806335049</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.137191119171745</v>
+      </c>
+      <c r="C10">
+        <v>366.2063235043289</v>
+      </c>
+      <c r="D10">
+        <v>242.7050864559831</v>
+      </c>
+      <c r="E10">
+        <v>25.56422605597695</v>
+      </c>
+      <c r="F10">
+        <v>31.49876295165418</v>
+      </c>
+      <c r="G10">
+        <v>155</v>
+      </c>
+      <c r="H10">
+        <v>387.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>182.667</v>
+      </c>
+      <c r="K10">
+        <v>80</v>
+      </c>
+      <c r="L10">
+        <v>102.667</v>
+      </c>
+      <c r="M10">
+        <v>1.439493466890596</v>
+      </c>
+      <c r="N10">
+        <v>101.2275065331094</v>
+      </c>
+      <c r="O10">
+        <v>19.23322624129078</v>
+      </c>
+      <c r="P10">
+        <v>81.99428029181863</v>
+      </c>
+      <c r="Q10">
+        <v>161.9942802918186</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1459019121432011</v>
+      </c>
+      <c r="T10">
+        <v>1.452264931843896</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>71.32161580543168</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1369831854527906</v>
+      </c>
+      <c r="C11">
+        <v>362.7829823510962</v>
+      </c>
+      <c r="D11">
+        <v>243.2190906717071</v>
+      </c>
+      <c r="E11">
+        <v>29.50157142493372</v>
+      </c>
+      <c r="F11">
+        <v>35.43610832061095</v>
+      </c>
+      <c r="G11">
+        <v>155</v>
+      </c>
+      <c r="H11">
+        <v>387.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>182.667</v>
+      </c>
+      <c r="K11">
+        <v>80</v>
+      </c>
+      <c r="L11">
+        <v>102.667</v>
+      </c>
+      <c r="M11">
+        <v>1.619430150251921</v>
+      </c>
+      <c r="N11">
+        <v>101.0475698497481</v>
+      </c>
+      <c r="O11">
+        <v>19.19903827145213</v>
+      </c>
+      <c r="P11">
+        <v>81.84853157829596</v>
+      </c>
+      <c r="Q11">
+        <v>161.848531578296</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1468699510470226</v>
+      </c>
+      <c r="T11">
+        <v>1.465391204984575</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>63.3969918270504</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1367752517338362</v>
+      </c>
+      <c r="C12">
+        <v>359.3618229489943</v>
+      </c>
+      <c r="D12">
+        <v>243.735276638562</v>
+      </c>
+      <c r="E12">
+        <v>33.43891679389049</v>
+      </c>
+      <c r="F12">
+        <v>39.37345368956773</v>
+      </c>
+      <c r="G12">
+        <v>155</v>
+      </c>
+      <c r="H12">
+        <v>387.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>182.667</v>
+      </c>
+      <c r="K12">
+        <v>80</v>
+      </c>
+      <c r="L12">
+        <v>102.667</v>
+      </c>
+      <c r="M12">
+        <v>1.799366833613245</v>
+      </c>
+      <c r="N12">
+        <v>100.8676331663868</v>
+      </c>
+      <c r="O12">
+        <v>19.16485030161348</v>
+      </c>
+      <c r="P12">
+        <v>81.70278286477327</v>
+      </c>
+      <c r="Q12">
+        <v>161.7027828647733</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1478595019264846</v>
+      </c>
+      <c r="T12">
+        <v>1.478809173083935</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>57.05729264434535</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1365673180148817</v>
+      </c>
+      <c r="C13">
+        <v>355.9428592186146</v>
+      </c>
+      <c r="D13">
+        <v>244.2536582771391</v>
+      </c>
+      <c r="E13">
+        <v>37.37626216284726</v>
+      </c>
+      <c r="F13">
+        <v>43.31079905852449</v>
+      </c>
+      <c r="G13">
+        <v>155</v>
+      </c>
+      <c r="H13">
+        <v>387.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>182.667</v>
+      </c>
+      <c r="K13">
+        <v>80</v>
+      </c>
+      <c r="L13">
+        <v>102.667</v>
+      </c>
+      <c r="M13">
+        <v>1.97930351697457</v>
+      </c>
+      <c r="N13">
+        <v>100.6876964830254</v>
+      </c>
+      <c r="O13">
+        <v>19.13066233177483</v>
+      </c>
+      <c r="P13">
+        <v>81.5570341512506</v>
+      </c>
+      <c r="Q13">
+        <v>161.5570341512506</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1488712899043615</v>
+      </c>
+      <c r="T13">
+        <v>1.492528668556315</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>51.87026604031396</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1363593842959273</v>
+      </c>
+      <c r="C14">
+        <v>352.5261051992273</v>
+      </c>
+      <c r="D14">
+        <v>244.7742496267086</v>
+      </c>
+      <c r="E14">
+        <v>41.31360753180404</v>
+      </c>
+      <c r="F14">
+        <v>47.24814442748127</v>
+      </c>
+      <c r="G14">
+        <v>155</v>
+      </c>
+      <c r="H14">
+        <v>387.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>182.667</v>
+      </c>
+      <c r="K14">
+        <v>80</v>
+      </c>
+      <c r="L14">
+        <v>102.667</v>
+      </c>
+      <c r="M14">
+        <v>2.159240200335894</v>
+      </c>
+      <c r="N14">
+        <v>100.5077597996641</v>
+      </c>
+      <c r="O14">
+        <v>19.09647436193618</v>
+      </c>
+      <c r="P14">
+        <v>81.41128543772794</v>
+      </c>
+      <c r="Q14">
+        <v>161.4112854377279</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1499060730635537</v>
+      </c>
+      <c r="T14">
+        <v>1.506559970743975</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>47.5477438702878</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1361514505769729</v>
+      </c>
+      <c r="C15">
+        <v>349.1115750500491</v>
+      </c>
+      <c r="D15">
+        <v>245.2970648464872</v>
+      </c>
+      <c r="E15">
+        <v>45.25095290076081</v>
+      </c>
+      <c r="F15">
+        <v>51.18548979643804</v>
+      </c>
+      <c r="G15">
+        <v>155</v>
+      </c>
+      <c r="H15">
+        <v>387.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>182.667</v>
+      </c>
+      <c r="K15">
+        <v>80</v>
+      </c>
+      <c r="L15">
+        <v>102.667</v>
+      </c>
+      <c r="M15">
+        <v>2.339176883697219</v>
+      </c>
+      <c r="N15">
+        <v>100.3278231163028</v>
+      </c>
+      <c r="O15">
+        <v>19.06228639209752</v>
+      </c>
+      <c r="P15">
+        <v>81.26553672420526</v>
+      </c>
+      <c r="Q15">
+        <v>161.2655367242053</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1509646443413482</v>
+      </c>
+      <c r="T15">
+        <v>1.520913831602617</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>43.89022511103489</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1359435168580184</v>
+      </c>
+      <c r="C16">
+        <v>345.6992830515265</v>
+      </c>
+      <c r="D16">
+        <v>245.8221182169214</v>
+      </c>
+      <c r="E16">
+        <v>49.18829826971758</v>
+      </c>
+      <c r="F16">
+        <v>55.12283516539482</v>
+      </c>
+      <c r="G16">
+        <v>155</v>
+      </c>
+      <c r="H16">
+        <v>387.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>182.667</v>
+      </c>
+      <c r="K16">
+        <v>80</v>
+      </c>
+      <c r="L16">
+        <v>102.667</v>
+      </c>
+      <c r="M16">
+        <v>2.519113567058544</v>
+      </c>
+      <c r="N16">
+        <v>100.1478864329415</v>
+      </c>
+      <c r="O16">
+        <v>19.02809842225887</v>
+      </c>
+      <c r="P16">
+        <v>81.11978801068258</v>
+      </c>
+      <c r="Q16">
+        <v>161.1197880106826</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1520478335558354</v>
+      </c>
+      <c r="T16">
+        <v>1.535601503178902</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>40.75520903167525</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.135735583139064</v>
+      </c>
+      <c r="C17">
+        <v>342.2892436066365</v>
+      </c>
+      <c r="D17">
+        <v>246.3494241409882</v>
+      </c>
+      <c r="E17">
+        <v>53.12564363867435</v>
+      </c>
+      <c r="F17">
+        <v>59.06018053435159</v>
+      </c>
+      <c r="G17">
+        <v>155</v>
+      </c>
+      <c r="H17">
+        <v>387.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>182.667</v>
+      </c>
+      <c r="K17">
+        <v>80</v>
+      </c>
+      <c r="L17">
+        <v>102.667</v>
+      </c>
+      <c r="M17">
+        <v>2.699050250419868</v>
+      </c>
+      <c r="N17">
+        <v>99.96794974958013</v>
+      </c>
+      <c r="O17">
+        <v>18.99391045242022</v>
+      </c>
+      <c r="P17">
+        <v>80.97403929715991</v>
+      </c>
+      <c r="Q17">
+        <v>160.9740392971599</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1531565095753695</v>
+      </c>
+      <c r="T17">
+        <v>1.55063476702757</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>38.03819509623023</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1355276494201096</v>
+      </c>
+      <c r="C18">
+        <v>338.8814712422034</v>
+      </c>
+      <c r="D18">
+        <v>246.8789971455118</v>
+      </c>
+      <c r="E18">
+        <v>57.06298900763113</v>
+      </c>
+      <c r="F18">
+        <v>62.99752590330836</v>
+      </c>
+      <c r="G18">
+        <v>155</v>
+      </c>
+      <c r="H18">
+        <v>387.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>182.667</v>
+      </c>
+      <c r="K18">
+        <v>80</v>
+      </c>
+      <c r="L18">
+        <v>102.667</v>
+      </c>
+      <c r="M18">
+        <v>2.878986933781193</v>
+      </c>
+      <c r="N18">
+        <v>99.78801306621881</v>
+      </c>
+      <c r="O18">
+        <v>18.95972248258157</v>
+      </c>
+      <c r="P18">
+        <v>80.82829058363724</v>
+      </c>
+      <c r="Q18">
+        <v>160.8282905836372</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1542915826429876</v>
+      </c>
+      <c r="T18">
+        <v>1.566025965729777</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>35.66080790271584</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1353197157011552</v>
+      </c>
+      <c r="C19">
+        <v>335.4759806102327</v>
+      </c>
+      <c r="D19">
+        <v>247.4108518824978</v>
+      </c>
+      <c r="E19">
+        <v>61.00033437658791</v>
+      </c>
+      <c r="F19">
+        <v>66.93487127226514</v>
+      </c>
+      <c r="G19">
+        <v>155</v>
+      </c>
+      <c r="H19">
+        <v>387.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>182.667</v>
+      </c>
+      <c r="K19">
+        <v>80</v>
+      </c>
+      <c r="L19">
+        <v>102.667</v>
+      </c>
+      <c r="M19">
+        <v>3.058923617142517</v>
+      </c>
+      <c r="N19">
+        <v>99.60807638285749</v>
+      </c>
+      <c r="O19">
+        <v>18.92553451274292</v>
+      </c>
+      <c r="P19">
+        <v>80.68254187011458</v>
+      </c>
+      <c r="Q19">
+        <v>160.6825418701146</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1554540068688617</v>
+      </c>
+      <c r="T19">
+        <v>1.581788036689869</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>33.56311332020314</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1351117819822008</v>
+      </c>
+      <c r="C20">
+        <v>332.0727864892626</v>
+      </c>
+      <c r="D20">
+        <v>247.9450031304845</v>
+      </c>
+      <c r="E20">
+        <v>64.93767974554467</v>
+      </c>
+      <c r="F20">
+        <v>70.8722166412219</v>
+      </c>
+      <c r="G20">
+        <v>155</v>
+      </c>
+      <c r="H20">
+        <v>387.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>182.667</v>
+      </c>
+      <c r="K20">
+        <v>80</v>
+      </c>
+      <c r="L20">
+        <v>102.667</v>
+      </c>
+      <c r="M20">
+        <v>3.238860300503841</v>
+      </c>
+      <c r="N20">
+        <v>99.42813969949616</v>
+      </c>
+      <c r="O20">
+        <v>18.89134654290427</v>
+      </c>
+      <c r="P20">
+        <v>80.5367931565919</v>
+      </c>
+      <c r="Q20">
+        <v>160.5367931565919</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1566447829051229</v>
+      </c>
+      <c r="T20">
+        <v>1.597934548405084</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>31.6984959135252</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1349038482632464</v>
+      </c>
+      <c r="C21">
+        <v>328.6719037857327</v>
+      </c>
+      <c r="D21">
+        <v>248.4814657959114</v>
+      </c>
+      <c r="E21">
+        <v>68.87502511450145</v>
+      </c>
+      <c r="F21">
+        <v>74.80956201017868</v>
+      </c>
+      <c r="G21">
+        <v>155</v>
+      </c>
+      <c r="H21">
+        <v>387.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>182.667</v>
+      </c>
+      <c r="K21">
+        <v>80</v>
+      </c>
+      <c r="L21">
+        <v>102.667</v>
+      </c>
+      <c r="M21">
+        <v>3.418796983865166</v>
+      </c>
+      <c r="N21">
+        <v>99.24820301613484</v>
+      </c>
+      <c r="O21">
+        <v>18.85715857306561</v>
+      </c>
+      <c r="P21">
+        <v>80.39104444306922</v>
+      </c>
+      <c r="Q21">
+        <v>160.3910444430692</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1578649608188226</v>
+      </c>
+      <c r="T21">
+        <v>1.614479739421911</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>30.03015402333966</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1346959145442919</v>
+      </c>
+      <c r="C22">
+        <v>325.273347535371</v>
+      </c>
+      <c r="D22">
+        <v>249.0202549145064</v>
+      </c>
+      <c r="E22">
+        <v>72.81237048345822</v>
+      </c>
+      <c r="F22">
+        <v>78.74690737913545</v>
+      </c>
+      <c r="G22">
+        <v>155</v>
+      </c>
+      <c r="H22">
+        <v>387.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>182.667</v>
+      </c>
+      <c r="K22">
+        <v>80</v>
+      </c>
+      <c r="L22">
+        <v>102.667</v>
+      </c>
+      <c r="M22">
+        <v>3.59873366722649</v>
+      </c>
+      <c r="N22">
+        <v>99.0682663327735</v>
+      </c>
+      <c r="O22">
+        <v>18.82297060322696</v>
+      </c>
+      <c r="P22">
+        <v>80.24529572954654</v>
+      </c>
+      <c r="Q22">
+        <v>160.2452957295465</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1591156431803649</v>
+      </c>
+      <c r="T22">
+        <v>1.631438560214158</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>28.52864632217268</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1344879808253375</v>
+      </c>
+      <c r="C23">
+        <v>321.8771329045983</v>
+      </c>
+      <c r="D23">
+        <v>249.5613856526905</v>
+      </c>
+      <c r="E23">
+        <v>76.74971585241499</v>
+      </c>
+      <c r="F23">
+        <v>82.68425274809222</v>
+      </c>
+      <c r="G23">
+        <v>155</v>
+      </c>
+      <c r="H23">
+        <v>387.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>182.667</v>
+      </c>
+      <c r="K23">
+        <v>80</v>
+      </c>
+      <c r="L23">
+        <v>102.667</v>
+      </c>
+      <c r="M23">
+        <v>3.778670350587815</v>
+      </c>
+      <c r="N23">
+        <v>98.88832964941219</v>
+      </c>
+      <c r="O23">
+        <v>18.78878263338831</v>
+      </c>
+      <c r="P23">
+        <v>80.09954701602388</v>
+      </c>
+      <c r="Q23">
+        <v>160.0995470160239</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1603979883865032</v>
+      </c>
+      <c r="T23">
+        <v>1.648826718241652</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>27.17013935445017</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1342800471063831</v>
+      </c>
+      <c r="C24">
+        <v>318.4832751919512</v>
+      </c>
+      <c r="D24">
+        <v>250.1048733090001</v>
+      </c>
+      <c r="E24">
+        <v>80.68706122137176</v>
+      </c>
+      <c r="F24">
+        <v>86.62159811704899</v>
+      </c>
+      <c r="G24">
+        <v>155</v>
+      </c>
+      <c r="H24">
+        <v>387.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>182.667</v>
+      </c>
+      <c r="K24">
+        <v>80</v>
+      </c>
+      <c r="L24">
+        <v>102.667</v>
+      </c>
+      <c r="M24">
+        <v>3.958607033949139</v>
+      </c>
+      <c r="N24">
+        <v>98.70839296605087</v>
+      </c>
+      <c r="O24">
+        <v>18.75459466354966</v>
+      </c>
+      <c r="P24">
+        <v>79.95379830250121</v>
+      </c>
+      <c r="Q24">
+        <v>159.9537983025012</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1617132142389527</v>
+      </c>
+      <c r="T24">
+        <v>1.666660726474978</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>25.93513302015698</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1340721133874287</v>
+      </c>
+      <c r="C25">
+        <v>315.0917898295241</v>
+      </c>
+      <c r="D25">
+        <v>250.6507333155299</v>
+      </c>
+      <c r="E25">
+        <v>84.62440659032855</v>
+      </c>
+      <c r="F25">
+        <v>90.55894348600577</v>
+      </c>
+      <c r="G25">
+        <v>155</v>
+      </c>
+      <c r="H25">
+        <v>387.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>182.667</v>
+      </c>
+      <c r="K25">
+        <v>80</v>
+      </c>
+      <c r="L25">
+        <v>102.667</v>
+      </c>
+      <c r="M25">
+        <v>4.138543717310465</v>
+      </c>
+      <c r="N25">
+        <v>98.52845628268953</v>
+      </c>
+      <c r="O25">
+        <v>18.72040669371101</v>
+      </c>
+      <c r="P25">
+        <v>79.80804958897852</v>
+      </c>
+      <c r="Q25">
+        <v>159.8080495889785</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1630626018018554</v>
+      </c>
+      <c r="T25">
+        <v>1.684957955701379</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>24.80751854101971</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1338641796684742</v>
+      </c>
+      <c r="C26">
+        <v>311.7026923844301</v>
+      </c>
+      <c r="D26">
+        <v>251.1989812393926</v>
+      </c>
+      <c r="E26">
+        <v>88.56175195928532</v>
+      </c>
+      <c r="F26">
+        <v>94.49628885496254</v>
+      </c>
+      <c r="G26">
+        <v>155</v>
+      </c>
+      <c r="H26">
+        <v>387.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>182.667</v>
+      </c>
+      <c r="K26">
+        <v>80</v>
+      </c>
+      <c r="L26">
+        <v>102.667</v>
+      </c>
+      <c r="M26">
+        <v>4.318480400671788</v>
+      </c>
+      <c r="N26">
+        <v>98.34851959932821</v>
+      </c>
+      <c r="O26">
+        <v>18.68621872387235</v>
+      </c>
+      <c r="P26">
+        <v>79.66230087545586</v>
+      </c>
+      <c r="Q26">
+        <v>159.6623008754559</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1644474995637819</v>
+      </c>
+      <c r="T26">
+        <v>1.703736690960053</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>23.7738719351439</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1336562459495198</v>
+      </c>
+      <c r="C27">
+        <v>308.31599856028</v>
+      </c>
+      <c r="D27">
+        <v>251.7496327841993</v>
+      </c>
+      <c r="E27">
+        <v>92.49909732824209</v>
+      </c>
+      <c r="F27">
+        <v>98.43363422391931</v>
+      </c>
+      <c r="G27">
+        <v>155</v>
+      </c>
+      <c r="H27">
+        <v>387.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>182.667</v>
+      </c>
+      <c r="K27">
+        <v>80</v>
+      </c>
+      <c r="L27">
+        <v>102.667</v>
+      </c>
+      <c r="M27">
+        <v>4.498417084033113</v>
+      </c>
+      <c r="N27">
+        <v>98.16858291596689</v>
+      </c>
+      <c r="O27">
+        <v>18.6520307540337</v>
+      </c>
+      <c r="P27">
+        <v>79.51655216193319</v>
+      </c>
+      <c r="Q27">
+        <v>159.5165521619332</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1658693279326931</v>
+      </c>
+      <c r="T27">
+        <v>1.723016192492291</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>22.82291705773814</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1334483122305654</v>
+      </c>
+      <c r="C28">
+        <v>304.9317241986827</v>
+      </c>
+      <c r="D28">
+        <v>252.3027037915588</v>
+      </c>
+      <c r="E28">
+        <v>96.43644269719886</v>
+      </c>
+      <c r="F28">
+        <v>102.3709795928761</v>
+      </c>
+      <c r="G28">
+        <v>155</v>
+      </c>
+      <c r="H28">
+        <v>387.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>182.667</v>
+      </c>
+      <c r="K28">
+        <v>80</v>
+      </c>
+      <c r="L28">
+        <v>102.667</v>
+      </c>
+      <c r="M28">
+        <v>4.678353767394437</v>
+      </c>
+      <c r="N28">
+        <v>97.98864623260556</v>
+      </c>
+      <c r="O28">
+        <v>18.61784278419505</v>
+      </c>
+      <c r="P28">
+        <v>79.37080344841051</v>
+      </c>
+      <c r="Q28">
+        <v>159.3708034484105</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1673295840953586</v>
+      </c>
+      <c r="T28">
+        <v>1.74281676163351</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>21.94511255551744</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.133240378511611</v>
+      </c>
+      <c r="C29">
+        <v>301.5498852807635</v>
+      </c>
+      <c r="D29">
+        <v>252.8582102425964</v>
+      </c>
+      <c r="E29">
+        <v>100.3737880661556</v>
+      </c>
+      <c r="F29">
+        <v>106.3083249618329</v>
+      </c>
+      <c r="G29">
+        <v>155</v>
+      </c>
+      <c r="H29">
+        <v>387.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>182.667</v>
+      </c>
+      <c r="K29">
+        <v>80</v>
+      </c>
+      <c r="L29">
+        <v>102.667</v>
+      </c>
+      <c r="M29">
+        <v>4.858290450755763</v>
+      </c>
+      <c r="N29">
+        <v>97.80870954924424</v>
+      </c>
+      <c r="O29">
+        <v>18.5836548143564</v>
+      </c>
+      <c r="P29">
+        <v>79.22505473488783</v>
+      </c>
+      <c r="Q29">
+        <v>159.2250547348878</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1688298472761794</v>
+      </c>
+      <c r="T29">
+        <v>1.763159812121062</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>21.13233060901679</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1330324447926566</v>
+      </c>
+      <c r="C30">
+        <v>298.1704979287041</v>
+      </c>
+      <c r="D30">
+        <v>253.4161682594938</v>
+      </c>
+      <c r="E30">
+        <v>104.3111334351124</v>
+      </c>
+      <c r="F30">
+        <v>110.2456703307896</v>
+      </c>
+      <c r="G30">
+        <v>155</v>
+      </c>
+      <c r="H30">
+        <v>387.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>182.667</v>
+      </c>
+      <c r="K30">
+        <v>80</v>
+      </c>
+      <c r="L30">
+        <v>102.667</v>
+      </c>
+      <c r="M30">
+        <v>5.038227134117087</v>
+      </c>
+      <c r="N30">
+        <v>97.62877286588291</v>
+      </c>
+      <c r="O30">
+        <v>18.54946684451775</v>
+      </c>
+      <c r="P30">
+        <v>79.07930602136516</v>
+      </c>
+      <c r="Q30">
+        <v>159.0793060213651</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1703717844342452</v>
+      </c>
+      <c r="T30">
+        <v>1.78406794734438</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>20.37760451583762</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1328245110737021</v>
+      </c>
+      <c r="C31">
+        <v>294.7935784073019</v>
+      </c>
+      <c r="D31">
+        <v>253.9765941070483</v>
+      </c>
+      <c r="E31">
+        <v>108.2484788040692</v>
+      </c>
+      <c r="F31">
+        <v>114.1830156997464</v>
+      </c>
+      <c r="G31">
+        <v>155</v>
+      </c>
+      <c r="H31">
+        <v>387.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>182.667</v>
+      </c>
+      <c r="K31">
+        <v>80</v>
+      </c>
+      <c r="L31">
+        <v>102.667</v>
+      </c>
+      <c r="M31">
+        <v>5.218163817478411</v>
+      </c>
+      <c r="N31">
+        <v>97.44883618252159</v>
+      </c>
+      <c r="O31">
+        <v>18.5152788746791</v>
+      </c>
+      <c r="P31">
+        <v>78.93355730784249</v>
+      </c>
+      <c r="Q31">
+        <v>158.9335573078425</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.171957156441834</v>
+      </c>
+      <c r="T31">
+        <v>1.805565044123285</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>19.67492849805012</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1326165773547477</v>
+      </c>
+      <c r="C32">
+        <v>291.4191431255503</v>
+      </c>
+      <c r="D32">
+        <v>254.5395041942535</v>
+      </c>
+      <c r="E32">
+        <v>112.1858241730259</v>
+      </c>
+      <c r="F32">
+        <v>118.1203610687032</v>
+      </c>
+      <c r="G32">
+        <v>155</v>
+      </c>
+      <c r="H32">
+        <v>387.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>182.667</v>
+      </c>
+      <c r="K32">
+        <v>80</v>
+      </c>
+      <c r="L32">
+        <v>102.667</v>
+      </c>
+      <c r="M32">
+        <v>5.398100500839735</v>
+      </c>
+      <c r="N32">
+        <v>97.26889949916027</v>
+      </c>
+      <c r="O32">
+        <v>18.48109090484045</v>
+      </c>
+      <c r="P32">
+        <v>78.78780859431983</v>
+      </c>
+      <c r="Q32">
+        <v>158.7878085943198</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1735878247924967</v>
+      </c>
+      <c r="T32">
+        <v>1.827676343667301</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>19.01909754811512</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1324086436357933</v>
+      </c>
+      <c r="C33">
+        <v>288.0472086382409</v>
+      </c>
+      <c r="D33">
+        <v>255.1049150759008</v>
+      </c>
+      <c r="E33">
+        <v>116.1231695419827</v>
+      </c>
+      <c r="F33">
+        <v>122.0577064376599</v>
+      </c>
+      <c r="G33">
+        <v>155</v>
+      </c>
+      <c r="H33">
+        <v>387.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>182.667</v>
+      </c>
+      <c r="K33">
+        <v>80</v>
+      </c>
+      <c r="L33">
+        <v>102.667</v>
+      </c>
+      <c r="M33">
+        <v>5.57803718420106</v>
+      </c>
+      <c r="N33">
+        <v>97.08896281579894</v>
+      </c>
+      <c r="O33">
+        <v>18.44690293500179</v>
+      </c>
+      <c r="P33">
+        <v>78.64205988079715</v>
+      </c>
+      <c r="Q33">
+        <v>158.6420598807971</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.175265758892454</v>
+      </c>
+      <c r="T33">
+        <v>1.850428550444477</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>18.40557827236947</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1322007099168389</v>
+      </c>
+      <c r="C34">
+        <v>284.6777916475857</v>
+      </c>
+      <c r="D34">
+        <v>255.6728434542024</v>
+      </c>
+      <c r="E34">
+        <v>120.0605149109395</v>
+      </c>
+      <c r="F34">
+        <v>125.9950518066167</v>
+      </c>
+      <c r="G34">
+        <v>155</v>
+      </c>
+      <c r="H34">
+        <v>387.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>182.667</v>
+      </c>
+      <c r="K34">
+        <v>80</v>
+      </c>
+      <c r="L34">
+        <v>102.667</v>
+      </c>
+      <c r="M34">
+        <v>5.757973867562385</v>
+      </c>
+      <c r="N34">
+        <v>96.90902613243762</v>
+      </c>
+      <c r="O34">
+        <v>18.41271496516314</v>
+      </c>
+      <c r="P34">
+        <v>78.49631116727447</v>
+      </c>
+      <c r="Q34">
+        <v>158.4963111672745</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1769930439953513</v>
+      </c>
+      <c r="T34">
+        <v>1.873849939773923</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>17.83040395135792</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1319927761978844</v>
+      </c>
+      <c r="C35">
+        <v>281.310909004862</v>
+      </c>
+      <c r="D35">
+        <v>256.2433061804355</v>
+      </c>
+      <c r="E35">
+        <v>123.9978602798963</v>
+      </c>
+      <c r="F35">
+        <v>129.9323971755735</v>
+      </c>
+      <c r="G35">
+        <v>155</v>
+      </c>
+      <c r="H35">
+        <v>387.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>182.667</v>
+      </c>
+      <c r="K35">
+        <v>80</v>
+      </c>
+      <c r="L35">
+        <v>102.667</v>
+      </c>
+      <c r="M35">
+        <v>5.93791055092371</v>
+      </c>
+      <c r="N35">
+        <v>96.7290894490763</v>
+      </c>
+      <c r="O35">
+        <v>18.37852699532449</v>
+      </c>
+      <c r="P35">
+        <v>78.35056245375181</v>
+      </c>
+      <c r="Q35">
+        <v>158.3505624537518</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1787718898475887</v>
+      </c>
+      <c r="T35">
+        <v>1.897970475053502</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>17.29008868010465</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.13178484247893</v>
+      </c>
+      <c r="C36">
+        <v>277.9465777120796</v>
+      </c>
+      <c r="D36">
+        <v>256.8163202566099</v>
+      </c>
+      <c r="E36">
+        <v>127.9352056488531</v>
+      </c>
+      <c r="F36">
+        <v>133.8697425445303</v>
+      </c>
+      <c r="G36">
+        <v>155</v>
+      </c>
+      <c r="H36">
+        <v>387.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>182.667</v>
+      </c>
+      <c r="K36">
+        <v>80</v>
+      </c>
+      <c r="L36">
+        <v>102.667</v>
+      </c>
+      <c r="M36">
+        <v>6.117847234285034</v>
+      </c>
+      <c r="N36">
+        <v>96.54915276571496</v>
+      </c>
+      <c r="O36">
+        <v>18.34433902548584</v>
+      </c>
+      <c r="P36">
+        <v>78.20481374022913</v>
+      </c>
+      <c r="Q36">
+        <v>158.2048137402291</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1806046401195909</v>
+      </c>
+      <c r="T36">
+        <v>1.922821935644583</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>16.78155666010157</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1315769087599756</v>
+      </c>
+      <c r="C37">
+        <v>274.5848149236688</v>
+      </c>
+      <c r="D37">
+        <v>257.3919028371558</v>
+      </c>
+      <c r="E37">
+        <v>131.8725510178098</v>
+      </c>
+      <c r="F37">
+        <v>137.807087913487</v>
+      </c>
+      <c r="G37">
+        <v>155</v>
+      </c>
+      <c r="H37">
+        <v>387.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>182.667</v>
+      </c>
+      <c r="K37">
+        <v>80</v>
+      </c>
+      <c r="L37">
+        <v>102.667</v>
+      </c>
+      <c r="M37">
+        <v>6.297783917646358</v>
+      </c>
+      <c r="N37">
+        <v>96.36921608235365</v>
+      </c>
+      <c r="O37">
+        <v>18.31015105564719</v>
+      </c>
+      <c r="P37">
+        <v>78.05906502670646</v>
+      </c>
+      <c r="Q37">
+        <v>158.0590650267065</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1824937827076547</v>
+      </c>
+      <c r="T37">
+        <v>1.948438056561543</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>16.3020836126701</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1313689750410212</v>
+      </c>
+      <c r="C38">
+        <v>271.2256379481934</v>
+      </c>
+      <c r="D38">
+        <v>257.9700712306372</v>
+      </c>
+      <c r="E38">
+        <v>135.8098963867666</v>
+      </c>
+      <c r="F38">
+        <v>141.7444332824438</v>
+      </c>
+      <c r="G38">
+        <v>155</v>
+      </c>
+      <c r="H38">
+        <v>387.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>182.667</v>
+      </c>
+      <c r="K38">
+        <v>80</v>
+      </c>
+      <c r="L38">
+        <v>102.667</v>
+      </c>
+      <c r="M38">
+        <v>6.477720601007682</v>
+      </c>
+      <c r="N38">
+        <v>96.18927939899231</v>
+      </c>
+      <c r="O38">
+        <v>18.27596308580853</v>
+      </c>
+      <c r="P38">
+        <v>77.91331631318377</v>
+      </c>
+      <c r="Q38">
+        <v>157.9133163131838</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1844419610015955</v>
+      </c>
+      <c r="T38">
+        <v>1.974854681257159</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>15.8492479567626</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1311610413220667</v>
+      </c>
+      <c r="C39">
+        <v>267.8690642500852</v>
+      </c>
+      <c r="D39">
+        <v>258.5508429014857</v>
+      </c>
+      <c r="E39">
+        <v>139.7472417557233</v>
+      </c>
+      <c r="F39">
+        <v>145.6817786514006</v>
+      </c>
+      <c r="G39">
+        <v>155</v>
+      </c>
+      <c r="H39">
+        <v>387.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>182.667</v>
+      </c>
+      <c r="K39">
+        <v>80</v>
+      </c>
+      <c r="L39">
+        <v>102.667</v>
+      </c>
+      <c r="M39">
+        <v>6.657657284369007</v>
+      </c>
+      <c r="N39">
+        <v>96.00934271563099</v>
+      </c>
+      <c r="O39">
+        <v>18.24177511596988</v>
+      </c>
+      <c r="P39">
+        <v>77.76756759966111</v>
+      </c>
+      <c r="Q39">
+        <v>157.7675675996611</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1864519862255028</v>
+      </c>
+      <c r="T39">
+        <v>2.002109928958984</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>15.42088990387712</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1309531076031123</v>
+      </c>
+      <c r="C40">
+        <v>264.5151114514023</v>
+      </c>
+      <c r="D40">
+        <v>259.1342354717596</v>
+      </c>
+      <c r="E40">
+        <v>143.6845871246801</v>
+      </c>
+      <c r="F40">
+        <v>149.6191240203574</v>
+      </c>
+      <c r="G40">
+        <v>155</v>
+      </c>
+      <c r="H40">
+        <v>387.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>182.667</v>
+      </c>
+      <c r="K40">
+        <v>80</v>
+      </c>
+      <c r="L40">
+        <v>102.667</v>
+      </c>
+      <c r="M40">
+        <v>6.837593967730332</v>
+      </c>
+      <c r="N40">
+        <v>95.82940603226967</v>
+      </c>
+      <c r="O40">
+        <v>18.20758714613123</v>
+      </c>
+      <c r="P40">
+        <v>77.62181888613844</v>
+      </c>
+      <c r="Q40">
+        <v>157.6218188861384</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1885268509727618</v>
+      </c>
+      <c r="T40">
+        <v>2.030244378199578</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>15.01507701166983</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1307451738841579</v>
+      </c>
+      <c r="C41">
+        <v>261.163797333612</v>
+      </c>
+      <c r="D41">
+        <v>259.7202667229262</v>
+      </c>
+      <c r="E41">
+        <v>147.6219324936369</v>
+      </c>
+      <c r="F41">
+        <v>153.5564693893141</v>
+      </c>
+      <c r="G41">
+        <v>155</v>
+      </c>
+      <c r="H41">
+        <v>387.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>182.667</v>
+      </c>
+      <c r="K41">
+        <v>80</v>
+      </c>
+      <c r="L41">
+        <v>102.667</v>
+      </c>
+      <c r="M41">
+        <v>7.017530651091657</v>
+      </c>
+      <c r="N41">
+        <v>95.64946934890834</v>
+      </c>
+      <c r="O41">
+        <v>18.17339917629258</v>
+      </c>
+      <c r="P41">
+        <v>77.47607017261576</v>
+      </c>
+      <c r="Q41">
+        <v>157.4760701726158</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.19066974407239</v>
+      </c>
+      <c r="T41">
+        <v>2.059301268398881</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>14.63007503701163</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1305372401652035</v>
+      </c>
+      <c r="C42">
+        <v>257.8151398393969</v>
+      </c>
+      <c r="D42">
+        <v>260.3089545976678</v>
+      </c>
+      <c r="E42">
+        <v>151.5592778625937</v>
+      </c>
+      <c r="F42">
+        <v>157.4938147582709</v>
+      </c>
+      <c r="G42">
+        <v>155</v>
+      </c>
+      <c r="H42">
+        <v>387.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>182.667</v>
+      </c>
+      <c r="K42">
+        <v>80</v>
+      </c>
+      <c r="L42">
+        <v>102.667</v>
+      </c>
+      <c r="M42">
+        <v>7.19746733445298</v>
+      </c>
+      <c r="N42">
+        <v>95.46953266554702</v>
+      </c>
+      <c r="O42">
+        <v>18.13921120645393</v>
+      </c>
+      <c r="P42">
+        <v>77.33032145909308</v>
+      </c>
+      <c r="Q42">
+        <v>157.3303214590931</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1928840669420058</v>
+      </c>
+      <c r="T42">
+        <v>2.089326721604826</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>14.26432316108634</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.130329306446249</v>
+      </c>
+      <c r="C43">
+        <v>254.4691570744868</v>
+      </c>
+      <c r="D43">
+        <v>260.9003172017145</v>
+      </c>
+      <c r="E43">
+        <v>155.4966232315504</v>
+      </c>
+      <c r="F43">
+        <v>161.4311601272277</v>
+      </c>
+      <c r="G43">
+        <v>155</v>
+      </c>
+      <c r="H43">
+        <v>387.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>182.667</v>
+      </c>
+      <c r="K43">
+        <v>80</v>
+      </c>
+      <c r="L43">
+        <v>102.667</v>
+      </c>
+      <c r="M43">
+        <v>7.377404017814306</v>
+      </c>
+      <c r="N43">
+        <v>95.2895959821857</v>
+      </c>
+      <c r="O43">
+        <v>18.10502323661528</v>
+      </c>
+      <c r="P43">
+        <v>77.18457274557042</v>
+      </c>
+      <c r="Q43">
+        <v>157.1845727455704</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1951734516038119</v>
+      </c>
+      <c r="T43">
+        <v>2.120369986783854</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>13.91641284008423</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1301213727272946</v>
+      </c>
+      <c r="C44">
+        <v>251.1258673095138</v>
+      </c>
+      <c r="D44">
+        <v>261.4943728056983</v>
+      </c>
+      <c r="E44">
+        <v>159.4339686005072</v>
+      </c>
+      <c r="F44">
+        <v>165.3685054961844</v>
+      </c>
+      <c r="G44">
+        <v>155</v>
+      </c>
+      <c r="H44">
+        <v>387.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>182.667</v>
+      </c>
+      <c r="K44">
+        <v>80</v>
+      </c>
+      <c r="L44">
+        <v>102.667</v>
+      </c>
+      <c r="M44">
+        <v>7.55734070117563</v>
+      </c>
+      <c r="N44">
+        <v>95.10965929882437</v>
+      </c>
+      <c r="O44">
+        <v>18.07083526677663</v>
+      </c>
+      <c r="P44">
+        <v>77.03882403204774</v>
+      </c>
+      <c r="Q44">
+        <v>157.0388240320477</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1975417805643011</v>
+      </c>
+      <c r="T44">
+        <v>2.152483709382849</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>13.58506967722508</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1299134390083402</v>
+      </c>
+      <c r="C45">
+        <v>247.785288981895</v>
+      </c>
+      <c r="D45">
+        <v>262.0911398470362</v>
+      </c>
+      <c r="E45">
+        <v>163.371313969464</v>
+      </c>
+      <c r="F45">
+        <v>169.3058508651412</v>
+      </c>
+      <c r="G45">
+        <v>155</v>
+      </c>
+      <c r="H45">
+        <v>387.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>182.667</v>
+      </c>
+      <c r="K45">
+        <v>80</v>
+      </c>
+      <c r="L45">
+        <v>102.667</v>
+      </c>
+      <c r="M45">
+        <v>7.737277384536955</v>
+      </c>
+      <c r="N45">
+        <v>94.92972261546305</v>
+      </c>
+      <c r="O45">
+        <v>18.03664729693797</v>
+      </c>
+      <c r="P45">
+        <v>76.89307531852508</v>
+      </c>
+      <c r="Q45">
+        <v>156.8930753185251</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1999932087865618</v>
+      </c>
+      <c r="T45">
+        <v>2.185724229266019</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>13.26913782426636</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1297055052893858</v>
+      </c>
+      <c r="C46">
+        <v>244.4474406977399</v>
+      </c>
+      <c r="D46">
+        <v>262.6906369318378</v>
+      </c>
+      <c r="E46">
+        <v>167.3086593384207</v>
+      </c>
+      <c r="F46">
+        <v>173.243196234098</v>
+      </c>
+      <c r="G46">
+        <v>155</v>
+      </c>
+      <c r="H46">
+        <v>387.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>182.667</v>
+      </c>
+      <c r="K46">
+        <v>80</v>
+      </c>
+      <c r="L46">
+        <v>102.667</v>
+      </c>
+      <c r="M46">
+        <v>7.917214067898279</v>
+      </c>
+      <c r="N46">
+        <v>94.74978593210173</v>
+      </c>
+      <c r="O46">
+        <v>18.00245932709932</v>
+      </c>
+      <c r="P46">
+        <v>76.7473266050024</v>
+      </c>
+      <c r="Q46">
+        <v>156.7473266050024</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2025321880167603</v>
+      </c>
+      <c r="T46">
+        <v>2.220151910573588</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W46">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>12.96756651007849</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1300807715704314</v>
+      </c>
+      <c r="C47">
+        <v>239.4301423804139</v>
+      </c>
+      <c r="D47">
+        <v>261.6106839834687</v>
+      </c>
+      <c r="E47">
+        <v>171.2460047073775</v>
+      </c>
+      <c r="F47">
+        <v>177.1805416030548</v>
+      </c>
+      <c r="G47">
+        <v>155</v>
+      </c>
+      <c r="H47">
+        <v>387.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>182.667</v>
+      </c>
+      <c r="K47">
+        <v>80</v>
+      </c>
+      <c r="L47">
+        <v>102.667</v>
+      </c>
+      <c r="M47">
+        <v>8.380639617824491</v>
+      </c>
+      <c r="N47">
+        <v>94.28636038217552</v>
+      </c>
+      <c r="O47">
+        <v>17.91440847261334</v>
+      </c>
+      <c r="P47">
+        <v>76.37195190956217</v>
+      </c>
+      <c r="Q47">
+        <v>156.3719519095622</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2051634937644206</v>
+      </c>
+      <c r="T47">
+        <v>2.255831507565068</v>
+      </c>
+      <c r="U47">
+        <v>0.0473</v>
+      </c>
+      <c r="V47">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W47">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>12.25049694078733</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1298857978514769</v>
+      </c>
+      <c r="C48">
+        <v>236.0527878023116</v>
+      </c>
+      <c r="D48">
+        <v>262.1706747743232</v>
+      </c>
+      <c r="E48">
+        <v>175.1833500763343</v>
+      </c>
+      <c r="F48">
+        <v>181.1178869720115</v>
+      </c>
+      <c r="G48">
+        <v>155</v>
+      </c>
+      <c r="H48">
+        <v>387.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>182.667</v>
+      </c>
+      <c r="K48">
+        <v>80</v>
+      </c>
+      <c r="L48">
+        <v>102.667</v>
+      </c>
+      <c r="M48">
+        <v>8.566876053776147</v>
+      </c>
+      <c r="N48">
+        <v>94.10012394622386</v>
+      </c>
+      <c r="O48">
+        <v>17.87902354978253</v>
+      </c>
+      <c r="P48">
+        <v>76.22110039644133</v>
+      </c>
+      <c r="Q48">
+        <v>156.2211003964413</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2078922552805128</v>
+      </c>
+      <c r="T48">
+        <v>2.292832571111789</v>
+      </c>
+      <c r="U48">
+        <v>0.0473</v>
+      </c>
+      <c r="V48">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W48">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>11.98418178990065</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1296908241325225</v>
+      </c>
+      <c r="C49">
+        <v>232.6778357436741</v>
+      </c>
+      <c r="D49">
+        <v>262.7330680846425</v>
+      </c>
+      <c r="E49">
+        <v>179.1206954452911</v>
+      </c>
+      <c r="F49">
+        <v>185.0552323409683</v>
+      </c>
+      <c r="G49">
+        <v>155</v>
+      </c>
+      <c r="H49">
+        <v>387.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>182.667</v>
+      </c>
+      <c r="K49">
+        <v>80</v>
+      </c>
+      <c r="L49">
+        <v>102.667</v>
+      </c>
+      <c r="M49">
+        <v>8.753112489727803</v>
+      </c>
+      <c r="N49">
+        <v>93.9138875102722</v>
+      </c>
+      <c r="O49">
+        <v>17.84363862695171</v>
+      </c>
+      <c r="P49">
+        <v>76.07024888332049</v>
+      </c>
+      <c r="Q49">
+        <v>156.0702488833205</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2107239889292878</v>
+      </c>
+      <c r="T49">
+        <v>2.331229901207443</v>
+      </c>
+      <c r="U49">
+        <v>0.0473</v>
+      </c>
+      <c r="V49">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W49">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>11.72919919862616</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1294958504135681</v>
+      </c>
+      <c r="C50">
+        <v>229.3053016989752</v>
+      </c>
+      <c r="D50">
+        <v>263.2978794089003</v>
+      </c>
+      <c r="E50">
+        <v>183.0580408142478</v>
+      </c>
+      <c r="F50">
+        <v>188.9925777099251</v>
+      </c>
+      <c r="G50">
+        <v>155</v>
+      </c>
+      <c r="H50">
+        <v>387.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>182.667</v>
+      </c>
+      <c r="K50">
+        <v>80</v>
+      </c>
+      <c r="L50">
+        <v>102.667</v>
+      </c>
+      <c r="M50">
+        <v>8.939348925679457</v>
+      </c>
+      <c r="N50">
+        <v>93.72765107432055</v>
+      </c>
+      <c r="O50">
+        <v>17.8082537041209</v>
+      </c>
+      <c r="P50">
+        <v>75.91939737019965</v>
+      </c>
+      <c r="Q50">
+        <v>155.9193973701996</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2136646354107078</v>
+      </c>
+      <c r="T50">
+        <v>2.371104051691391</v>
+      </c>
+      <c r="U50">
+        <v>0.0473</v>
+      </c>
+      <c r="V50">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W50">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>11.48484088198812</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1293008766946137</v>
+      </c>
+      <c r="C51">
+        <v>225.9352012962124</v>
+      </c>
+      <c r="D51">
+        <v>263.8651243750942</v>
+      </c>
+      <c r="E51">
+        <v>186.9953861832046</v>
+      </c>
+      <c r="F51">
+        <v>192.9299230788818</v>
+      </c>
+      <c r="G51">
+        <v>155</v>
+      </c>
+      <c r="H51">
+        <v>387.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>182.667</v>
+      </c>
+      <c r="K51">
+        <v>80</v>
+      </c>
+      <c r="L51">
+        <v>102.667</v>
+      </c>
+      <c r="M51">
+        <v>9.125585361631112</v>
+      </c>
+      <c r="N51">
+        <v>93.54141463836889</v>
+      </c>
+      <c r="O51">
+        <v>17.77286878129009</v>
+      </c>
+      <c r="P51">
+        <v>75.76854585707881</v>
+      </c>
+      <c r="Q51">
+        <v>155.7685458570788</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2167206013619876</v>
+      </c>
+      <c r="T51">
+        <v>2.41254189435118</v>
+      </c>
+      <c r="U51">
+        <v>0.0473</v>
+      </c>
+      <c r="V51">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W51">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>11.25045637419244</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1291059029756592</v>
+      </c>
+      <c r="C52">
+        <v>222.5675502983495</v>
+      </c>
+      <c r="D52">
+        <v>264.4348187461882</v>
+      </c>
+      <c r="E52">
+        <v>190.9327315521614</v>
+      </c>
+      <c r="F52">
+        <v>196.8672684478386</v>
+      </c>
+      <c r="G52">
+        <v>155</v>
+      </c>
+      <c r="H52">
+        <v>387.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>182.667</v>
+      </c>
+      <c r="K52">
+        <v>80</v>
+      </c>
+      <c r="L52">
+        <v>102.667</v>
+      </c>
+      <c r="M52">
+        <v>9.311821797582768</v>
+      </c>
+      <c r="N52">
+        <v>93.35517820241724</v>
+      </c>
+      <c r="O52">
+        <v>17.73748385845927</v>
+      </c>
+      <c r="P52">
+        <v>75.61769434395796</v>
+      </c>
+      <c r="Q52">
+        <v>155.617694343958</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2198988059513185</v>
+      </c>
+      <c r="T52">
+        <v>2.45563725071736</v>
+      </c>
+      <c r="U52">
+        <v>0.0473</v>
+      </c>
+      <c r="V52">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W52">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>11.02544724670859</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1289109292567048</v>
+      </c>
+      <c r="C53">
+        <v>219.2023646047758</v>
+      </c>
+      <c r="D53">
+        <v>265.0069784215712</v>
+      </c>
+      <c r="E53">
+        <v>194.8700769211182</v>
+      </c>
+      <c r="F53">
+        <v>200.8046138167954</v>
+      </c>
+      <c r="G53">
+        <v>155</v>
+      </c>
+      <c r="H53">
+        <v>387.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>182.667</v>
+      </c>
+      <c r="K53">
+        <v>80</v>
+      </c>
+      <c r="L53">
+        <v>102.667</v>
+      </c>
+      <c r="M53">
+        <v>9.498058233534422</v>
+      </c>
+      <c r="N53">
+        <v>93.16894176646558</v>
+      </c>
+      <c r="O53">
+        <v>17.70209893562846</v>
+      </c>
+      <c r="P53">
+        <v>75.46684283083712</v>
+      </c>
+      <c r="Q53">
+        <v>155.4668428308371</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2232067331769486</v>
+      </c>
+      <c r="T53">
+        <v>2.500491601220936</v>
+      </c>
+      <c r="U53">
+        <v>0.0473</v>
+      </c>
+      <c r="V53">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W53">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>10.80926200657705</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1287159555377504</v>
+      </c>
+      <c r="C54">
+        <v>215.8396602527855</v>
+      </c>
+      <c r="D54">
+        <v>265.5816194385377</v>
+      </c>
+      <c r="E54">
+        <v>198.8074222900749</v>
+      </c>
+      <c r="F54">
+        <v>204.7419591857522</v>
+      </c>
+      <c r="G54">
+        <v>155</v>
+      </c>
+      <c r="H54">
+        <v>387.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>182.667</v>
+      </c>
+      <c r="K54">
+        <v>80</v>
+      </c>
+      <c r="L54">
+        <v>102.667</v>
+      </c>
+      <c r="M54">
+        <v>9.684294669486079</v>
+      </c>
+      <c r="N54">
+        <v>92.98270533051392</v>
+      </c>
+      <c r="O54">
+        <v>17.66671401279764</v>
+      </c>
+      <c r="P54">
+        <v>75.31599131771628</v>
+      </c>
+      <c r="Q54">
+        <v>155.3159913177163</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2266524907036467</v>
+      </c>
+      <c r="T54">
+        <v>2.547214882995494</v>
+      </c>
+      <c r="U54">
+        <v>0.0473</v>
+      </c>
+      <c r="V54">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W54">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>10.60139158337365</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.128520981818796</v>
+      </c>
+      <c r="C55">
+        <v>212.4794534190763</v>
+      </c>
+      <c r="D55">
+        <v>266.1587579737852</v>
+      </c>
+      <c r="E55">
+        <v>202.7447676590317</v>
+      </c>
+      <c r="F55">
+        <v>208.6793045547089</v>
+      </c>
+      <c r="G55">
+        <v>155</v>
+      </c>
+      <c r="H55">
+        <v>387.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>182.667</v>
+      </c>
+      <c r="K55">
+        <v>80</v>
+      </c>
+      <c r="L55">
+        <v>102.667</v>
+      </c>
+      <c r="M55">
+        <v>9.870531105437733</v>
+      </c>
+      <c r="N55">
+        <v>92.79646889456227</v>
+      </c>
+      <c r="O55">
+        <v>17.63132908996683</v>
+      </c>
+      <c r="P55">
+        <v>75.16513980459544</v>
+      </c>
+      <c r="Q55">
+        <v>155.1651398045954</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2302448762102042</v>
+      </c>
+      <c r="T55">
+        <v>2.595926389526416</v>
+      </c>
+      <c r="U55">
+        <v>0.0473</v>
+      </c>
+      <c r="V55">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W55">
+        <v>0.03831300000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>10.40136532708358</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1299881280998416</v>
+      </c>
+      <c r="C56">
+        <v>204.2598199928255</v>
+      </c>
+      <c r="D56">
+        <v>261.8764699164912</v>
+      </c>
+      <c r="E56">
+        <v>206.6821130279885</v>
+      </c>
+      <c r="F56">
+        <v>212.6166499236657</v>
+      </c>
+      <c r="G56">
+        <v>155</v>
+      </c>
+      <c r="H56">
+        <v>387.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>182.667</v>
+      </c>
+      <c r="K56">
+        <v>80</v>
+      </c>
+      <c r="L56">
+        <v>102.667</v>
+      </c>
+      <c r="M56">
+        <v>10.86471081109932</v>
+      </c>
+      <c r="N56">
+        <v>91.80228918890069</v>
+      </c>
+      <c r="O56">
+        <v>17.44243494589113</v>
+      </c>
+      <c r="P56">
+        <v>74.35985424300956</v>
+      </c>
+      <c r="Q56">
+        <v>154.3598542430096</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2339934523909599</v>
+      </c>
+      <c r="T56">
+        <v>2.646755787645639</v>
+      </c>
+      <c r="U56">
+        <v>0.0511</v>
+      </c>
+      <c r="V56">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W56">
+        <v>0.041391</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>9.449584235147434</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1298239343808871</v>
+      </c>
+      <c r="C57">
+        <v>200.7948610549179</v>
+      </c>
+      <c r="D57">
+        <v>262.3488563475404</v>
+      </c>
+      <c r="E57">
+        <v>210.6194583969453</v>
+      </c>
+      <c r="F57">
+        <v>216.5539952926225</v>
+      </c>
+      <c r="G57">
+        <v>155</v>
+      </c>
+      <c r="H57">
+        <v>387.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>182.667</v>
+      </c>
+      <c r="K57">
+        <v>80</v>
+      </c>
+      <c r="L57">
+        <v>102.667</v>
+      </c>
+      <c r="M57">
+        <v>11.06590915945301</v>
+      </c>
+      <c r="N57">
+        <v>91.60109084054699</v>
+      </c>
+      <c r="O57">
+        <v>17.40420725970392</v>
+      </c>
+      <c r="P57">
+        <v>74.19688358084306</v>
+      </c>
+      <c r="Q57">
+        <v>154.1968835808431</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.237908631957527</v>
+      </c>
+      <c r="T57">
+        <v>2.699844270125717</v>
+      </c>
+      <c r="U57">
+        <v>0.0511</v>
+      </c>
+      <c r="V57">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W57">
+        <v>0.041391</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>9.277773612690206</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1296597406619327</v>
+      </c>
+      <c r="C58">
+        <v>197.3316094272961</v>
+      </c>
+      <c r="D58">
+        <v>262.8229500888754</v>
+      </c>
+      <c r="E58">
+        <v>214.556803765902</v>
+      </c>
+      <c r="F58">
+        <v>220.4913406615793</v>
+      </c>
+      <c r="G58">
+        <v>155</v>
+      </c>
+      <c r="H58">
+        <v>387.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>182.667</v>
+      </c>
+      <c r="K58">
+        <v>80</v>
+      </c>
+      <c r="L58">
+        <v>102.667</v>
+      </c>
+      <c r="M58">
+        <v>11.2671075078067</v>
+      </c>
+      <c r="N58">
+        <v>91.3998924921933</v>
+      </c>
+      <c r="O58">
+        <v>17.36597957351672</v>
+      </c>
+      <c r="P58">
+        <v>74.03391291867658</v>
+      </c>
+      <c r="Q58">
+        <v>154.0339129186766</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2420017742316653</v>
+      </c>
+      <c r="T58">
+        <v>2.755345865445798</v>
+      </c>
+      <c r="U58">
+        <v>0.0511</v>
+      </c>
+      <c r="V58">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W58">
+        <v>0.041391</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>9.112099083892168</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1294955469429783</v>
+      </c>
+      <c r="C59">
+        <v>193.8700743826191</v>
+      </c>
+      <c r="D59">
+        <v>263.2987604131552</v>
+      </c>
+      <c r="E59">
+        <v>218.4941491348588</v>
+      </c>
+      <c r="F59">
+        <v>224.4286860305361</v>
+      </c>
+      <c r="G59">
+        <v>155</v>
+      </c>
+      <c r="H59">
+        <v>387.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>182.667</v>
+      </c>
+      <c r="K59">
+        <v>80</v>
+      </c>
+      <c r="L59">
+        <v>102.667</v>
+      </c>
+      <c r="M59">
+        <v>11.46830585616039</v>
+      </c>
+      <c r="N59">
+        <v>91.1986941438396</v>
+      </c>
+      <c r="O59">
+        <v>17.32775188732952</v>
+      </c>
+      <c r="P59">
+        <v>73.87094225651009</v>
+      </c>
+      <c r="Q59">
+        <v>153.8709422565101</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2462852952162286</v>
+      </c>
+      <c r="T59">
+        <v>2.81342893031565</v>
+      </c>
+      <c r="U59">
+        <v>0.0511</v>
+      </c>
+      <c r="V59">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W59">
+        <v>0.041391</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.952237696455462</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1293313532240238</v>
+      </c>
+      <c r="C60">
+        <v>190.4102652608159</v>
+      </c>
+      <c r="D60">
+        <v>263.7762966603087</v>
+      </c>
+      <c r="E60">
+        <v>222.4314945038155</v>
+      </c>
+      <c r="F60">
+        <v>228.3660313994928</v>
+      </c>
+      <c r="G60">
+        <v>155</v>
+      </c>
+      <c r="H60">
+        <v>387.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>182.667</v>
+      </c>
+      <c r="K60">
+        <v>80</v>
+      </c>
+      <c r="L60">
+        <v>102.667</v>
+      </c>
+      <c r="M60">
+        <v>11.66950420451408</v>
+      </c>
+      <c r="N60">
+        <v>90.99749579548592</v>
+      </c>
+      <c r="O60">
+        <v>17.28952420114232</v>
+      </c>
+      <c r="P60">
+        <v>73.7079715943436</v>
+      </c>
+      <c r="Q60">
+        <v>153.7079715943436</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2507727933905329</v>
+      </c>
+      <c r="T60">
+        <v>2.874277855417399</v>
+      </c>
+      <c r="U60">
+        <v>0.0511</v>
+      </c>
+      <c r="V60">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W60">
+        <v>0.041391</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>8.797888770654506</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1291671595050694</v>
+      </c>
+      <c r="C61">
+        <v>186.9521914696965</v>
+      </c>
+      <c r="D61">
+        <v>264.2555682381461</v>
+      </c>
+      <c r="E61">
+        <v>226.3688398727723</v>
+      </c>
+      <c r="F61">
+        <v>232.3033767684496</v>
+      </c>
+      <c r="G61">
+        <v>155</v>
+      </c>
+      <c r="H61">
+        <v>387.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>182.667</v>
+      </c>
+      <c r="K61">
+        <v>80</v>
+      </c>
+      <c r="L61">
+        <v>102.667</v>
+      </c>
+      <c r="M61">
+        <v>11.87070255286777</v>
+      </c>
+      <c r="N61">
+        <v>90.79629744713223</v>
+      </c>
+      <c r="O61">
+        <v>17.25129651495512</v>
+      </c>
+      <c r="P61">
+        <v>73.54500093217712</v>
+      </c>
+      <c r="Q61">
+        <v>153.5450009321771</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2554791939148034</v>
+      </c>
+      <c r="T61">
+        <v>2.938095020768015</v>
+      </c>
+      <c r="U61">
+        <v>0.0511</v>
+      </c>
+      <c r="V61">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W61">
+        <v>0.041391</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>8.648772011829855</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.129002965786115</v>
+      </c>
+      <c r="C62">
+        <v>183.4958624855704</v>
+      </c>
+      <c r="D62">
+        <v>264.7365846229767</v>
+      </c>
+      <c r="E62">
+        <v>230.3061852417291</v>
+      </c>
+      <c r="F62">
+        <v>236.2407221374064</v>
+      </c>
+      <c r="G62">
+        <v>155</v>
+      </c>
+      <c r="H62">
+        <v>387.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>182.667</v>
+      </c>
+      <c r="K62">
+        <v>80</v>
+      </c>
+      <c r="L62">
+        <v>102.667</v>
+      </c>
+      <c r="M62">
+        <v>12.07190090122146</v>
+      </c>
+      <c r="N62">
+        <v>90.59509909877853</v>
+      </c>
+      <c r="O62">
+        <v>17.21306882876792</v>
+      </c>
+      <c r="P62">
+        <v>73.38203027001062</v>
+      </c>
+      <c r="Q62">
+        <v>153.3820302700106</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2604209144652875</v>
+      </c>
+      <c r="T62">
+        <v>3.005103044386161</v>
+      </c>
+      <c r="U62">
+        <v>0.0511</v>
+      </c>
+      <c r="V62">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W62">
+        <v>0.041391</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>8.504625811632689</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1288387720671606</v>
+      </c>
+      <c r="C63">
+        <v>180.0412878538701</v>
+      </c>
+      <c r="D63">
+        <v>265.2193553602332</v>
+      </c>
+      <c r="E63">
+        <v>234.2435306106859</v>
+      </c>
+      <c r="F63">
+        <v>240.1780675063631</v>
+      </c>
+      <c r="G63">
+        <v>155</v>
+      </c>
+      <c r="H63">
+        <v>387.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>182.667</v>
+      </c>
+      <c r="K63">
+        <v>80</v>
+      </c>
+      <c r="L63">
+        <v>102.667</v>
+      </c>
+      <c r="M63">
+        <v>12.27309924957516</v>
+      </c>
+      <c r="N63">
+        <v>90.39390075042485</v>
+      </c>
+      <c r="O63">
+        <v>17.17484114258072</v>
+      </c>
+      <c r="P63">
+        <v>73.21905960784413</v>
+      </c>
+      <c r="Q63">
+        <v>153.2190596078441</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2656160565824631</v>
+      </c>
+      <c r="T63">
+        <v>3.075547376907803</v>
+      </c>
+      <c r="U63">
+        <v>0.0511</v>
+      </c>
+      <c r="V63">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W63">
+        <v>0.041391</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>8.365205716360023</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1286745783482062</v>
+      </c>
+      <c r="C64">
+        <v>176.5884771897837</v>
+      </c>
+      <c r="D64">
+        <v>265.7038900651036</v>
+      </c>
+      <c r="E64">
+        <v>238.1808759796427</v>
+      </c>
+      <c r="F64">
+        <v>244.1154128753199</v>
+      </c>
+      <c r="G64">
+        <v>155</v>
+      </c>
+      <c r="H64">
+        <v>387.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>182.667</v>
+      </c>
+      <c r="K64">
+        <v>80</v>
+      </c>
+      <c r="L64">
+        <v>102.667</v>
+      </c>
+      <c r="M64">
+        <v>12.47429759792885</v>
+      </c>
+      <c r="N64">
+        <v>90.19270240207115</v>
+      </c>
+      <c r="O64">
+        <v>17.13661345639351</v>
+      </c>
+      <c r="P64">
+        <v>73.05608894567763</v>
+      </c>
+      <c r="Q64">
+        <v>153.0560889456776</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2710846272321215</v>
+      </c>
+      <c r="T64">
+        <v>3.149699305877952</v>
+      </c>
+      <c r="U64">
+        <v>0.0511</v>
+      </c>
+      <c r="V64">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W64">
+        <v>0.041391</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>8.230283043515506</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1285103846292517</v>
+      </c>
+      <c r="C65">
+        <v>173.1374401788921</v>
+      </c>
+      <c r="D65">
+        <v>266.1901984231688</v>
+      </c>
+      <c r="E65">
+        <v>242.1182213485994</v>
+      </c>
+      <c r="F65">
+        <v>248.0527582442767</v>
+      </c>
+      <c r="G65">
+        <v>155</v>
+      </c>
+      <c r="H65">
+        <v>387.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>182.667</v>
+      </c>
+      <c r="K65">
+        <v>80</v>
+      </c>
+      <c r="L65">
+        <v>102.667</v>
+      </c>
+      <c r="M65">
+        <v>12.67549594628254</v>
+      </c>
+      <c r="N65">
+        <v>89.99150405371746</v>
+      </c>
+      <c r="O65">
+        <v>17.09838577020631</v>
+      </c>
+      <c r="P65">
+        <v>72.89311828351114</v>
+      </c>
+      <c r="Q65">
+        <v>152.8931182835111</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2768487962952749</v>
+      </c>
+      <c r="T65">
+        <v>3.227859447224865</v>
+      </c>
+      <c r="U65">
+        <v>0.0511</v>
+      </c>
+      <c r="V65">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W65">
+        <v>0.041391</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>8.099643630126371</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1283461909102973</v>
+      </c>
+      <c r="C66">
+        <v>169.6881865778151</v>
+      </c>
+      <c r="D66">
+        <v>266.6782901910485</v>
+      </c>
+      <c r="E66">
+        <v>246.0555667175562</v>
+      </c>
+      <c r="F66">
+        <v>251.9901036132335</v>
+      </c>
+      <c r="G66">
+        <v>155</v>
+      </c>
+      <c r="H66">
+        <v>387.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>182.667</v>
+      </c>
+      <c r="K66">
+        <v>80</v>
+      </c>
+      <c r="L66">
+        <v>102.667</v>
+      </c>
+      <c r="M66">
+        <v>12.87669429463623</v>
+      </c>
+      <c r="N66">
+        <v>89.79030570536378</v>
+      </c>
+      <c r="O66">
+        <v>17.06015808401911</v>
+      </c>
+      <c r="P66">
+        <v>72.73014762134466</v>
+      </c>
+      <c r="Q66">
+        <v>152.7301476213447</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2829331969730481</v>
+      </c>
+      <c r="T66">
+        <v>3.310361818646607</v>
+      </c>
+      <c r="U66">
+        <v>0.0511</v>
+      </c>
+      <c r="V66">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W66">
+        <v>0.041391</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>7.973086698405647</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1281819971913429</v>
+      </c>
+      <c r="C67">
+        <v>166.240726214864</v>
+      </c>
+      <c r="D67">
+        <v>267.1681751970542</v>
+      </c>
+      <c r="E67">
+        <v>249.992912086513</v>
+      </c>
+      <c r="F67">
+        <v>255.9274489821902</v>
+      </c>
+      <c r="G67">
+        <v>155</v>
+      </c>
+      <c r="H67">
+        <v>387.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>182.667</v>
+      </c>
+      <c r="K67">
+        <v>80</v>
+      </c>
+      <c r="L67">
+        <v>102.667</v>
+      </c>
+      <c r="M67">
+        <v>13.07789264298992</v>
+      </c>
+      <c r="N67">
+        <v>89.58910735701008</v>
+      </c>
+      <c r="O67">
+        <v>17.02193039783191</v>
+      </c>
+      <c r="P67">
+        <v>72.56717695917817</v>
+      </c>
+      <c r="Q67">
+        <v>152.5671769591782</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2893652776895512</v>
+      </c>
+      <c r="T67">
+        <v>3.397578611292449</v>
+      </c>
+      <c r="U67">
+        <v>0.0511</v>
+      </c>
+      <c r="V67">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W67">
+        <v>0.041391</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>7.850423826122483</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1290335434723885</v>
+      </c>
+      <c r="C68">
+        <v>159.7820782654272</v>
+      </c>
+      <c r="D68">
+        <v>264.6468726165742</v>
+      </c>
+      <c r="E68">
+        <v>253.9302574554698</v>
+      </c>
+      <c r="F68">
+        <v>259.864794351147</v>
+      </c>
+      <c r="G68">
+        <v>155</v>
+      </c>
+      <c r="H68">
+        <v>387.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>182.667</v>
+      </c>
+      <c r="K68">
+        <v>80</v>
+      </c>
+      <c r="L68">
+        <v>102.667</v>
+      </c>
+      <c r="M68">
+        <v>13.77283410061079</v>
+      </c>
+      <c r="N68">
+        <v>88.89416589938921</v>
+      </c>
+      <c r="O68">
+        <v>16.88989152088395</v>
+      </c>
+      <c r="P68">
+        <v>72.00427437850526</v>
+      </c>
+      <c r="Q68">
+        <v>152.0042743785053</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2961757160952603</v>
+      </c>
+      <c r="T68">
+        <v>3.489925803505693</v>
+      </c>
+      <c r="U68">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W68">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>7.454311817743232</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.128884739753434</v>
+      </c>
+      <c r="C69">
+        <v>156.2818817294781</v>
+      </c>
+      <c r="D69">
+        <v>265.0840214495818</v>
+      </c>
+      <c r="E69">
+        <v>257.8676028244265</v>
+      </c>
+      <c r="F69">
+        <v>263.8021397201038</v>
+      </c>
+      <c r="G69">
+        <v>155</v>
+      </c>
+      <c r="H69">
+        <v>387.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>182.667</v>
+      </c>
+      <c r="K69">
+        <v>80</v>
+      </c>
+      <c r="L69">
+        <v>102.667</v>
+      </c>
+      <c r="M69">
+        <v>13.9815134051655</v>
+      </c>
+      <c r="N69">
+        <v>88.6854865948345</v>
+      </c>
+      <c r="O69">
+        <v>16.85024245301855</v>
+      </c>
+      <c r="P69">
+        <v>71.83524414181595</v>
+      </c>
+      <c r="Q69">
+        <v>151.835244141816</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3033989083437396</v>
+      </c>
+      <c r="T69">
+        <v>3.587869795247012</v>
+      </c>
+      <c r="U69">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W69">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>7.343053432403781</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1287359360344796</v>
+      </c>
+      <c r="C70">
+        <v>152.7831317648318</v>
+      </c>
+      <c r="D70">
+        <v>265.5226168538923</v>
+      </c>
+      <c r="E70">
+        <v>261.8049481933833</v>
+      </c>
+      <c r="F70">
+        <v>267.7394850890606</v>
+      </c>
+      <c r="G70">
+        <v>155</v>
+      </c>
+      <c r="H70">
+        <v>387.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>182.667</v>
+      </c>
+      <c r="K70">
+        <v>80</v>
+      </c>
+      <c r="L70">
+        <v>102.667</v>
+      </c>
+      <c r="M70">
+        <v>14.19019270972021</v>
+      </c>
+      <c r="N70">
+        <v>88.47680729027979</v>
+      </c>
+      <c r="O70">
+        <v>16.81059338515315</v>
+      </c>
+      <c r="P70">
+        <v>71.66621390512664</v>
+      </c>
+      <c r="Q70">
+        <v>151.6662139051267</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3110735501077489</v>
+      </c>
+      <c r="T70">
+        <v>3.691935286472164</v>
+      </c>
+      <c r="U70">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W70">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>7.23506735251549</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1285871323155252</v>
+      </c>
+      <c r="C71">
+        <v>149.2858355636725</v>
+      </c>
+      <c r="D71">
+        <v>265.9626660216899</v>
+      </c>
+      <c r="E71">
+        <v>265.7422935623401</v>
+      </c>
+      <c r="F71">
+        <v>271.6768304580173</v>
+      </c>
+      <c r="G71">
+        <v>155</v>
+      </c>
+      <c r="H71">
+        <v>387.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>182.667</v>
+      </c>
+      <c r="K71">
+        <v>80</v>
+      </c>
+      <c r="L71">
+        <v>102.667</v>
+      </c>
+      <c r="M71">
+        <v>14.39887201427492</v>
+      </c>
+      <c r="N71">
+        <v>88.26812798572509</v>
+      </c>
+      <c r="O71">
+        <v>16.77094431728776</v>
+      </c>
+      <c r="P71">
+        <v>71.49718366843733</v>
+      </c>
+      <c r="Q71">
+        <v>151.4971836684373</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3192433300500814</v>
+      </c>
+      <c r="T71">
+        <v>3.802714680357004</v>
+      </c>
+      <c r="U71">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W71">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>7.130211303928308</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1284383285965708</v>
+      </c>
+      <c r="C72">
+        <v>145.7900003659415</v>
+      </c>
+      <c r="D72">
+        <v>266.4041761929155</v>
+      </c>
+      <c r="E72">
+        <v>269.6796389312968</v>
+      </c>
+      <c r="F72">
+        <v>275.6141758269741</v>
+      </c>
+      <c r="G72">
+        <v>155</v>
+      </c>
+      <c r="H72">
+        <v>387.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>182.667</v>
+      </c>
+      <c r="K72">
+        <v>80</v>
+      </c>
+      <c r="L72">
+        <v>102.667</v>
+      </c>
+      <c r="M72">
+        <v>14.60755131882963</v>
+      </c>
+      <c r="N72">
+        <v>88.05944868117038</v>
+      </c>
+      <c r="O72">
+        <v>16.73129524942237</v>
+      </c>
+      <c r="P72">
+        <v>71.32815343174801</v>
+      </c>
+      <c r="Q72">
+        <v>151.328153431748</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3279577619885694</v>
+      </c>
+      <c r="T72">
+        <v>3.920879367167498</v>
+      </c>
+      <c r="U72">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W72">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>7.028351142443618</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1282895248776164</v>
+      </c>
+      <c r="C73">
+        <v>142.2956334597345</v>
+      </c>
+      <c r="D73">
+        <v>266.8471546556653</v>
+      </c>
+      <c r="E73">
+        <v>273.6169843002536</v>
+      </c>
+      <c r="F73">
+        <v>279.5515211959308</v>
+      </c>
+      <c r="G73">
+        <v>155</v>
+      </c>
+      <c r="H73">
+        <v>387.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>182.667</v>
+      </c>
+      <c r="K73">
+        <v>80</v>
+      </c>
+      <c r="L73">
+        <v>102.667</v>
+      </c>
+      <c r="M73">
+        <v>14.81623062338434</v>
+      </c>
+      <c r="N73">
+        <v>87.85076937661566</v>
+      </c>
+      <c r="O73">
+        <v>16.69164618155697</v>
+      </c>
+      <c r="P73">
+        <v>71.1591231950587</v>
+      </c>
+      <c r="Q73">
+        <v>151.1591231950587</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3372731892331599</v>
+      </c>
+      <c r="T73">
+        <v>4.047193342723544</v>
+      </c>
+      <c r="U73">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W73">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.929360281282441</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.128140721158662</v>
+      </c>
+      <c r="C74">
+        <v>138.8027421817029</v>
+      </c>
+      <c r="D74">
+        <v>267.2916087465905</v>
+      </c>
+      <c r="E74">
+        <v>277.5543296692103</v>
+      </c>
+      <c r="F74">
+        <v>283.4888665648876</v>
+      </c>
+      <c r="G74">
+        <v>155</v>
+      </c>
+      <c r="H74">
+        <v>387.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>182.667</v>
+      </c>
+      <c r="K74">
+        <v>80</v>
+      </c>
+      <c r="L74">
+        <v>102.667</v>
+      </c>
+      <c r="M74">
+        <v>15.02490992793904</v>
+      </c>
+      <c r="N74">
+        <v>87.64209007206095</v>
+      </c>
+      <c r="O74">
+        <v>16.65199711369157</v>
+      </c>
+      <c r="P74">
+        <v>70.99009295836937</v>
+      </c>
+      <c r="Q74">
+        <v>150.9900929583694</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3472540041380783</v>
+      </c>
+      <c r="T74">
+        <v>4.182529745105022</v>
+      </c>
+      <c r="U74">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W74">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.83311916626463</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1279919174397075</v>
+      </c>
+      <c r="C75">
+        <v>135.3113339174583</v>
+      </c>
+      <c r="D75">
+        <v>267.7375458513027</v>
+      </c>
+      <c r="E75">
+        <v>281.4916750381672</v>
+      </c>
+      <c r="F75">
+        <v>287.4262119338444</v>
+      </c>
+      <c r="G75">
+        <v>155</v>
+      </c>
+      <c r="H75">
+        <v>387.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>182.667</v>
+      </c>
+      <c r="K75">
+        <v>80</v>
+      </c>
+      <c r="L75">
+        <v>102.667</v>
+      </c>
+      <c r="M75">
+        <v>15.23358923249375</v>
+      </c>
+      <c r="N75">
+        <v>87.43341076750625</v>
+      </c>
+      <c r="O75">
+        <v>16.61234804582618</v>
+      </c>
+      <c r="P75">
+        <v>70.82106272168006</v>
+      </c>
+      <c r="Q75">
+        <v>150.8210627216801</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3579741386655834</v>
+      </c>
+      <c r="T75">
+        <v>4.327891066181425</v>
+      </c>
+      <c r="U75">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W75">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>6.739514794124018</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1278431137207531</v>
+      </c>
+      <c r="C76">
+        <v>131.8214161019826</v>
+      </c>
+      <c r="D76">
+        <v>268.1849734047838</v>
+      </c>
+      <c r="E76">
+        <v>285.4290204071239</v>
+      </c>
+      <c r="F76">
+        <v>291.3635573028012</v>
+      </c>
+      <c r="G76">
+        <v>155</v>
+      </c>
+      <c r="H76">
+        <v>387.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>182.667</v>
+      </c>
+      <c r="K76">
+        <v>80</v>
+      </c>
+      <c r="L76">
+        <v>102.667</v>
+      </c>
+      <c r="M76">
+        <v>15.44226853704846</v>
+      </c>
+      <c r="N76">
+        <v>87.22473146295154</v>
+      </c>
+      <c r="O76">
+        <v>16.57269897796079</v>
+      </c>
+      <c r="P76">
+        <v>70.65203248499076</v>
+      </c>
+      <c r="Q76">
+        <v>150.6520324849907</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3695188989259734</v>
+      </c>
+      <c r="T76">
+        <v>4.484434027340628</v>
+      </c>
+      <c r="U76">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W76">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>6.648440269879099</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1276943100017987</v>
+      </c>
+      <c r="C77">
+        <v>128.3329962200398</v>
+      </c>
+      <c r="D77">
+        <v>268.6338988917977</v>
+      </c>
+      <c r="E77">
+        <v>289.3663657760807</v>
+      </c>
+      <c r="F77">
+        <v>295.300902671758</v>
+      </c>
+      <c r="G77">
+        <v>155</v>
+      </c>
+      <c r="H77">
+        <v>387.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>182.667</v>
+      </c>
+      <c r="K77">
+        <v>80</v>
+      </c>
+      <c r="L77">
+        <v>102.667</v>
+      </c>
+      <c r="M77">
+        <v>15.65094784160317</v>
+      </c>
+      <c r="N77">
+        <v>87.01605215839683</v>
+      </c>
+      <c r="O77">
+        <v>16.53304991009539</v>
+      </c>
+      <c r="P77">
+        <v>70.48300224830143</v>
+      </c>
+      <c r="Q77">
+        <v>150.4830022483014</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3819872400071947</v>
+      </c>
+      <c r="T77">
+        <v>4.653500425392567</v>
+      </c>
+      <c r="U77">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W77">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>6.559794399614044</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1275455062828443</v>
+      </c>
+      <c r="C78">
+        <v>124.8460818065943</v>
+      </c>
+      <c r="D78">
+        <v>269.084329847309</v>
+      </c>
+      <c r="E78">
+        <v>293.3037111450375</v>
+      </c>
+      <c r="F78">
+        <v>299.2382480407147</v>
+      </c>
+      <c r="G78">
+        <v>155</v>
+      </c>
+      <c r="H78">
+        <v>387.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>182.667</v>
+      </c>
+      <c r="K78">
+        <v>80</v>
+      </c>
+      <c r="L78">
+        <v>102.667</v>
+      </c>
+      <c r="M78">
+        <v>15.85962714615788</v>
+      </c>
+      <c r="N78">
+        <v>86.80737285384212</v>
+      </c>
+      <c r="O78">
+        <v>16.49340084223</v>
+      </c>
+      <c r="P78">
+        <v>70.31397201161212</v>
+      </c>
+      <c r="Q78">
+        <v>150.3139720116121</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3954946095118511</v>
+      </c>
+      <c r="T78">
+        <v>4.836655689948834</v>
+      </c>
+      <c r="U78">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W78">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>6.473481315408597</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1273967025638899</v>
+      </c>
+      <c r="C79">
+        <v>121.3606804472328</v>
+      </c>
+      <c r="D79">
+        <v>269.5362738569042</v>
+      </c>
+      <c r="E79">
+        <v>297.2410565139942</v>
+      </c>
+      <c r="F79">
+        <v>303.1755934096715</v>
+      </c>
+      <c r="G79">
+        <v>155</v>
+      </c>
+      <c r="H79">
+        <v>387.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>182.667</v>
+      </c>
+      <c r="K79">
+        <v>80</v>
+      </c>
+      <c r="L79">
+        <v>102.667</v>
+      </c>
+      <c r="M79">
+        <v>16.06830645071259</v>
+      </c>
+      <c r="N79">
+        <v>86.59869354928742</v>
+      </c>
+      <c r="O79">
+        <v>16.4537517743646</v>
+      </c>
+      <c r="P79">
+        <v>70.14494177492281</v>
+      </c>
+      <c r="Q79">
+        <v>150.1449417749228</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4101765328864775</v>
+      </c>
+      <c r="T79">
+        <v>5.035737499249125</v>
+      </c>
+      <c r="U79">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W79">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>6.389410129494199</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1272478988449354</v>
+      </c>
+      <c r="C80">
+        <v>117.876799778589</v>
+      </c>
+      <c r="D80">
+        <v>269.9897385572173</v>
+      </c>
+      <c r="E80">
+        <v>301.1784018829511</v>
+      </c>
+      <c r="F80">
+        <v>307.1129387786283</v>
+      </c>
+      <c r="G80">
+        <v>155</v>
+      </c>
+      <c r="H80">
+        <v>387.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>182.667</v>
+      </c>
+      <c r="K80">
+        <v>80</v>
+      </c>
+      <c r="L80">
+        <v>102.667</v>
+      </c>
+      <c r="M80">
+        <v>16.2769857552673</v>
+      </c>
+      <c r="N80">
+        <v>86.3900142447327</v>
+      </c>
+      <c r="O80">
+        <v>16.41410270649921</v>
+      </c>
+      <c r="P80">
+        <v>69.97591153823349</v>
+      </c>
+      <c r="Q80">
+        <v>149.9759115382335</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4261931765678882</v>
+      </c>
+      <c r="T80">
+        <v>5.252917654849441</v>
+      </c>
+      <c r="U80">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W80">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>6.307494615013503</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.127099095125981</v>
+      </c>
+      <c r="C81">
+        <v>114.3944474887744</v>
+      </c>
+      <c r="D81">
+        <v>270.4447316363594</v>
+      </c>
+      <c r="E81">
+        <v>305.1157472519078</v>
+      </c>
+      <c r="F81">
+        <v>311.050284147585</v>
+      </c>
+      <c r="G81">
+        <v>155</v>
+      </c>
+      <c r="H81">
+        <v>387.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>182.667</v>
+      </c>
+      <c r="K81">
+        <v>80</v>
+      </c>
+      <c r="L81">
+        <v>102.667</v>
+      </c>
+      <c r="M81">
+        <v>16.48566505982201</v>
+      </c>
+      <c r="N81">
+        <v>86.18133494017799</v>
+      </c>
+      <c r="O81">
+        <v>16.37445363863381</v>
+      </c>
+      <c r="P81">
+        <v>69.80688130154418</v>
+      </c>
+      <c r="Q81">
+        <v>149.8068813015442</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4437352148856238</v>
+      </c>
+      <c r="T81">
+        <v>5.490781634792646</v>
+      </c>
+      <c r="U81">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V81">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W81">
+        <v>0.04293000000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>6.227652911025992</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1282462914070266</v>
+      </c>
+      <c r="C82">
+        <v>106.9885045348178</v>
+      </c>
+      <c r="D82">
+        <v>266.9761340513596</v>
+      </c>
+      <c r="E82">
+        <v>309.0530926208646</v>
+      </c>
+      <c r="F82">
+        <v>314.9876295165418</v>
+      </c>
+      <c r="G82">
+        <v>155</v>
+      </c>
+      <c r="H82">
+        <v>387.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>182.667</v>
+      </c>
+      <c r="K82">
+        <v>80</v>
+      </c>
+      <c r="L82">
+        <v>102.667</v>
+      </c>
+      <c r="M82">
+        <v>17.3243196234098</v>
+      </c>
+      <c r="N82">
+        <v>85.34268037659021</v>
+      </c>
+      <c r="O82">
+        <v>16.21510927155213</v>
+      </c>
+      <c r="P82">
+        <v>69.12757110503807</v>
+      </c>
+      <c r="Q82">
+        <v>149.1275711050381</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4630314570351329</v>
+      </c>
+      <c r="T82">
+        <v>5.752432012730171</v>
+      </c>
+      <c r="U82">
+        <v>0.055</v>
+      </c>
+      <c r="V82">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W82">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.92617789510587</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1281136876880721</v>
+      </c>
+      <c r="C83">
+        <v>103.4475376960023</v>
+      </c>
+      <c r="D83">
+        <v>267.3725125815009</v>
+      </c>
+      <c r="E83">
+        <v>312.9904379898214</v>
+      </c>
+      <c r="F83">
+        <v>318.9249748854986</v>
+      </c>
+      <c r="G83">
+        <v>155</v>
+      </c>
+      <c r="H83">
+        <v>387.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>182.667</v>
+      </c>
+      <c r="K83">
+        <v>80</v>
+      </c>
+      <c r="L83">
+        <v>102.667</v>
+      </c>
+      <c r="M83">
+        <v>17.54087361870242</v>
+      </c>
+      <c r="N83">
+        <v>85.12612638129758</v>
+      </c>
+      <c r="O83">
+        <v>16.17396401244654</v>
+      </c>
+      <c r="P83">
+        <v>68.95216236885105</v>
+      </c>
+      <c r="Q83">
+        <v>148.952162368851</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4843588825688008</v>
+      </c>
+      <c r="T83">
+        <v>6.041624535713751</v>
+      </c>
+      <c r="U83">
+        <v>0.055</v>
+      </c>
+      <c r="V83">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W83">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.853015205042834</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1279810839691177</v>
+      </c>
+      <c r="C84">
+        <v>99.90774961090602</v>
+      </c>
+      <c r="D84">
+        <v>267.7700698653614</v>
+      </c>
+      <c r="E84">
+        <v>316.9277833587781</v>
+      </c>
+      <c r="F84">
+        <v>322.8623202544554</v>
+      </c>
+      <c r="G84">
+        <v>155</v>
+      </c>
+      <c r="H84">
+        <v>387.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>182.667</v>
+      </c>
+      <c r="K84">
+        <v>80</v>
+      </c>
+      <c r="L84">
+        <v>102.667</v>
+      </c>
+      <c r="M84">
+        <v>17.75742761399504</v>
+      </c>
+      <c r="N84">
+        <v>84.90957238600495</v>
+      </c>
+      <c r="O84">
+        <v>16.13281875334093</v>
+      </c>
+      <c r="P84">
+        <v>68.77675363266403</v>
+      </c>
+      <c r="Q84">
+        <v>148.776753632664</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.508056022050654</v>
+      </c>
+      <c r="T84">
+        <v>6.362949561251062</v>
+      </c>
+      <c r="U84">
+        <v>0.055</v>
+      </c>
+      <c r="V84">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W84">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.781636970834994</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1278484802501633</v>
+      </c>
+      <c r="C85">
+        <v>96.36914554544001</v>
+      </c>
+      <c r="D85">
+        <v>268.1688111688521</v>
+      </c>
+      <c r="E85">
+        <v>320.8651287277349</v>
+      </c>
+      <c r="F85">
+        <v>326.7996656234121</v>
+      </c>
+      <c r="G85">
+        <v>155</v>
+      </c>
+      <c r="H85">
+        <v>387.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>182.667</v>
+      </c>
+      <c r="K85">
+        <v>80</v>
+      </c>
+      <c r="L85">
+        <v>102.667</v>
+      </c>
+      <c r="M85">
+        <v>17.97398160928767</v>
+      </c>
+      <c r="N85">
+        <v>84.69301839071234</v>
+      </c>
+      <c r="O85">
+        <v>16.09167349423534</v>
+      </c>
+      <c r="P85">
+        <v>68.601344896477</v>
+      </c>
+      <c r="Q85">
+        <v>148.601344896477</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5345410602950784</v>
+      </c>
+      <c r="T85">
+        <v>6.722077530969234</v>
+      </c>
+      <c r="U85">
+        <v>0.055</v>
+      </c>
+      <c r="V85">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W85">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.711978694077947</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1277158765312089</v>
+      </c>
+      <c r="C86">
+        <v>92.83173079692881</v>
+      </c>
+      <c r="D86">
+        <v>268.5687417892977</v>
+      </c>
+      <c r="E86">
+        <v>324.8024740966916</v>
+      </c>
+      <c r="F86">
+        <v>330.7370109923689</v>
+      </c>
+      <c r="G86">
+        <v>155</v>
+      </c>
+      <c r="H86">
+        <v>387.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>182.667</v>
+      </c>
+      <c r="K86">
+        <v>80</v>
+      </c>
+      <c r="L86">
+        <v>102.667</v>
+      </c>
+      <c r="M86">
+        <v>18.19053560458029</v>
+      </c>
+      <c r="N86">
+        <v>84.47646439541971</v>
+      </c>
+      <c r="O86">
+        <v>16.05052823512974</v>
+      </c>
+      <c r="P86">
+        <v>68.42593616028998</v>
+      </c>
+      <c r="Q86">
+        <v>148.42593616029</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5643367283200553</v>
+      </c>
+      <c r="T86">
+        <v>7.126096496902172</v>
+      </c>
+      <c r="U86">
+        <v>0.055</v>
+      </c>
+      <c r="V86">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W86">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.643978947719877</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1275832728122545</v>
+      </c>
+      <c r="C87">
+        <v>89.29551069434376</v>
+      </c>
+      <c r="D87">
+        <v>268.9698670556694</v>
+      </c>
+      <c r="E87">
+        <v>328.7398194656484</v>
+      </c>
+      <c r="F87">
+        <v>334.6743563613256</v>
+      </c>
+      <c r="G87">
+        <v>155</v>
+      </c>
+      <c r="H87">
+        <v>387.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>182.667</v>
+      </c>
+      <c r="K87">
+        <v>80</v>
+      </c>
+      <c r="L87">
+        <v>102.667</v>
+      </c>
+      <c r="M87">
+        <v>18.40708959987291</v>
+      </c>
+      <c r="N87">
+        <v>84.2599104001271</v>
+      </c>
+      <c r="O87">
+        <v>16.00938297602415</v>
+      </c>
+      <c r="P87">
+        <v>68.25052742410296</v>
+      </c>
+      <c r="Q87">
+        <v>148.250527424103</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5981051520816962</v>
+      </c>
+      <c r="T87">
+        <v>7.583984658292841</v>
+      </c>
+      <c r="U87">
+        <v>0.055</v>
+      </c>
+      <c r="V87">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W87">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.577579195393761</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1274506690933</v>
+      </c>
+      <c r="C88">
+        <v>85.76049059854108</v>
+      </c>
+      <c r="D88">
+        <v>269.3721923288235</v>
+      </c>
+      <c r="E88">
+        <v>332.6771648346052</v>
+      </c>
+      <c r="F88">
+        <v>338.6117017302824</v>
+      </c>
+      <c r="G88">
+        <v>155</v>
+      </c>
+      <c r="H88">
+        <v>387.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>182.667</v>
+      </c>
+      <c r="K88">
+        <v>80</v>
+      </c>
+      <c r="L88">
+        <v>102.667</v>
+      </c>
+      <c r="M88">
+        <v>18.62364359516554</v>
+      </c>
+      <c r="N88">
+        <v>84.04335640483447</v>
+      </c>
+      <c r="O88">
+        <v>15.96823771691854</v>
+      </c>
+      <c r="P88">
+        <v>68.07511868791593</v>
+      </c>
+      <c r="Q88">
+        <v>148.0751186879159</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6366976363807144</v>
+      </c>
+      <c r="T88">
+        <v>8.10728541416789</v>
+      </c>
+      <c r="U88">
+        <v>0.055</v>
+      </c>
+      <c r="V88">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W88">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.512723623354297</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1273180653743456</v>
+      </c>
+      <c r="C89">
+        <v>82.22667590250012</v>
+      </c>
+      <c r="D89">
+        <v>269.7757230017393</v>
+      </c>
+      <c r="E89">
+        <v>336.614510203562</v>
+      </c>
+      <c r="F89">
+        <v>342.5490470992392</v>
+      </c>
+      <c r="G89">
+        <v>155</v>
+      </c>
+      <c r="H89">
+        <v>387.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>182.667</v>
+      </c>
+      <c r="K89">
+        <v>80</v>
+      </c>
+      <c r="L89">
+        <v>102.667</v>
+      </c>
+      <c r="M89">
+        <v>18.84019759045816</v>
+      </c>
+      <c r="N89">
+        <v>83.82680240954184</v>
+      </c>
+      <c r="O89">
+        <v>15.92709245781294</v>
+      </c>
+      <c r="P89">
+        <v>67.89970995172889</v>
+      </c>
+      <c r="Q89">
+        <v>147.8997099517289</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6812274259565045</v>
+      </c>
+      <c r="T89">
+        <v>8.7110939786391</v>
+      </c>
+      <c r="U89">
+        <v>0.055</v>
+      </c>
+      <c r="V89">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W89">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.449358984005397</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1271854616553912</v>
+      </c>
+      <c r="C90">
+        <v>78.69407203156396</v>
+      </c>
+      <c r="D90">
+        <v>270.1804644997599</v>
+      </c>
+      <c r="E90">
+        <v>340.5518555725187</v>
+      </c>
+      <c r="F90">
+        <v>346.486392468196</v>
+      </c>
+      <c r="G90">
+        <v>155</v>
+      </c>
+      <c r="H90">
+        <v>387.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>182.667</v>
+      </c>
+      <c r="K90">
+        <v>80</v>
+      </c>
+      <c r="L90">
+        <v>102.667</v>
+      </c>
+      <c r="M90">
+        <v>19.05675158575078</v>
+      </c>
+      <c r="N90">
+        <v>83.61024841424923</v>
+      </c>
+      <c r="O90">
+        <v>15.88594719870735</v>
+      </c>
+      <c r="P90">
+        <v>67.72430121554189</v>
+      </c>
+      <c r="Q90">
+        <v>147.7243012155419</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7331788471282599</v>
+      </c>
+      <c r="T90">
+        <v>9.415537303855515</v>
+      </c>
+      <c r="U90">
+        <v>0.055</v>
+      </c>
+      <c r="V90">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W90">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>5.387434450096246</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1270528579364368</v>
+      </c>
+      <c r="C91">
+        <v>75.16268444368325</v>
+      </c>
+      <c r="D91">
+        <v>270.586422280836</v>
+      </c>
+      <c r="E91">
+        <v>344.4892009414755</v>
+      </c>
+      <c r="F91">
+        <v>350.4237378371528</v>
+      </c>
+      <c r="G91">
+        <v>155</v>
+      </c>
+      <c r="H91">
+        <v>387.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>182.667</v>
+      </c>
+      <c r="K91">
+        <v>80</v>
+      </c>
+      <c r="L91">
+        <v>102.667</v>
+      </c>
+      <c r="M91">
+        <v>19.2733055810434</v>
+      </c>
+      <c r="N91">
+        <v>83.3936944189566</v>
+      </c>
+      <c r="O91">
+        <v>15.84480193960175</v>
+      </c>
+      <c r="P91">
+        <v>67.54889247935485</v>
+      </c>
+      <c r="Q91">
+        <v>147.5488924793548</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7945759812403341</v>
+      </c>
+      <c r="T91">
+        <v>10.24806123365673</v>
+      </c>
+      <c r="U91">
+        <v>0.055</v>
+      </c>
+      <c r="V91">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W91">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>5.32690147874685</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1269202542174823</v>
+      </c>
+      <c r="C92">
+        <v>71.63251862966126</v>
+      </c>
+      <c r="D92">
+        <v>270.9936018357708</v>
+      </c>
+      <c r="E92">
+        <v>348.4265463104323</v>
+      </c>
+      <c r="F92">
+        <v>354.3610832061095</v>
+      </c>
+      <c r="G92">
+        <v>155</v>
+      </c>
+      <c r="H92">
+        <v>387.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>182.667</v>
+      </c>
+      <c r="K92">
+        <v>80</v>
+      </c>
+      <c r="L92">
+        <v>102.667</v>
+      </c>
+      <c r="M92">
+        <v>19.48985957633602</v>
+      </c>
+      <c r="N92">
+        <v>83.17714042366399</v>
+      </c>
+      <c r="O92">
+        <v>15.80365668049615</v>
+      </c>
+      <c r="P92">
+        <v>67.37348374316784</v>
+      </c>
+      <c r="Q92">
+        <v>147.3734837431678</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8682525421748235</v>
+      </c>
+      <c r="T92">
+        <v>11.24708994941819</v>
+      </c>
+      <c r="U92">
+        <v>0.055</v>
+      </c>
+      <c r="V92">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W92">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>5.267713684538552</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1267876504985279</v>
+      </c>
+      <c r="C93">
+        <v>68.10358011340105</v>
+      </c>
+      <c r="D93">
+        <v>271.4020086884674</v>
+      </c>
+      <c r="E93">
+        <v>352.3638916793891</v>
+      </c>
+      <c r="F93">
+        <v>358.2984285750663</v>
+      </c>
+      <c r="G93">
+        <v>155</v>
+      </c>
+      <c r="H93">
+        <v>387.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>182.667</v>
+      </c>
+      <c r="K93">
+        <v>80</v>
+      </c>
+      <c r="L93">
+        <v>102.667</v>
+      </c>
+      <c r="M93">
+        <v>19.70641357162865</v>
+      </c>
+      <c r="N93">
+        <v>82.96058642837136</v>
+      </c>
+      <c r="O93">
+        <v>15.76251142139055</v>
+      </c>
+      <c r="P93">
+        <v>67.1980750069808</v>
+      </c>
+      <c r="Q93">
+        <v>147.1980750069808</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9583016722058659</v>
+      </c>
+      <c r="T93">
+        <v>12.46812504645997</v>
+      </c>
+      <c r="U93">
+        <v>0.055</v>
+      </c>
+      <c r="V93">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W93">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>5.209826720972194</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1266550467795735</v>
+      </c>
+      <c r="C94">
+        <v>64.57587445215603</v>
+      </c>
+      <c r="D94">
+        <v>271.8116483961791</v>
+      </c>
+      <c r="E94">
+        <v>356.3012370483459</v>
+      </c>
+      <c r="F94">
+        <v>362.2357739440231</v>
+      </c>
+      <c r="G94">
+        <v>155</v>
+      </c>
+      <c r="H94">
+        <v>387.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>182.667</v>
+      </c>
+      <c r="K94">
+        <v>80</v>
+      </c>
+      <c r="L94">
+        <v>102.667</v>
+      </c>
+      <c r="M94">
+        <v>19.92296756692127</v>
+      </c>
+      <c r="N94">
+        <v>82.74403243307873</v>
+      </c>
+      <c r="O94">
+        <v>15.72136616228495</v>
+      </c>
+      <c r="P94">
+        <v>67.02266627079378</v>
+      </c>
+      <c r="Q94">
+        <v>147.0226662707938</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.070863084744669</v>
+      </c>
+      <c r="T94">
+        <v>13.9944189177622</v>
+      </c>
+      <c r="U94">
+        <v>0.055</v>
+      </c>
+      <c r="V94">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W94">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>5.153198169657278</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.126522443060619</v>
+      </c>
+      <c r="C95">
+        <v>61.04940723678163</v>
+      </c>
+      <c r="D95">
+        <v>272.2225265497615</v>
+      </c>
+      <c r="E95">
+        <v>360.2385824173026</v>
+      </c>
+      <c r="F95">
+        <v>366.1731193129798</v>
+      </c>
+      <c r="G95">
+        <v>155</v>
+      </c>
+      <c r="H95">
+        <v>387.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>182.667</v>
+      </c>
+      <c r="K95">
+        <v>80</v>
+      </c>
+      <c r="L95">
+        <v>102.667</v>
+      </c>
+      <c r="M95">
+        <v>20.13952156221389</v>
+      </c>
+      <c r="N95">
+        <v>82.5274784377861</v>
+      </c>
+      <c r="O95">
+        <v>15.68022090317936</v>
+      </c>
+      <c r="P95">
+        <v>66.84725753460674</v>
+      </c>
+      <c r="Q95">
+        <v>146.8472575346067</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.215584900865987</v>
+      </c>
+      <c r="T95">
+        <v>15.95679675229364</v>
+      </c>
+      <c r="U95">
+        <v>0.055</v>
+      </c>
+      <c r="V95">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W95">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>5.09778743665021</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1263898393416646</v>
+      </c>
+      <c r="C96">
+        <v>57.52418409198884</v>
+      </c>
+      <c r="D96">
+        <v>272.6346487739255</v>
+      </c>
+      <c r="E96">
+        <v>364.1759277862594</v>
+      </c>
+      <c r="F96">
+        <v>370.1104646819367</v>
+      </c>
+      <c r="G96">
+        <v>155</v>
+      </c>
+      <c r="H96">
+        <v>387.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>182.667</v>
+      </c>
+      <c r="K96">
+        <v>80</v>
+      </c>
+      <c r="L96">
+        <v>102.667</v>
+      </c>
+      <c r="M96">
+        <v>20.35607555750652</v>
+      </c>
+      <c r="N96">
+        <v>82.31092444249349</v>
+      </c>
+      <c r="O96">
+        <v>15.63907564407376</v>
+      </c>
+      <c r="P96">
+        <v>66.67184879841973</v>
+      </c>
+      <c r="Q96">
+        <v>146.6718487984197</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.408547322361079</v>
+      </c>
+      <c r="T96">
+        <v>18.57330053166889</v>
+      </c>
+      <c r="U96">
+        <v>0.055</v>
+      </c>
+      <c r="V96">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W96">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>5.04355565540925</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1262572356227102</v>
+      </c>
+      <c r="C97">
+        <v>54.00021067660288</v>
+      </c>
+      <c r="D97">
+        <v>273.0480207274963</v>
+      </c>
+      <c r="E97">
+        <v>368.1132731552162</v>
+      </c>
+      <c r="F97">
+        <v>374.0478100508934</v>
+      </c>
+      <c r="G97">
+        <v>155</v>
+      </c>
+      <c r="H97">
+        <v>387.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>182.667</v>
+      </c>
+      <c r="K97">
+        <v>80</v>
+      </c>
+      <c r="L97">
+        <v>102.667</v>
+      </c>
+      <c r="M97">
+        <v>20.57262955279914</v>
+      </c>
+      <c r="N97">
+        <v>82.09437044720086</v>
+      </c>
+      <c r="O97">
+        <v>15.59793038496816</v>
+      </c>
+      <c r="P97">
+        <v>66.49644006223269</v>
+      </c>
+      <c r="Q97">
+        <v>146.4964400622327</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.678694712454206</v>
+      </c>
+      <c r="T97">
+        <v>22.23640582279425</v>
+      </c>
+      <c r="U97">
+        <v>0.055</v>
+      </c>
+      <c r="V97">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W97">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.990465595878627</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1261246319037558</v>
+      </c>
+      <c r="C98">
+        <v>50.47749268382006</v>
+      </c>
+      <c r="D98">
+        <v>273.4626481036702</v>
+      </c>
+      <c r="E98">
+        <v>372.0506185241729</v>
+      </c>
+      <c r="F98">
+        <v>377.9851554198502</v>
+      </c>
+      <c r="G98">
+        <v>155</v>
+      </c>
+      <c r="H98">
+        <v>387.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>182.667</v>
+      </c>
+      <c r="K98">
+        <v>80</v>
+      </c>
+      <c r="L98">
+        <v>102.667</v>
+      </c>
+      <c r="M98">
+        <v>20.78918354809176</v>
+      </c>
+      <c r="N98">
+        <v>81.87781645190825</v>
+      </c>
+      <c r="O98">
+        <v>15.55678512586256</v>
+      </c>
+      <c r="P98">
+        <v>66.32103132604568</v>
+      </c>
+      <c r="Q98">
+        <v>146.3210313260457</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.083915797593893</v>
+      </c>
+      <c r="T98">
+        <v>27.73106375948221</v>
+      </c>
+      <c r="U98">
+        <v>0.055</v>
+      </c>
+      <c r="V98">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W98">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.938481579254892</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1259920281848014</v>
+      </c>
+      <c r="C99">
+        <v>46.95603584147057</v>
+      </c>
+      <c r="D99">
+        <v>273.8785366302775</v>
+      </c>
+      <c r="E99">
+        <v>375.9879638931297</v>
+      </c>
+      <c r="F99">
+        <v>381.9225007888069</v>
+      </c>
+      <c r="G99">
+        <v>155</v>
+      </c>
+      <c r="H99">
+        <v>387.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>182.667</v>
+      </c>
+      <c r="K99">
+        <v>80</v>
+      </c>
+      <c r="L99">
+        <v>102.667</v>
+      </c>
+      <c r="M99">
+        <v>21.00573754338438</v>
+      </c>
+      <c r="N99">
+        <v>81.66126245661562</v>
+      </c>
+      <c r="O99">
+        <v>15.51563986675696</v>
+      </c>
+      <c r="P99">
+        <v>66.14562258985865</v>
+      </c>
+      <c r="Q99">
+        <v>146.1456225898586</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.759284272826711</v>
+      </c>
+      <c r="T99">
+        <v>36.88882698729557</v>
+      </c>
+      <c r="U99">
+        <v>0.055</v>
+      </c>
+      <c r="V99">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W99">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.88756939802546</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.125859424465847</v>
+      </c>
+      <c r="C100">
+        <v>43.43584591228137</v>
+      </c>
+      <c r="D100">
+        <v>274.295692070045</v>
+      </c>
+      <c r="E100">
+        <v>379.9253092620864</v>
+      </c>
+      <c r="F100">
+        <v>385.8598461577637</v>
+      </c>
+      <c r="G100">
+        <v>155</v>
+      </c>
+      <c r="H100">
+        <v>387.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>182.667</v>
+      </c>
+      <c r="K100">
+        <v>80</v>
+      </c>
+      <c r="L100">
+        <v>102.667</v>
+      </c>
+      <c r="M100">
+        <v>21.222291538677</v>
+      </c>
+      <c r="N100">
+        <v>81.444708461323</v>
+      </c>
+      <c r="O100">
+        <v>15.47449460765137</v>
+      </c>
+      <c r="P100">
+        <v>65.97021385367164</v>
+      </c>
+      <c r="Q100">
+        <v>145.9702138536716</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.110021223292344</v>
+      </c>
+      <c r="T100">
+        <v>55.20435344292227</v>
+      </c>
+      <c r="U100">
+        <v>0.055</v>
+      </c>
+      <c r="V100">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W100">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.837696240902751</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1257268207468925</v>
+      </c>
+      <c r="C101">
+        <v>39.91692869414322</v>
+      </c>
+      <c r="D101">
+        <v>274.7141202208637</v>
+      </c>
+      <c r="E101">
+        <v>383.8626546310433</v>
+      </c>
+      <c r="F101">
+        <v>389.7971915267205</v>
+      </c>
+      <c r="G101">
+        <v>155</v>
+      </c>
+      <c r="H101">
+        <v>387.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>182.667</v>
+      </c>
+      <c r="K101">
+        <v>80</v>
+      </c>
+      <c r="L101">
+        <v>102.667</v>
+      </c>
+      <c r="M101">
+        <v>21.43884553396963</v>
+      </c>
+      <c r="N101">
+        <v>81.22815446603038</v>
+      </c>
+      <c r="O101">
+        <v>15.43334934854577</v>
+      </c>
+      <c r="P101">
+        <v>65.79480511748461</v>
+      </c>
+      <c r="Q101">
+        <v>145.7948051174846</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.162232074689246</v>
+      </c>
+      <c r="T101">
+        <v>110.1509328098024</v>
+      </c>
+      <c r="U101">
+        <v>0.055</v>
+      </c>
+      <c r="V101">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W101">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.788830622307774</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_coal_related_energy.xlsx
@@ -1127,43 +1127,43 @@
         <v>466.908212560387</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>2076.25606241529</v>
       </c>
       <c r="G2">
         <v>0.0251143043762247</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.00604474199869366</v>
       </c>
       <c r="I2">
         <v>0.0415473553406451</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>177.4</v>
       </c>
       <c r="L2">
-        <v>185.179015288453</v>
+        <v>183.264253619592</v>
       </c>
       <c r="M2">
         <v>-23.21</v>
       </c>
       <c r="N2">
-        <v>-23.1209847115467</v>
+        <v>-23.1848463804082</v>
       </c>
       <c r="O2">
         <v>7.69</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.8509</v>
       </c>
       <c r="Q2">
         <v>0.104756784104609</v>
       </c>
       <c r="R2">
-        <v>0.1049837664416</v>
+        <v>0.104820747285361</v>
       </c>
       <c r="S2">
         <v>0.0515816957599802</v>
@@ -1185,13 +1185,13 @@
         <v>0.107061837257767</v>
       </c>
       <c r="X2">
-        <v>0.1049837664416</v>
+        <v>0.10546799725794</v>
       </c>
       <c r="Y2">
         <v>1.1220320636446</v>
       </c>
       <c r="Z2">
-        <v>1.08397146685817</v>
+        <v>1.09284032431428</v>
       </c>
       <c r="AA2">
         <v>7.69</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1049837664415997</v>
+        <v>0.1048207472853607</v>
       </c>
       <c r="C2">
-        <v>185.1790152884533</v>
+        <v>183.2642536195918</v>
       </c>
       <c r="D2">
-        <v>-23.12098471154674</v>
+        <v>-23.18484638040817</v>
       </c>
       <c r="E2">
-        <v>-7.69</v>
+        <v>-5.839099999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.8509</v>
       </c>
       <c r="G2">
         <v>208.3</v>
@@ -1445,28 +1445,28 @@
         <v>193.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09310027</v>
       </c>
       <c r="N2">
-        <v>193.3</v>
+        <v>193.20689973</v>
       </c>
       <c r="O2">
-        <v>36.727</v>
+        <v>36.7093109487</v>
       </c>
       <c r="P2">
-        <v>156.573</v>
+        <v>156.4975887813</v>
       </c>
       <c r="Q2">
-        <v>269.473</v>
+        <v>269.3975887813</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1049837664415997</v>
+        <v>0.1054679972579401</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.092840324314281</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>2076.256062415286</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1048207472853607</v>
+        <v>0.1046577281291216</v>
       </c>
       <c r="C3">
-        <v>183.2642536195918</v>
+        <v>181.3491381934345</v>
       </c>
       <c r="D3">
-        <v>-23.18484638040817</v>
+        <v>-23.24906180656554</v>
       </c>
       <c r="E3">
-        <v>-5.839099999999999</v>
+        <v>-3.9882</v>
       </c>
       <c r="F3">
-        <v>1.8509</v>
+        <v>3.7018</v>
       </c>
       <c r="G3">
         <v>208.3</v>
@@ -1527,28 +1527,28 @@
         <v>193.3</v>
       </c>
       <c r="M3">
-        <v>0.09310027</v>
+        <v>0.18620054</v>
       </c>
       <c r="N3">
-        <v>193.20689973</v>
+        <v>193.11379946</v>
       </c>
       <c r="O3">
-        <v>36.7093109487</v>
+        <v>36.6916218974</v>
       </c>
       <c r="P3">
-        <v>156.4975887813</v>
+        <v>156.4221775626</v>
       </c>
       <c r="Q3">
-        <v>269.3975887813</v>
+        <v>269.3221775626</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1054679972579401</v>
+        <v>0.1059621103358384</v>
       </c>
       <c r="T3">
-        <v>1.092840324314281</v>
+        <v>1.101890178861334</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>2076.256062415286</v>
+        <v>1038.128031207643</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1046577281291216</v>
+        <v>0.1044947089728826</v>
       </c>
       <c r="C4">
-        <v>181.3491381934345</v>
+        <v>179.4336660623961</v>
       </c>
       <c r="D4">
-        <v>-23.24906180656554</v>
+        <v>-23.3136339376039</v>
       </c>
       <c r="E4">
-        <v>-3.9882</v>
+        <v>-2.1373</v>
       </c>
       <c r="F4">
-        <v>3.7018</v>
+        <v>5.5527</v>
       </c>
       <c r="G4">
         <v>208.3</v>
@@ -1609,28 +1609,28 @@
         <v>193.3</v>
       </c>
       <c r="M4">
-        <v>0.18620054</v>
+        <v>0.27930081</v>
       </c>
       <c r="N4">
-        <v>193.11379946</v>
+        <v>193.02069919</v>
       </c>
       <c r="O4">
-        <v>36.6916218974</v>
+        <v>36.6739328461</v>
       </c>
       <c r="P4">
-        <v>156.4221775626</v>
+        <v>156.3467663439</v>
       </c>
       <c r="Q4">
-        <v>269.3221775626</v>
+        <v>269.2467663439</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1059621103358384</v>
+        <v>0.1064664113122501</v>
       </c>
       <c r="T4">
-        <v>1.101890178861334</v>
+        <v>1.111126628347502</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>1038.128031207643</v>
+        <v>692.0853541384289</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1044947089728826</v>
+        <v>0.1043316898166435</v>
       </c>
       <c r="C5">
-        <v>179.4336660623961</v>
+        <v>177.5178342460539</v>
       </c>
       <c r="D5">
-        <v>-23.3136339376039</v>
+        <v>-23.37856575394613</v>
       </c>
       <c r="E5">
-        <v>-2.1373</v>
+        <v>-0.2863999999999995</v>
       </c>
       <c r="F5">
-        <v>5.5527</v>
+        <v>7.4036</v>
       </c>
       <c r="G5">
         <v>208.3</v>
@@ -1691,28 +1691,28 @@
         <v>193.3</v>
       </c>
       <c r="M5">
-        <v>0.27930081</v>
+        <v>0.37240108</v>
       </c>
       <c r="N5">
-        <v>193.02069919</v>
+        <v>192.92759892</v>
       </c>
       <c r="O5">
-        <v>36.6739328461</v>
+        <v>36.65624379480001</v>
       </c>
       <c r="P5">
-        <v>156.3467663439</v>
+        <v>156.2713551252</v>
       </c>
       <c r="Q5">
-        <v>269.2467663439</v>
+        <v>269.1713551252</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1064664113122501</v>
+        <v>0.1069812185590037</v>
       </c>
       <c r="T5">
-        <v>1.111126628347502</v>
+        <v>1.120555503864631</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>692.0853541384289</v>
+        <v>519.0640156038215</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1043316898166435</v>
+        <v>0.1041686706604045</v>
       </c>
       <c r="C6">
-        <v>177.5178342460539</v>
+        <v>175.6016397306886</v>
       </c>
       <c r="D6">
-        <v>-23.37856575394613</v>
+        <v>-23.44386026931141</v>
       </c>
       <c r="E6">
-        <v>-0.2863999999999995</v>
+        <v>1.564500000000001</v>
       </c>
       <c r="F6">
-        <v>7.4036</v>
+        <v>9.2545</v>
       </c>
       <c r="G6">
         <v>208.3</v>
@@ -1773,28 +1773,28 @@
         <v>193.3</v>
       </c>
       <c r="M6">
-        <v>0.37240108</v>
+        <v>0.46550135</v>
       </c>
       <c r="N6">
-        <v>192.92759892</v>
+        <v>192.83449865</v>
       </c>
       <c r="O6">
-        <v>36.65624379480001</v>
+        <v>36.6385547435</v>
       </c>
       <c r="P6">
-        <v>156.2713551252</v>
+        <v>156.1959439065</v>
       </c>
       <c r="Q6">
-        <v>269.1713551252</v>
+        <v>269.0959439065</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1069812185590037</v>
+        <v>0.1075068638530574</v>
       </c>
       <c r="T6">
-        <v>1.120555503864631</v>
+        <v>1.130182882024227</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>519.0640156038215</v>
+        <v>415.2512124830573</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1041686706604045</v>
+        <v>0.1040056515041654</v>
       </c>
       <c r="C7">
-        <v>175.6016397306886</v>
+        <v>173.6850794688184</v>
       </c>
       <c r="D7">
-        <v>-23.44386026931141</v>
+        <v>-23.50952053118161</v>
       </c>
       <c r="E7">
-        <v>1.564500000000001</v>
+        <v>3.415400000000002</v>
       </c>
       <c r="F7">
-        <v>9.2545</v>
+        <v>11.1054</v>
       </c>
       <c r="G7">
         <v>208.3</v>
@@ -1855,28 +1855,28 @@
         <v>193.3</v>
       </c>
       <c r="M7">
-        <v>0.46550135</v>
+        <v>0.55860162</v>
       </c>
       <c r="N7">
-        <v>192.83449865</v>
+        <v>192.74139838</v>
       </c>
       <c r="O7">
-        <v>36.6385547435</v>
+        <v>36.62086569220001</v>
       </c>
       <c r="P7">
-        <v>156.1959439065</v>
+        <v>156.1205326878</v>
       </c>
       <c r="Q7">
-        <v>269.0959439065</v>
+        <v>269.0205326878</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1075068638530574</v>
+        <v>0.1080436930895377</v>
       </c>
       <c r="T7">
-        <v>1.130182882024227</v>
+        <v>1.140015098017005</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>415.2512124830573</v>
+        <v>346.0426770692144</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1040056515041654</v>
+        <v>0.1038426323479264</v>
       </c>
       <c r="C8">
-        <v>173.6850794688184</v>
+        <v>171.7681503787247</v>
       </c>
       <c r="D8">
-        <v>-23.50952053118161</v>
+        <v>-23.57554962127533</v>
       </c>
       <c r="E8">
-        <v>3.4154</v>
+        <v>5.266299999999999</v>
       </c>
       <c r="F8">
-        <v>11.1054</v>
+        <v>12.9563</v>
       </c>
       <c r="G8">
         <v>208.3</v>
@@ -1937,28 +1937,28 @@
         <v>193.3</v>
       </c>
       <c r="M8">
-        <v>0.5586016199999999</v>
+        <v>0.6517018899999999</v>
       </c>
       <c r="N8">
-        <v>192.74139838</v>
+        <v>192.64829811</v>
       </c>
       <c r="O8">
-        <v>36.62086569220001</v>
+        <v>36.6031766409</v>
       </c>
       <c r="P8">
-        <v>156.1205326878</v>
+        <v>156.0451214691</v>
       </c>
       <c r="Q8">
-        <v>269.0205326878</v>
+        <v>268.9451214691</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1080436930895377</v>
+        <v>0.1085920670407811</v>
       </c>
       <c r="T8">
-        <v>1.140015098017005</v>
+        <v>1.150058759515005</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>346.0426770692144</v>
+        <v>296.6080089164695</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1038426323479264</v>
+        <v>0.1036796131916874</v>
       </c>
       <c r="C9">
-        <v>171.7681503787247</v>
+        <v>169.85084934397</v>
       </c>
       <c r="D9">
-        <v>-23.57554962127533</v>
+        <v>-23.64195065603005</v>
       </c>
       <c r="E9">
-        <v>5.266300000000001</v>
+        <v>7.1172</v>
       </c>
       <c r="F9">
-        <v>12.9563</v>
+        <v>14.8072</v>
       </c>
       <c r="G9">
         <v>208.3</v>
@@ -2019,28 +2019,28 @@
         <v>193.3</v>
       </c>
       <c r="M9">
-        <v>0.65170189</v>
+        <v>0.74480216</v>
       </c>
       <c r="N9">
-        <v>192.64829811</v>
+        <v>192.55519784</v>
       </c>
       <c r="O9">
-        <v>36.6031766409</v>
+        <v>36.5854875896</v>
       </c>
       <c r="P9">
-        <v>156.0451214691</v>
+        <v>155.9697102504</v>
       </c>
       <c r="Q9">
-        <v>268.9451214691</v>
+        <v>268.8697102504</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1085920670407811</v>
+        <v>0.1091523621648776</v>
       </c>
       <c r="T9">
-        <v>1.150058759515005</v>
+        <v>1.160320761480352</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>296.6080089164695</v>
+        <v>259.5320078019108</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1036796131916874</v>
+        <v>0.1035165940354483</v>
       </c>
       <c r="C10">
-        <v>169.85084934397</v>
+        <v>167.9331732129075</v>
       </c>
       <c r="D10">
-        <v>-23.64195065603005</v>
+        <v>-23.70872678709254</v>
       </c>
       <c r="E10">
-        <v>7.1172</v>
+        <v>8.968100000000002</v>
       </c>
       <c r="F10">
-        <v>14.8072</v>
+        <v>16.6581</v>
       </c>
       <c r="G10">
         <v>208.3</v>
@@ -2101,28 +2101,28 @@
         <v>193.3</v>
       </c>
       <c r="M10">
-        <v>0.74480216</v>
+        <v>0.83790243</v>
       </c>
       <c r="N10">
-        <v>192.55519784</v>
+        <v>192.46209757</v>
       </c>
       <c r="O10">
-        <v>36.5854875896</v>
+        <v>36.5677985383</v>
       </c>
       <c r="P10">
-        <v>155.9697102504</v>
+        <v>155.8942990317</v>
       </c>
       <c r="Q10">
-        <v>268.8697102504</v>
+        <v>268.7942990317</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1091523621648776</v>
+        <v>0.1097249714675256</v>
       </c>
       <c r="T10">
-        <v>1.160320761480352</v>
+        <v>1.170808301950432</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>259.5320078019108</v>
+        <v>230.6951180461429</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1035165940354483</v>
+        <v>0.1033535748792093</v>
       </c>
       <c r="C11">
-        <v>167.9331732129075</v>
+        <v>166.0151187981826</v>
       </c>
       <c r="D11">
-        <v>-23.70872678709254</v>
+        <v>-23.77588120181735</v>
       </c>
       <c r="E11">
-        <v>8.968100000000002</v>
+        <v>10.819</v>
       </c>
       <c r="F11">
-        <v>16.6581</v>
+        <v>18.509</v>
       </c>
       <c r="G11">
         <v>208.3</v>
@@ -2183,28 +2183,28 @@
         <v>193.3</v>
       </c>
       <c r="M11">
-        <v>0.83790243</v>
+        <v>0.9310027</v>
       </c>
       <c r="N11">
-        <v>192.46209757</v>
+        <v>192.3689973</v>
       </c>
       <c r="O11">
-        <v>36.5677985383</v>
+        <v>36.55010948700001</v>
       </c>
       <c r="P11">
-        <v>155.8942990317</v>
+        <v>155.818887813</v>
       </c>
       <c r="Q11">
-        <v>268.7942990317</v>
+        <v>268.718887813</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1097249714675256</v>
+        <v>0.1103103054213437</v>
       </c>
       <c r="T11">
-        <v>1.170808301950432</v>
+        <v>1.181528898875403</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>230.6951180461429</v>
+        <v>207.6256062415287</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1033535748792093</v>
+        <v>0.1031905557229703</v>
       </c>
       <c r="C12">
-        <v>166.0151187981826</v>
+        <v>164.0966828762259</v>
       </c>
       <c r="D12">
-        <v>-23.77588120181735</v>
+        <v>-23.84341712377408</v>
       </c>
       <c r="E12">
-        <v>10.819</v>
+        <v>12.6699</v>
       </c>
       <c r="F12">
-        <v>18.509</v>
+        <v>20.3599</v>
       </c>
       <c r="G12">
         <v>208.3</v>
@@ -2265,28 +2265,28 @@
         <v>193.3</v>
       </c>
       <c r="M12">
-        <v>0.9310027</v>
+        <v>1.02410297</v>
       </c>
       <c r="N12">
-        <v>192.3689973</v>
+        <v>192.27589703</v>
       </c>
       <c r="O12">
-        <v>36.55010948700001</v>
+        <v>36.5324204357</v>
       </c>
       <c r="P12">
-        <v>155.818887813</v>
+        <v>155.7434765943</v>
       </c>
       <c r="Q12">
-        <v>268.718887813</v>
+        <v>268.6434765943</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1103103054213437</v>
+        <v>0.1109087929471576</v>
       </c>
       <c r="T12">
-        <v>1.181528898875403</v>
+        <v>1.192490408090823</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>207.6256062415287</v>
+        <v>188.7505511286624</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1031905557229703</v>
+        <v>0.1030275365667312</v>
       </c>
       <c r="C13">
-        <v>164.0966828762259</v>
+        <v>162.1778621867369</v>
       </c>
       <c r="D13">
-        <v>-23.84341712377408</v>
+        <v>-23.91133781326315</v>
       </c>
       <c r="E13">
-        <v>12.6699</v>
+        <v>14.5208</v>
       </c>
       <c r="F13">
-        <v>20.3599</v>
+        <v>22.2108</v>
       </c>
       <c r="G13">
         <v>208.3</v>
@@ -2347,28 +2347,28 @@
         <v>193.3</v>
       </c>
       <c r="M13">
-        <v>1.02410297</v>
+        <v>1.11720324</v>
       </c>
       <c r="N13">
-        <v>192.27589703</v>
+        <v>192.18279676</v>
       </c>
       <c r="O13">
-        <v>36.5324204357</v>
+        <v>36.5147313844</v>
       </c>
       <c r="P13">
-        <v>155.7434765943</v>
+        <v>155.6680653756</v>
       </c>
       <c r="Q13">
-        <v>268.6434765943</v>
+        <v>268.5680653756</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1109087929471576</v>
+        <v>0.1115208824621945</v>
       </c>
       <c r="T13">
-        <v>1.192490408090823</v>
+        <v>1.203701042515684</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>188.7505511286624</v>
+        <v>173.0213385346072</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1030275365667312</v>
+        <v>0.1028645174104922</v>
       </c>
       <c r="C14">
-        <v>162.1778621867369</v>
+        <v>160.2586534321596</v>
       </c>
       <c r="D14">
-        <v>-23.91133781326315</v>
+        <v>-23.97964656784043</v>
       </c>
       <c r="E14">
-        <v>14.5208</v>
+        <v>16.3717</v>
       </c>
       <c r="F14">
-        <v>22.2108</v>
+        <v>24.0617</v>
       </c>
       <c r="G14">
         <v>208.3</v>
@@ -2429,28 +2429,28 @@
         <v>193.3</v>
       </c>
       <c r="M14">
-        <v>1.11720324</v>
+        <v>1.21030351</v>
       </c>
       <c r="N14">
-        <v>192.18279676</v>
+        <v>192.08969649</v>
       </c>
       <c r="O14">
-        <v>36.5147313844</v>
+        <v>36.4970423331</v>
       </c>
       <c r="P14">
-        <v>155.6680653756</v>
+        <v>155.5926541569</v>
       </c>
       <c r="Q14">
-        <v>268.5680653756</v>
+        <v>268.4926541569</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1115208824621945</v>
+        <v>0.1121470430005657</v>
       </c>
       <c r="T14">
-        <v>1.203701042515684</v>
+        <v>1.21516939267445</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>173.0213385346072</v>
+        <v>159.7120048011759</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1028645174104922</v>
+        <v>0.1027014982542531</v>
       </c>
       <c r="C15">
-        <v>160.2586534321596</v>
+        <v>158.339053277149</v>
       </c>
       <c r="D15">
-        <v>-23.97964656784043</v>
+        <v>-24.04834672285098</v>
       </c>
       <c r="E15">
-        <v>16.3717</v>
+        <v>18.2226</v>
       </c>
       <c r="F15">
-        <v>24.0617</v>
+        <v>25.9126</v>
       </c>
       <c r="G15">
         <v>208.3</v>
@@ -2511,28 +2511,28 @@
         <v>193.3</v>
       </c>
       <c r="M15">
-        <v>1.21030351</v>
+        <v>1.30340378</v>
       </c>
       <c r="N15">
-        <v>192.08969649</v>
+        <v>191.99659622</v>
       </c>
       <c r="O15">
-        <v>36.4970423331</v>
+        <v>36.4793532818</v>
       </c>
       <c r="P15">
-        <v>155.5926541569</v>
+        <v>155.5172429382</v>
       </c>
       <c r="Q15">
-        <v>268.4926541569</v>
+        <v>268.4172429382</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1121470430005657</v>
+        <v>0.1127877654119223</v>
       </c>
       <c r="T15">
-        <v>1.21516939267445</v>
+        <v>1.226904448650862</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>159.7120048011759</v>
+        <v>148.3040044582347</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1027014982542531</v>
+        <v>0.1025384790980141</v>
       </c>
       <c r="C16">
-        <v>158.339053277149</v>
+        <v>156.4190583480282</v>
       </c>
       <c r="D16">
-        <v>-24.04834672285098</v>
+        <v>-24.11744165197185</v>
       </c>
       <c r="E16">
-        <v>18.2226</v>
+        <v>20.0735</v>
       </c>
       <c r="F16">
-        <v>25.9126</v>
+        <v>27.7635</v>
       </c>
       <c r="G16">
         <v>208.3</v>
@@ -2593,28 +2593,28 @@
         <v>193.3</v>
       </c>
       <c r="M16">
-        <v>1.30340378</v>
+        <v>1.39650405</v>
       </c>
       <c r="N16">
-        <v>191.99659622</v>
+        <v>191.90349595</v>
       </c>
       <c r="O16">
-        <v>36.4793532818</v>
+        <v>36.4616642305</v>
       </c>
       <c r="P16">
-        <v>155.5172429382</v>
+        <v>155.4418317195</v>
       </c>
       <c r="Q16">
-        <v>268.4172429382</v>
+        <v>268.3418317195</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1127877654119223</v>
+        <v>0.1134435636447225</v>
       </c>
       <c r="T16">
-        <v>1.226904448650862</v>
+        <v>1.238915623591424</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>148.3040044582347</v>
+        <v>138.4170708276857</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1025384790980141</v>
+        <v>0.1023754599417751</v>
       </c>
       <c r="C17">
-        <v>156.4190583480282</v>
+        <v>154.4986652322357</v>
       </c>
       <c r="D17">
-        <v>-24.11744165197185</v>
+        <v>-24.18693476776436</v>
       </c>
       <c r="E17">
-        <v>20.0735</v>
+        <v>21.9244</v>
       </c>
       <c r="F17">
-        <v>27.7635</v>
+        <v>29.6144</v>
       </c>
       <c r="G17">
         <v>208.3</v>
@@ -2675,28 +2675,28 @@
         <v>193.3</v>
       </c>
       <c r="M17">
-        <v>1.39650405</v>
+        <v>1.48960432</v>
       </c>
       <c r="N17">
-        <v>191.90349595</v>
+        <v>191.81039568</v>
       </c>
       <c r="O17">
-        <v>36.4616642305</v>
+        <v>36.4439751792</v>
       </c>
       <c r="P17">
-        <v>155.4418317195</v>
+        <v>155.3664205008</v>
       </c>
       <c r="Q17">
-        <v>268.3418317195</v>
+        <v>268.2664205008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1134435636447225</v>
+        <v>0.1141149761211608</v>
       </c>
       <c r="T17">
-        <v>1.238915623591424</v>
+        <v>1.251212778887714</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>138.4170708276858</v>
+        <v>129.7660039009554</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1023754599417751</v>
+        <v>0.102212440785536</v>
       </c>
       <c r="C18">
-        <v>154.4986652322357</v>
+        <v>152.577870477764</v>
       </c>
       <c r="D18">
-        <v>-24.18693476776436</v>
+        <v>-24.25682952223598</v>
       </c>
       <c r="E18">
-        <v>21.9244</v>
+        <v>23.7753</v>
       </c>
       <c r="F18">
-        <v>29.6144</v>
+        <v>31.4653</v>
       </c>
       <c r="G18">
         <v>208.3</v>
@@ -2757,28 +2757,28 @@
         <v>193.3</v>
       </c>
       <c r="M18">
-        <v>1.48960432</v>
+        <v>1.58270459</v>
       </c>
       <c r="N18">
-        <v>191.81039568</v>
+        <v>191.71729541</v>
       </c>
       <c r="O18">
-        <v>36.4439751792</v>
+        <v>36.42628612790001</v>
       </c>
       <c r="P18">
-        <v>155.3664205008</v>
+        <v>155.2910092821</v>
       </c>
       <c r="Q18">
-        <v>268.2664205008</v>
+        <v>268.1910092821</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1141149761211608</v>
+        <v>0.1148025672114892</v>
       </c>
       <c r="T18">
-        <v>1.251212778887714</v>
+        <v>1.263806251179096</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>129.7660039009554</v>
+        <v>122.1327095538404</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.102212440785536</v>
+        <v>0.102049421629297</v>
       </c>
       <c r="C19">
-        <v>152.577870477764</v>
+        <v>150.6566705925881</v>
       </c>
       <c r="D19">
-        <v>-24.25682952223598</v>
+        <v>-24.32712940741186</v>
       </c>
       <c r="E19">
-        <v>23.7753</v>
+        <v>25.6262</v>
       </c>
       <c r="F19">
-        <v>31.4653</v>
+        <v>33.3162</v>
       </c>
       <c r="G19">
         <v>208.3</v>
@@ -2839,28 +2839,28 @@
         <v>193.3</v>
       </c>
       <c r="M19">
-        <v>1.58270459</v>
+        <v>1.67580486</v>
       </c>
       <c r="N19">
-        <v>191.71729541</v>
+        <v>191.62419514</v>
       </c>
       <c r="O19">
-        <v>36.42628612790001</v>
+        <v>36.4085970766</v>
       </c>
       <c r="P19">
-        <v>155.2910092821</v>
+        <v>155.2155980634</v>
       </c>
       <c r="Q19">
-        <v>268.1910092821</v>
+        <v>268.1155980634</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1148025672114892</v>
+        <v>0.1155069288162158</v>
       </c>
       <c r="T19">
-        <v>1.263806251179096</v>
+        <v>1.276706881331242</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>122.1327095538404</v>
+        <v>115.3475590230715</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.102049421629297</v>
+        <v>0.101886402473058</v>
       </c>
       <c r="C20">
-        <v>150.6566705925881</v>
+        <v>148.7350620440835</v>
       </c>
       <c r="D20">
-        <v>-24.32712940741186</v>
+        <v>-24.39783795591645</v>
       </c>
       <c r="E20">
-        <v>25.6262</v>
+        <v>27.4771</v>
       </c>
       <c r="F20">
-        <v>33.3162</v>
+        <v>35.1671</v>
       </c>
       <c r="G20">
         <v>208.3</v>
@@ -2921,28 +2921,28 @@
         <v>193.3</v>
       </c>
       <c r="M20">
-        <v>1.67580486</v>
+        <v>1.76890513</v>
       </c>
       <c r="N20">
-        <v>191.62419514</v>
+        <v>191.53109487</v>
       </c>
       <c r="O20">
-        <v>36.4085970766</v>
+        <v>36.3909080253</v>
       </c>
       <c r="P20">
-        <v>155.2155980634</v>
+        <v>155.1401868447</v>
       </c>
       <c r="Q20">
-        <v>268.1155980634</v>
+        <v>268.0401868447</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1155069288162158</v>
+        <v>0.1162286820655036</v>
       </c>
       <c r="T20">
-        <v>1.276706881331242</v>
+        <v>1.28992604556122</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>115.3475590230715</v>
+        <v>109.2766348639624</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.101886402473058</v>
+        <v>0.1017233833168189</v>
       </c>
       <c r="C21">
-        <v>148.7350620440835</v>
+        <v>146.8130412584348</v>
       </c>
       <c r="D21">
-        <v>-24.39783795591645</v>
+        <v>-24.46895874156523</v>
       </c>
       <c r="E21">
-        <v>27.4771</v>
+        <v>29.328</v>
       </c>
       <c r="F21">
-        <v>35.1671</v>
+        <v>37.018</v>
       </c>
       <c r="G21">
         <v>208.3</v>
@@ -3003,28 +3003,28 @@
         <v>193.3</v>
       </c>
       <c r="M21">
-        <v>1.76890513</v>
+        <v>1.8620054</v>
       </c>
       <c r="N21">
-        <v>191.53109487</v>
+        <v>191.4379946</v>
       </c>
       <c r="O21">
-        <v>36.3909080253</v>
+        <v>36.373218974</v>
       </c>
       <c r="P21">
-        <v>155.1401868447</v>
+        <v>155.064775626</v>
       </c>
       <c r="Q21">
-        <v>268.0401868447</v>
+        <v>267.964775626</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1162286820655036</v>
+        <v>0.1169684791460236</v>
       </c>
       <c r="T21">
-        <v>1.28992604556122</v>
+        <v>1.303475688896947</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>109.2766348639624</v>
+        <v>103.8128031207643</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1017233833168189</v>
+        <v>0.1015603641605799</v>
       </c>
       <c r="C22">
-        <v>146.8130412584348</v>
+        <v>144.8906046200332</v>
       </c>
       <c r="D22">
-        <v>-24.46895874156523</v>
+        <v>-24.54049537996686</v>
       </c>
       <c r="E22">
-        <v>29.328</v>
+        <v>31.17890000000001</v>
       </c>
       <c r="F22">
-        <v>37.018</v>
+        <v>38.8689</v>
       </c>
       <c r="G22">
         <v>208.3</v>
@@ -3085,28 +3085,28 @@
         <v>193.3</v>
       </c>
       <c r="M22">
-        <v>1.8620054</v>
+        <v>1.95510567</v>
       </c>
       <c r="N22">
-        <v>191.4379946</v>
+        <v>191.34489433</v>
       </c>
       <c r="O22">
-        <v>36.373218974</v>
+        <v>36.3555299227</v>
       </c>
       <c r="P22">
-        <v>155.064775626</v>
+        <v>154.9893644073</v>
       </c>
       <c r="Q22">
-        <v>267.964775626</v>
+        <v>267.8893644073</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1169684791460236</v>
+        <v>0.1177270052665568</v>
       </c>
       <c r="T22">
-        <v>1.303475688896947</v>
+        <v>1.317368361177883</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>103.8128031207643</v>
+        <v>98.86933630548982</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1015603641605798</v>
+        <v>0.1013973450043408</v>
       </c>
       <c r="C23">
-        <v>144.8906046200331</v>
+        <v>142.9677484708642</v>
       </c>
       <c r="D23">
-        <v>-24.54049537996686</v>
+        <v>-24.61245152913581</v>
       </c>
       <c r="E23">
-        <v>31.1789</v>
+        <v>33.0298</v>
       </c>
       <c r="F23">
-        <v>38.8689</v>
+        <v>40.7198</v>
       </c>
       <c r="G23">
         <v>208.3</v>
@@ -3167,28 +3167,28 @@
         <v>193.3</v>
       </c>
       <c r="M23">
-        <v>1.95510567</v>
+        <v>2.04820594</v>
       </c>
       <c r="N23">
-        <v>191.34489433</v>
+        <v>191.25179406</v>
       </c>
       <c r="O23">
-        <v>36.3555299227</v>
+        <v>36.3378408714</v>
       </c>
       <c r="P23">
-        <v>154.9893644073</v>
+        <v>154.9139531886</v>
       </c>
       <c r="Q23">
-        <v>267.8893644073</v>
+        <v>267.8139531886</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1177270052665568</v>
+        <v>0.1185049807747959</v>
       </c>
       <c r="T23">
-        <v>1.317368361177883</v>
+        <v>1.331617255824996</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>98.86933630548984</v>
+        <v>94.3752755643312</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1013973450043408</v>
+        <v>0.1012343258481018</v>
       </c>
       <c r="C24">
-        <v>142.9677484708642</v>
+        <v>141.044469109884</v>
       </c>
       <c r="D24">
-        <v>-24.61245152913581</v>
+        <v>-24.684830890116</v>
       </c>
       <c r="E24">
-        <v>33.0298</v>
+        <v>34.8807</v>
       </c>
       <c r="F24">
-        <v>40.7198</v>
+        <v>42.5707</v>
       </c>
       <c r="G24">
         <v>208.3</v>
@@ -3249,28 +3249,28 @@
         <v>193.3</v>
       </c>
       <c r="M24">
-        <v>2.04820594</v>
+        <v>2.14130621</v>
       </c>
       <c r="N24">
-        <v>191.25179406</v>
+        <v>191.15869379</v>
       </c>
       <c r="O24">
-        <v>36.3378408714</v>
+        <v>36.3201518201</v>
       </c>
       <c r="P24">
-        <v>154.9139531886</v>
+        <v>154.8385419699</v>
       </c>
       <c r="Q24">
-        <v>267.8139531886</v>
+        <v>267.7385419699</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1185049807747959</v>
+        <v>0.1193031634390932</v>
       </c>
       <c r="T24">
-        <v>1.331617255824996</v>
+        <v>1.346236251631774</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>94.3752755643312</v>
+        <v>90.27200271370809</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1012343258481018</v>
+        <v>0.1010713066918627</v>
       </c>
       <c r="C25">
-        <v>141.044469109884</v>
+        <v>139.1207627923847</v>
       </c>
       <c r="D25">
-        <v>-24.684830890116</v>
+        <v>-24.75763720761533</v>
       </c>
       <c r="E25">
-        <v>34.8807</v>
+        <v>36.73160000000001</v>
       </c>
       <c r="F25">
-        <v>42.5707</v>
+        <v>44.42160000000001</v>
       </c>
       <c r="G25">
         <v>208.3</v>
@@ -3331,28 +3331,28 @@
         <v>193.3</v>
       </c>
       <c r="M25">
-        <v>2.14130621</v>
+        <v>2.23440648</v>
       </c>
       <c r="N25">
-        <v>191.15869379</v>
+        <v>191.06559352</v>
       </c>
       <c r="O25">
-        <v>36.3201518201</v>
+        <v>36.30246276880001</v>
       </c>
       <c r="P25">
-        <v>154.8385419699</v>
+        <v>154.7631307512</v>
       </c>
       <c r="Q25">
-        <v>267.7385419699</v>
+        <v>267.6631307512</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1193031634390932</v>
+        <v>0.1201223509103457</v>
       </c>
       <c r="T25">
-        <v>1.346236251631774</v>
+        <v>1.361239957854521</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>90.27200271370809</v>
+        <v>86.5106692673036</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1010713066918627</v>
+        <v>0.1009082875356237</v>
       </c>
       <c r="C26">
-        <v>139.1207627923847</v>
+        <v>137.1966257293486</v>
       </c>
       <c r="D26">
-        <v>-24.75763720761534</v>
+        <v>-24.83087427065143</v>
       </c>
       <c r="E26">
-        <v>36.7316</v>
+        <v>38.5825</v>
       </c>
       <c r="F26">
-        <v>44.4216</v>
+        <v>46.2725</v>
       </c>
       <c r="G26">
         <v>208.3</v>
@@ -3413,28 +3413,28 @@
         <v>193.3</v>
       </c>
       <c r="M26">
-        <v>2.23440648</v>
+        <v>2.32750675</v>
       </c>
       <c r="N26">
-        <v>191.06559352</v>
+        <v>190.97249325</v>
       </c>
       <c r="O26">
-        <v>36.30246276880001</v>
+        <v>36.2847737175</v>
       </c>
       <c r="P26">
-        <v>154.7631307512</v>
+        <v>154.6877195325</v>
       </c>
       <c r="Q26">
-        <v>267.6631307512</v>
+        <v>267.5877195325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1201223509103457</v>
+        <v>0.1209633833808316</v>
       </c>
       <c r="T26">
-        <v>1.361239957854521</v>
+        <v>1.376643762909874</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>86.51066926730361</v>
+        <v>83.05024249661146</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1009082875356237</v>
+        <v>0.1007452683793847</v>
       </c>
       <c r="C27">
-        <v>137.1966257293486</v>
+        <v>135.2720540867909</v>
       </c>
       <c r="D27">
-        <v>-24.83087427065143</v>
+        <v>-24.90454591320906</v>
       </c>
       <c r="E27">
-        <v>38.5825</v>
+        <v>40.43340000000001</v>
       </c>
       <c r="F27">
-        <v>46.2725</v>
+        <v>48.1234</v>
       </c>
       <c r="G27">
         <v>208.3</v>
@@ -3495,28 +3495,28 @@
         <v>193.3</v>
       </c>
       <c r="M27">
-        <v>2.32750675</v>
+        <v>2.42060702</v>
       </c>
       <c r="N27">
-        <v>190.97249325</v>
+        <v>190.87939298</v>
       </c>
       <c r="O27">
-        <v>36.2847737175</v>
+        <v>36.2670846662</v>
       </c>
       <c r="P27">
-        <v>154.6877195325</v>
+        <v>154.6123083138</v>
       </c>
       <c r="Q27">
-        <v>267.5877195325</v>
+        <v>267.5123083138</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1209633833808316</v>
+        <v>0.1218271464586279</v>
       </c>
       <c r="T27">
-        <v>1.376643762909874</v>
+        <v>1.392463887020777</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>83.05024249661146</v>
+        <v>79.85600240058793</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1007452683793847</v>
+        <v>0.1005822492231456</v>
       </c>
       <c r="C28">
-        <v>135.2720540867909</v>
+        <v>133.3470439850908</v>
       </c>
       <c r="D28">
-        <v>-24.90454591320906</v>
+        <v>-24.97865601490917</v>
       </c>
       <c r="E28">
-        <v>40.43340000000001</v>
+        <v>42.28430000000001</v>
       </c>
       <c r="F28">
-        <v>48.1234</v>
+        <v>49.97430000000001</v>
       </c>
       <c r="G28">
         <v>208.3</v>
@@ -3577,28 +3577,28 @@
         <v>193.3</v>
       </c>
       <c r="M28">
-        <v>2.42060702</v>
+        <v>2.51370729</v>
       </c>
       <c r="N28">
-        <v>190.87939298</v>
+        <v>190.78629271</v>
       </c>
       <c r="O28">
-        <v>36.2670846662</v>
+        <v>36.2493956149</v>
       </c>
       <c r="P28">
-        <v>154.6123083138</v>
+        <v>154.5368970951</v>
       </c>
       <c r="Q28">
-        <v>267.5123083138</v>
+        <v>267.4368970951</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1218271464586279</v>
+        <v>0.1227145742782817</v>
       </c>
       <c r="T28">
-        <v>1.392463887020777</v>
+        <v>1.408717439189513</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>79.85600240058793</v>
+        <v>76.89837268204764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1005822492231456</v>
+        <v>0.1004192300669066</v>
       </c>
       <c r="C29">
-        <v>133.3470439850908</v>
+        <v>131.4215914983101</v>
       </c>
       <c r="D29">
-        <v>-24.97865601490917</v>
+        <v>-25.05320850168987</v>
       </c>
       <c r="E29">
-        <v>42.28430000000001</v>
+        <v>44.1352</v>
       </c>
       <c r="F29">
-        <v>49.97430000000001</v>
+        <v>51.8252</v>
       </c>
       <c r="G29">
         <v>208.3</v>
@@ -3659,28 +3659,28 @@
         <v>193.3</v>
       </c>
       <c r="M29">
-        <v>2.51370729</v>
+        <v>2.60680756</v>
       </c>
       <c r="N29">
-        <v>190.78629271</v>
+        <v>190.69319244</v>
       </c>
       <c r="O29">
-        <v>36.2493956149</v>
+        <v>36.23170656360001</v>
       </c>
       <c r="P29">
-        <v>154.5368970951</v>
+        <v>154.4614858764</v>
       </c>
       <c r="Q29">
-        <v>267.4368970951</v>
+        <v>267.3614858764</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1227145742782817</v>
+        <v>0.1236266528707036</v>
       </c>
       <c r="T29">
-        <v>1.408717439189513</v>
+        <v>1.425422478918491</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>76.89837268204764</v>
+        <v>74.15200222911737</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1004192300669066</v>
+        <v>0.1002562109106676</v>
       </c>
       <c r="C30">
-        <v>131.4215914983101</v>
+        <v>129.4956926535002</v>
       </c>
       <c r="D30">
-        <v>-25.05320850168987</v>
+        <v>-25.12820734649981</v>
       </c>
       <c r="E30">
-        <v>44.1352</v>
+        <v>45.98610000000001</v>
       </c>
       <c r="F30">
-        <v>51.8252</v>
+        <v>53.67610000000001</v>
       </c>
       <c r="G30">
         <v>208.3</v>
@@ -3741,28 +3741,28 @@
         <v>193.3</v>
       </c>
       <c r="M30">
-        <v>2.60680756</v>
+        <v>2.69990783</v>
       </c>
       <c r="N30">
-        <v>190.69319244</v>
+        <v>190.60009217</v>
       </c>
       <c r="O30">
-        <v>36.23170656360001</v>
+        <v>36.2140175123</v>
       </c>
       <c r="P30">
-        <v>154.4614858764</v>
+        <v>154.3860746577</v>
       </c>
       <c r="Q30">
-        <v>267.3614858764</v>
+        <v>267.2860746577</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1236266528707036</v>
+        <v>0.1245644238178416</v>
       </c>
       <c r="T30">
-        <v>1.425422478918491</v>
+        <v>1.442598083146878</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>74.15200222911737</v>
+        <v>71.59503663500986</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1002562109106675</v>
+        <v>0.1000931917544285</v>
       </c>
       <c r="C31">
-        <v>129.4956926535002</v>
+        <v>127.5693434299962</v>
       </c>
       <c r="D31">
-        <v>-25.12820734649982</v>
+        <v>-25.20365657000383</v>
       </c>
       <c r="E31">
-        <v>45.9861</v>
+        <v>47.837</v>
       </c>
       <c r="F31">
-        <v>53.6761</v>
+        <v>55.527</v>
       </c>
       <c r="G31">
         <v>208.3</v>
@@ -3823,28 +3823,28 @@
         <v>193.3</v>
       </c>
       <c r="M31">
-        <v>2.69990783</v>
+        <v>2.7930081</v>
       </c>
       <c r="N31">
-        <v>190.60009217</v>
+        <v>190.5069919</v>
       </c>
       <c r="O31">
-        <v>36.2140175123</v>
+        <v>36.196328461</v>
       </c>
       <c r="P31">
-        <v>154.3860746577</v>
+        <v>154.310663439</v>
       </c>
       <c r="Q31">
-        <v>267.2860746577</v>
+        <v>267.210663439</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1245644238178416</v>
+        <v>0.1255289882206121</v>
       </c>
       <c r="T31">
-        <v>1.442598083146878</v>
+        <v>1.460264418924647</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>71.59503663500988</v>
+        <v>69.20853541384288</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1000931917544285</v>
+        <v>0.09993017259818945</v>
       </c>
       <c r="C32">
-        <v>127.5693434299962</v>
+        <v>125.6425397586985</v>
       </c>
       <c r="D32">
-        <v>-25.20365657000383</v>
+        <v>-25.27956024130152</v>
       </c>
       <c r="E32">
-        <v>47.837</v>
+        <v>49.68790000000001</v>
       </c>
       <c r="F32">
-        <v>55.527</v>
+        <v>57.3779</v>
       </c>
       <c r="G32">
         <v>208.3</v>
@@ -3905,28 +3905,28 @@
         <v>193.3</v>
       </c>
       <c r="M32">
-        <v>2.7930081</v>
+        <v>2.88610837</v>
       </c>
       <c r="N32">
-        <v>190.5069919</v>
+        <v>190.41389163</v>
       </c>
       <c r="O32">
-        <v>36.196328461</v>
+        <v>36.1786394097</v>
       </c>
       <c r="P32">
-        <v>154.310663439</v>
+        <v>154.2352522203</v>
       </c>
       <c r="Q32">
-        <v>267.210663439</v>
+        <v>267.1352522203</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1255289882206121</v>
+        <v>0.1265215110118688</v>
       </c>
       <c r="T32">
-        <v>1.460264418924647</v>
+        <v>1.478442822406119</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>69.20853541384288</v>
+        <v>66.97600201339634</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09993017259818945</v>
+        <v>0.09976715344195042</v>
       </c>
       <c r="C33">
-        <v>125.6425397586985</v>
+        <v>123.7152775213412</v>
       </c>
       <c r="D33">
-        <v>-25.27956024130152</v>
+        <v>-25.3559224786588</v>
       </c>
       <c r="E33">
-        <v>49.68790000000001</v>
+        <v>51.5388</v>
       </c>
       <c r="F33">
-        <v>57.3779</v>
+        <v>59.2288</v>
       </c>
       <c r="G33">
         <v>208.3</v>
@@ -3987,28 +3987,28 @@
         <v>193.3</v>
       </c>
       <c r="M33">
-        <v>2.88610837</v>
+        <v>2.97920864</v>
       </c>
       <c r="N33">
-        <v>190.41389163</v>
+        <v>190.32079136</v>
       </c>
       <c r="O33">
-        <v>36.1786394097</v>
+        <v>36.1609503584</v>
       </c>
       <c r="P33">
-        <v>154.2352522203</v>
+        <v>154.1598410016</v>
       </c>
       <c r="Q33">
-        <v>267.1352522203</v>
+        <v>267.0598410016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1265215110118688</v>
+        <v>0.1275432256499271</v>
       </c>
       <c r="T33">
-        <v>1.478442822406119</v>
+        <v>1.497155884813517</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>66.97600201339634</v>
+        <v>64.88300195047771</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09976715344195042</v>
+        <v>0.09960413428571138</v>
       </c>
       <c r="C34">
-        <v>123.7152775213412</v>
+        <v>121.7875525497473</v>
       </c>
       <c r="D34">
-        <v>-25.3559224786588</v>
+        <v>-25.43274745025269</v>
       </c>
       <c r="E34">
-        <v>51.5388</v>
+        <v>53.3897</v>
       </c>
       <c r="F34">
-        <v>59.2288</v>
+        <v>61.0797</v>
       </c>
       <c r="G34">
         <v>208.3</v>
@@ -4069,28 +4069,28 @@
         <v>193.3</v>
       </c>
       <c r="M34">
-        <v>2.97920864</v>
+        <v>3.07230891</v>
       </c>
       <c r="N34">
-        <v>190.32079136</v>
+        <v>190.22769109</v>
       </c>
       <c r="O34">
-        <v>36.1609503584</v>
+        <v>36.1432613071</v>
       </c>
       <c r="P34">
-        <v>154.1598410016</v>
+        <v>154.0844297829</v>
       </c>
       <c r="Q34">
-        <v>267.0598410016</v>
+        <v>266.9844297829</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1275432256499271</v>
+        <v>0.1285954392324051</v>
       </c>
       <c r="T34">
-        <v>1.497155884813517</v>
+        <v>1.516427546098748</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>64.88300195047771</v>
+        <v>62.9168503762208</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09960413428571138</v>
+        <v>0.09944111512947233</v>
       </c>
       <c r="C35">
-        <v>121.7875525497473</v>
+        <v>119.8593606250703</v>
       </c>
       <c r="D35">
-        <v>-25.43274745025269</v>
+        <v>-25.51003937492976</v>
       </c>
       <c r="E35">
-        <v>53.3897</v>
+        <v>55.24060000000001</v>
       </c>
       <c r="F35">
-        <v>61.0797</v>
+        <v>62.93060000000001</v>
       </c>
       <c r="G35">
         <v>208.3</v>
@@ -4151,28 +4151,28 @@
         <v>193.3</v>
       </c>
       <c r="M35">
-        <v>3.07230891</v>
+        <v>3.16540918</v>
       </c>
       <c r="N35">
-        <v>190.22769109</v>
+        <v>190.13459082</v>
       </c>
       <c r="O35">
-        <v>36.1432613071</v>
+        <v>36.1255722558</v>
       </c>
       <c r="P35">
-        <v>154.0844297829</v>
+        <v>154.0090185642</v>
       </c>
       <c r="Q35">
-        <v>266.9844297829</v>
+        <v>266.9090185642</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1285954392324051</v>
+        <v>0.1296795380749581</v>
       </c>
       <c r="T35">
-        <v>1.516427546098748</v>
+        <v>1.536283197119895</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>62.9168503762208</v>
+        <v>61.06635477692018</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09944111512947233</v>
+        <v>0.09927809597323328</v>
       </c>
       <c r="C36">
-        <v>119.8593606250703</v>
+        <v>117.9306974770216</v>
       </c>
       <c r="D36">
-        <v>-25.51003937492976</v>
+        <v>-25.5878025229784</v>
       </c>
       <c r="E36">
-        <v>55.24060000000001</v>
+        <v>57.09150000000001</v>
       </c>
       <c r="F36">
-        <v>62.93060000000001</v>
+        <v>64.78150000000001</v>
       </c>
       <c r="G36">
         <v>208.3</v>
@@ -4233,28 +4233,28 @@
         <v>193.3</v>
       </c>
       <c r="M36">
-        <v>3.16540918</v>
+        <v>3.25850945</v>
       </c>
       <c r="N36">
-        <v>190.13459082</v>
+        <v>190.04149055</v>
       </c>
       <c r="O36">
-        <v>36.1255722558</v>
+        <v>36.10788320450001</v>
       </c>
       <c r="P36">
-        <v>154.0090185642</v>
+        <v>153.9336073455</v>
       </c>
       <c r="Q36">
-        <v>266.9090185642</v>
+        <v>266.8336073455</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1296795380749581</v>
+        <v>0.1307969938049743</v>
       </c>
       <c r="T36">
-        <v>1.536283197119895</v>
+        <v>1.556749791249385</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>61.06635477692018</v>
+        <v>59.32160178329389</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09927809597323328</v>
+        <v>0.09911507681699426</v>
       </c>
       <c r="C37">
-        <v>117.9306974770216</v>
+        <v>116.0015587830847</v>
       </c>
       <c r="D37">
-        <v>-25.5878025229784</v>
+        <v>-25.66604121691529</v>
       </c>
       <c r="E37">
-        <v>57.09150000000001</v>
+        <v>58.94240000000001</v>
       </c>
       <c r="F37">
-        <v>64.78150000000001</v>
+        <v>66.6324</v>
       </c>
       <c r="G37">
         <v>208.3</v>
@@ -4315,28 +4315,28 @@
         <v>193.3</v>
       </c>
       <c r="M37">
-        <v>3.25850945</v>
+        <v>3.35160972</v>
       </c>
       <c r="N37">
-        <v>190.04149055</v>
+        <v>189.94839028</v>
       </c>
       <c r="O37">
-        <v>36.10788320450001</v>
+        <v>36.0901941532</v>
       </c>
       <c r="P37">
-        <v>153.9336073455</v>
+        <v>153.8581961268</v>
       </c>
       <c r="Q37">
-        <v>266.8336073455</v>
+        <v>266.7581961268</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1307969938049743</v>
+        <v>0.1319493700265535</v>
       </c>
       <c r="T37">
-        <v>1.556749791249385</v>
+        <v>1.577855966445421</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>59.32160178329389</v>
+        <v>57.67377951153573</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09911507681699427</v>
+        <v>0.09895205766075524</v>
       </c>
       <c r="C38">
-        <v>116.0015587830847</v>
+        <v>114.0719401677137</v>
       </c>
       <c r="D38">
-        <v>-25.66604121691528</v>
+        <v>-25.74475983228635</v>
       </c>
       <c r="E38">
-        <v>58.94240000000001</v>
+        <v>60.7933</v>
       </c>
       <c r="F38">
-        <v>66.6324</v>
+        <v>68.4833</v>
       </c>
       <c r="G38">
         <v>208.3</v>
@@ -4397,28 +4397,28 @@
         <v>193.3</v>
       </c>
       <c r="M38">
-        <v>3.35160972</v>
+        <v>3.44470999</v>
       </c>
       <c r="N38">
-        <v>189.94839028</v>
+        <v>189.85529001</v>
       </c>
       <c r="O38">
-        <v>36.0901941532</v>
+        <v>36.0725051019</v>
       </c>
       <c r="P38">
-        <v>153.8581961268</v>
+        <v>153.7827849081</v>
       </c>
       <c r="Q38">
-        <v>266.7581961268</v>
+        <v>266.6827849081</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1319493700265535</v>
+        <v>0.1331383296202464</v>
       </c>
       <c r="T38">
-        <v>1.577855966445421</v>
+        <v>1.599632178949268</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>57.67377951153573</v>
+        <v>56.11502871392666</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09895205766075524</v>
+        <v>0.09878903850451619</v>
       </c>
       <c r="C39">
-        <v>114.0719401677137</v>
+        <v>112.1418372015176</v>
       </c>
       <c r="D39">
-        <v>-25.74475983228635</v>
+        <v>-25.82396279848244</v>
       </c>
       <c r="E39">
-        <v>60.7933</v>
+        <v>62.6442</v>
       </c>
       <c r="F39">
-        <v>68.4833</v>
+        <v>70.3342</v>
       </c>
       <c r="G39">
         <v>208.3</v>
@@ -4479,28 +4479,28 @@
         <v>193.3</v>
       </c>
       <c r="M39">
-        <v>3.44470999</v>
+        <v>3.53781026</v>
       </c>
       <c r="N39">
-        <v>189.85529001</v>
+        <v>189.76218974</v>
       </c>
       <c r="O39">
-        <v>36.0725051019</v>
+        <v>36.0548160506</v>
       </c>
       <c r="P39">
-        <v>153.7827849081</v>
+        <v>153.7073736894</v>
       </c>
       <c r="Q39">
-        <v>266.6827849081</v>
+        <v>266.6073736894</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1331383296202464</v>
+        <v>0.1343656427492197</v>
       </c>
       <c r="T39">
-        <v>1.599632178949268</v>
+        <v>1.622110849920981</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>56.11502871392666</v>
+        <v>54.63831743198123</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09878903850451619</v>
+        <v>0.09862601934827715</v>
       </c>
       <c r="C40">
-        <v>112.1418372015176</v>
+        <v>110.2112454004299</v>
       </c>
       <c r="D40">
-        <v>-25.82396279848244</v>
+        <v>-25.90365459957012</v>
       </c>
       <c r="E40">
-        <v>62.6442</v>
+        <v>64.49510000000001</v>
       </c>
       <c r="F40">
-        <v>70.3342</v>
+        <v>72.18510000000001</v>
       </c>
       <c r="G40">
         <v>208.3</v>
@@ -4561,28 +4561,28 @@
         <v>193.3</v>
       </c>
       <c r="M40">
-        <v>3.53781026</v>
+        <v>3.63091053</v>
       </c>
       <c r="N40">
-        <v>189.76218974</v>
+        <v>189.66908947</v>
       </c>
       <c r="O40">
-        <v>36.0548160506</v>
+        <v>36.03712699930001</v>
       </c>
       <c r="P40">
-        <v>153.7073736894</v>
+        <v>153.6319624707</v>
       </c>
       <c r="Q40">
-        <v>266.6073736894</v>
+        <v>266.5319624707</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1343656427492197</v>
+        <v>0.1356331956529134</v>
       </c>
       <c r="T40">
-        <v>1.622110849920981</v>
+        <v>1.645326526498325</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>54.63831743198123</v>
+        <v>53.23733493372529</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09862601934827715</v>
+        <v>0.0984630001920381</v>
       </c>
       <c r="C41">
-        <v>110.2112454004299</v>
+        <v>108.280160224862</v>
       </c>
       <c r="D41">
-        <v>-25.90365459957012</v>
+        <v>-25.98383977513799</v>
       </c>
       <c r="E41">
-        <v>64.49510000000001</v>
+        <v>66.346</v>
       </c>
       <c r="F41">
-        <v>72.18510000000001</v>
+        <v>74.036</v>
       </c>
       <c r="G41">
         <v>208.3</v>
@@ -4643,28 +4643,28 @@
         <v>193.3</v>
       </c>
       <c r="M41">
-        <v>3.63091053</v>
+        <v>3.7240108</v>
       </c>
       <c r="N41">
-        <v>189.66908947</v>
+        <v>189.5759892</v>
       </c>
       <c r="O41">
-        <v>36.03712699930001</v>
+        <v>36.019437948</v>
       </c>
       <c r="P41">
-        <v>153.6319624707</v>
+        <v>153.556551252</v>
       </c>
       <c r="Q41">
-        <v>266.5319624707</v>
+        <v>266.456551252</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1356331956529134</v>
+        <v>0.1369430003200635</v>
       </c>
       <c r="T41">
-        <v>1.645326526498325</v>
+        <v>1.669316058961579</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>53.23733493372529</v>
+        <v>51.90640156038216</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0984630001920381</v>
+        <v>0.09829998103579907</v>
       </c>
       <c r="C42">
-        <v>108.280160224862</v>
+        <v>106.3485770788414</v>
       </c>
       <c r="D42">
-        <v>-25.98383977513799</v>
+        <v>-26.06452292115866</v>
       </c>
       <c r="E42">
-        <v>66.346</v>
+        <v>68.19690000000001</v>
       </c>
       <c r="F42">
-        <v>74.036</v>
+        <v>75.88690000000001</v>
       </c>
       <c r="G42">
         <v>208.3</v>
@@ -4725,28 +4725,28 @@
         <v>193.3</v>
       </c>
       <c r="M42">
-        <v>3.7240108</v>
+        <v>3.81711107</v>
       </c>
       <c r="N42">
-        <v>189.5759892</v>
+        <v>189.48288893</v>
       </c>
       <c r="O42">
-        <v>36.019437948</v>
+        <v>36.0017488967</v>
       </c>
       <c r="P42">
-        <v>153.556551252</v>
+        <v>153.4811400333</v>
       </c>
       <c r="Q42">
-        <v>266.456551252</v>
+        <v>266.3811400333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1369430003200635</v>
+        <v>0.1382972051454222</v>
       </c>
       <c r="T42">
-        <v>1.669316058961579</v>
+        <v>1.694118795915113</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>51.90640156038216</v>
+        <v>50.64039176622649</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09829998103579907</v>
+        <v>0.09813696187956003</v>
       </c>
       <c r="C43">
-        <v>106.3485770788414</v>
+        <v>104.4164913091331</v>
       </c>
       <c r="D43">
-        <v>-26.06452292115866</v>
+        <v>-26.14570869086684</v>
       </c>
       <c r="E43">
-        <v>68.19690000000001</v>
+        <v>70.04780000000001</v>
       </c>
       <c r="F43">
-        <v>75.88690000000001</v>
+        <v>77.73780000000001</v>
       </c>
       <c r="G43">
         <v>208.3</v>
@@ -4807,28 +4807,28 @@
         <v>193.3</v>
       </c>
       <c r="M43">
-        <v>3.81711107</v>
+        <v>3.91021134</v>
       </c>
       <c r="N43">
-        <v>189.48288893</v>
+        <v>189.38978866</v>
       </c>
       <c r="O43">
-        <v>36.0017488967</v>
+        <v>35.9840598454</v>
       </c>
       <c r="P43">
-        <v>153.4811400333</v>
+        <v>153.4057288146</v>
       </c>
       <c r="Q43">
-        <v>266.3811400333</v>
+        <v>266.3057288146</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1382972051454222</v>
+        <v>0.1396981066888966</v>
       </c>
       <c r="T43">
-        <v>1.694118795915113</v>
+        <v>1.719776799660149</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>50.64039176622649</v>
+        <v>49.43466815274491</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09813696187956003</v>
+        <v>0.09797394272332099</v>
       </c>
       <c r="C44">
-        <v>104.4164913091332</v>
+        <v>102.483898204346</v>
       </c>
       <c r="D44">
-        <v>-26.14570869086684</v>
+        <v>-26.22740179565402</v>
       </c>
       <c r="E44">
-        <v>70.0478</v>
+        <v>71.89870000000001</v>
       </c>
       <c r="F44">
-        <v>77.73779999999999</v>
+        <v>79.5887</v>
       </c>
       <c r="G44">
         <v>208.3</v>
@@ -4889,28 +4889,28 @@
         <v>193.3</v>
       </c>
       <c r="M44">
-        <v>3.91021134</v>
+        <v>4.00331161</v>
       </c>
       <c r="N44">
-        <v>189.38978866</v>
+        <v>189.29668839</v>
       </c>
       <c r="O44">
-        <v>35.9840598454</v>
+        <v>35.9663707941</v>
       </c>
       <c r="P44">
-        <v>153.4057288146</v>
+        <v>153.3303175959</v>
       </c>
       <c r="Q44">
-        <v>266.3057288146</v>
+        <v>266.2303175959</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1396981066888966</v>
+        <v>0.141148162672493</v>
       </c>
       <c r="T44">
-        <v>1.719776799660149</v>
+        <v>1.746335084238343</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>49.43466815274492</v>
+        <v>48.28502470733224</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09797394272332099</v>
+        <v>0.09781092356708196</v>
       </c>
       <c r="C45">
-        <v>102.483898204346</v>
+        <v>100.5507929940202</v>
       </c>
       <c r="D45">
-        <v>-26.22740179565402</v>
+        <v>-26.3096070059798</v>
       </c>
       <c r="E45">
-        <v>71.89870000000001</v>
+        <v>73.7496</v>
       </c>
       <c r="F45">
-        <v>79.5887</v>
+        <v>81.4396</v>
       </c>
       <c r="G45">
         <v>208.3</v>
@@ -4971,28 +4971,28 @@
         <v>193.3</v>
       </c>
       <c r="M45">
-        <v>4.00331161</v>
+        <v>4.09641188</v>
       </c>
       <c r="N45">
-        <v>189.29668839</v>
+        <v>189.20358812</v>
       </c>
       <c r="O45">
-        <v>35.9663707941</v>
+        <v>35.9486817428</v>
       </c>
       <c r="P45">
-        <v>153.3303175959</v>
+        <v>153.2549063772</v>
       </c>
       <c r="Q45">
-        <v>266.2303175959</v>
+        <v>266.1549063771999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.141148162672493</v>
+        <v>0.1426500063697892</v>
       </c>
       <c r="T45">
-        <v>1.746335084238343</v>
+        <v>1.773841878980045</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>48.28502470733224</v>
+        <v>47.1876377821656</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09781092356708196</v>
+        <v>0.09764790441084291</v>
       </c>
       <c r="C46">
-        <v>100.5507929940202</v>
+        <v>98.6171708476995</v>
       </c>
       <c r="D46">
-        <v>-26.3096070059798</v>
+        <v>-26.39232915230051</v>
       </c>
       <c r="E46">
-        <v>73.7496</v>
+        <v>75.60050000000001</v>
       </c>
       <c r="F46">
-        <v>81.4396</v>
+        <v>83.29050000000001</v>
       </c>
       <c r="G46">
         <v>208.3</v>
@@ -5053,28 +5053,28 @@
         <v>193.3</v>
       </c>
       <c r="M46">
-        <v>4.09641188</v>
+        <v>4.189512150000001</v>
       </c>
       <c r="N46">
-        <v>189.20358812</v>
+        <v>189.11048785</v>
       </c>
       <c r="O46">
-        <v>35.9486817428</v>
+        <v>35.9309926915</v>
       </c>
       <c r="P46">
-        <v>153.2549063772</v>
+        <v>153.1794951585</v>
       </c>
       <c r="Q46">
-        <v>266.1549063771999</v>
+        <v>266.0794951585</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1426500063697892</v>
+        <v>0.1442064625651689</v>
       </c>
       <c r="T46">
-        <v>1.773841878980045</v>
+        <v>1.802348920803263</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>47.1876377821656</v>
+        <v>46.13902360922857</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09764790441084291</v>
+        <v>0.09748488525460387</v>
       </c>
       <c r="C47">
-        <v>98.6171708476995</v>
+        <v>96.68302687398463</v>
       </c>
       <c r="D47">
-        <v>-26.39232915230051</v>
+        <v>-26.47557312601539</v>
       </c>
       <c r="E47">
-        <v>75.60050000000001</v>
+        <v>77.45140000000001</v>
       </c>
       <c r="F47">
-        <v>83.29050000000001</v>
+        <v>85.1414</v>
       </c>
       <c r="G47">
         <v>208.3</v>
@@ -5135,28 +5135,28 @@
         <v>193.3</v>
       </c>
       <c r="M47">
-        <v>4.189512150000001</v>
+        <v>4.28261242</v>
       </c>
       <c r="N47">
-        <v>189.11048785</v>
+        <v>189.01738758</v>
       </c>
       <c r="O47">
-        <v>35.9309926915</v>
+        <v>35.91330364020001</v>
       </c>
       <c r="P47">
-        <v>153.1794951585</v>
+        <v>153.1040839398</v>
       </c>
       <c r="Q47">
-        <v>266.0794951585</v>
+        <v>266.0040839398</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1442064625651689</v>
+        <v>0.1458205652863035</v>
       </c>
       <c r="T47">
-        <v>1.802348920803263</v>
+        <v>1.831911778990304</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>46.13902360922857</v>
+        <v>45.13600135685405</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09748488525460387</v>
+        <v>0.09732186609836484</v>
       </c>
       <c r="C48">
-        <v>96.68302687398463</v>
+        <v>94.74835611956925</v>
       </c>
       <c r="D48">
-        <v>-26.47557312601539</v>
+        <v>-26.55934388043076</v>
       </c>
       <c r="E48">
-        <v>77.45140000000001</v>
+        <v>79.3023</v>
       </c>
       <c r="F48">
-        <v>85.1414</v>
+        <v>86.9923</v>
       </c>
       <c r="G48">
         <v>208.3</v>
@@ -5217,28 +5217,28 @@
         <v>193.3</v>
       </c>
       <c r="M48">
-        <v>4.28261242</v>
+        <v>4.375712689999999</v>
       </c>
       <c r="N48">
-        <v>189.01738758</v>
+        <v>188.92428731</v>
       </c>
       <c r="O48">
-        <v>35.91330364020001</v>
+        <v>35.8956145889</v>
       </c>
       <c r="P48">
-        <v>153.1040839398</v>
+        <v>153.0286727211</v>
       </c>
       <c r="Q48">
-        <v>266.0040839398</v>
+        <v>265.9286727211</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1458205652863035</v>
+        <v>0.1474955775440846</v>
       </c>
       <c r="T48">
-        <v>1.831911778990304</v>
+        <v>1.862590216731573</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>45.13600135685405</v>
+        <v>44.1756609024529</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09732186609836484</v>
+        <v>0.0971588469421258</v>
       </c>
       <c r="C49">
-        <v>94.74835611956925</v>
+        <v>92.8131535682575</v>
       </c>
       <c r="D49">
-        <v>-26.55934388043076</v>
+        <v>-26.6436464317425</v>
       </c>
       <c r="E49">
-        <v>79.3023</v>
+        <v>81.15320000000001</v>
       </c>
       <c r="F49">
-        <v>86.9923</v>
+        <v>88.84320000000001</v>
       </c>
       <c r="G49">
         <v>208.3</v>
@@ -5299,28 +5299,28 @@
         <v>193.3</v>
       </c>
       <c r="M49">
-        <v>4.375712689999999</v>
+        <v>4.46881296</v>
       </c>
       <c r="N49">
-        <v>188.92428731</v>
+        <v>188.83118704</v>
       </c>
       <c r="O49">
-        <v>35.8956145889</v>
+        <v>35.8779255376</v>
       </c>
       <c r="P49">
-        <v>153.0286727211</v>
+        <v>152.9532615024</v>
       </c>
       <c r="Q49">
-        <v>265.9286727211</v>
+        <v>265.8532615024</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1474955775440846</v>
+        <v>0.1492350133502419</v>
       </c>
       <c r="T49">
-        <v>1.862590216731573</v>
+        <v>1.894448594385968</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>44.1756609024529</v>
+        <v>43.2553346336518</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0971588469421258</v>
+        <v>0.09699582778588677</v>
       </c>
       <c r="C50">
-        <v>92.81315356825752</v>
+        <v>90.87741413996271</v>
       </c>
       <c r="D50">
-        <v>-26.6436464317425</v>
+        <v>-26.72848586003731</v>
       </c>
       <c r="E50">
-        <v>81.1532</v>
+        <v>83.00410000000001</v>
       </c>
       <c r="F50">
-        <v>88.8432</v>
+        <v>90.69410000000001</v>
       </c>
       <c r="G50">
         <v>208.3</v>
@@ -5381,28 +5381,28 @@
         <v>193.3</v>
       </c>
       <c r="M50">
-        <v>4.468812959999999</v>
+        <v>4.56191323</v>
       </c>
       <c r="N50">
-        <v>188.83118704</v>
+        <v>188.73808677</v>
       </c>
       <c r="O50">
-        <v>35.8779255376</v>
+        <v>35.8602364863</v>
       </c>
       <c r="P50">
-        <v>152.9532615024</v>
+        <v>152.8778502837</v>
       </c>
       <c r="Q50">
-        <v>265.8532615024</v>
+        <v>265.7778502837</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1492350133502419</v>
+        <v>0.1510426623252682</v>
       </c>
       <c r="T50">
-        <v>1.894448594385968</v>
+        <v>1.927556320183672</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>43.25533463365181</v>
+        <v>42.37257270235278</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09699582778588677</v>
+        <v>0.09683280862964772</v>
       </c>
       <c r="C51">
-        <v>90.87741413996271</v>
+        <v>88.94113268968682</v>
       </c>
       <c r="D51">
-        <v>-26.72848586003731</v>
+        <v>-26.81386731031319</v>
       </c>
       <c r="E51">
-        <v>83.00410000000001</v>
+        <v>84.855</v>
       </c>
       <c r="F51">
-        <v>90.69410000000001</v>
+        <v>92.545</v>
       </c>
       <c r="G51">
         <v>208.3</v>
@@ -5463,28 +5463,28 @@
         <v>193.3</v>
       </c>
       <c r="M51">
-        <v>4.56191323</v>
+        <v>4.6550135</v>
       </c>
       <c r="N51">
-        <v>188.73808677</v>
+        <v>188.6449865</v>
       </c>
       <c r="O51">
-        <v>35.8602364863</v>
+        <v>35.842547435</v>
       </c>
       <c r="P51">
-        <v>152.8778502837</v>
+        <v>152.802439065</v>
       </c>
       <c r="Q51">
-        <v>265.7778502837</v>
+        <v>265.702439065</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1510426623252682</v>
+        <v>0.1529226172592954</v>
       </c>
       <c r="T51">
-        <v>1.927556320183672</v>
+        <v>1.961988355013284</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>42.37257270235278</v>
+        <v>41.52512124830573</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09683280862964772</v>
+        <v>0.09666978947340869</v>
       </c>
       <c r="C52">
-        <v>88.94113268968682</v>
+        <v>87.00430400648052</v>
       </c>
       <c r="D52">
-        <v>-26.81386731031319</v>
+        <v>-26.8997959935195</v>
       </c>
       <c r="E52">
-        <v>84.855</v>
+        <v>86.7059</v>
       </c>
       <c r="F52">
-        <v>92.545</v>
+        <v>94.3959</v>
       </c>
       <c r="G52">
         <v>208.3</v>
@@ -5545,28 +5545,28 @@
         <v>193.3</v>
       </c>
       <c r="M52">
-        <v>4.6550135</v>
+        <v>4.74811377</v>
       </c>
       <c r="N52">
-        <v>188.6449865</v>
+        <v>188.55188623</v>
       </c>
       <c r="O52">
-        <v>35.842547435</v>
+        <v>35.8248583837</v>
       </c>
       <c r="P52">
-        <v>152.802439065</v>
+        <v>152.7270278463</v>
       </c>
       <c r="Q52">
-        <v>265.702439065</v>
+        <v>265.6270278463</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1529226172592954</v>
+        <v>0.1548793050477728</v>
       </c>
       <c r="T52">
-        <v>1.961988355013284</v>
+        <v>1.997825779019616</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>41.52512124830573</v>
+        <v>40.71090318461346</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09666978947340869</v>
+        <v>0.09650677031716963</v>
       </c>
       <c r="C53">
-        <v>87.00430400648052</v>
+        <v>85.06692281238281</v>
       </c>
       <c r="D53">
-        <v>-26.8997959935195</v>
+        <v>-26.98627718761719</v>
       </c>
       <c r="E53">
-        <v>86.7059</v>
+        <v>88.55680000000001</v>
       </c>
       <c r="F53">
-        <v>94.3959</v>
+        <v>96.24680000000001</v>
       </c>
       <c r="G53">
         <v>208.3</v>
@@ -5627,28 +5627,28 @@
         <v>193.3</v>
       </c>
       <c r="M53">
-        <v>4.74811377</v>
+        <v>4.841214040000001</v>
       </c>
       <c r="N53">
-        <v>188.55188623</v>
+        <v>188.45878596</v>
       </c>
       <c r="O53">
-        <v>35.8248583837</v>
+        <v>35.8071693324</v>
       </c>
       <c r="P53">
-        <v>152.7270278463</v>
+        <v>152.6516166276</v>
       </c>
       <c r="Q53">
-        <v>265.6270278463</v>
+        <v>265.5516166276</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1548793050477728</v>
+        <v>0.1569175214941034</v>
       </c>
       <c r="T53">
-        <v>1.997825779019616</v>
+        <v>2.035156429026211</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>40.71090318461346</v>
+        <v>39.92800120029396</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09650677031716963</v>
+        <v>0.09634375116093059</v>
       </c>
       <c r="C54">
-        <v>85.06692281238281</v>
+        <v>83.12898376134066</v>
       </c>
       <c r="D54">
-        <v>-26.98627718761719</v>
+        <v>-27.07331623865934</v>
       </c>
       <c r="E54">
-        <v>88.55680000000001</v>
+        <v>90.40770000000001</v>
       </c>
       <c r="F54">
-        <v>96.24680000000001</v>
+        <v>98.0977</v>
       </c>
       <c r="G54">
         <v>208.3</v>
@@ -5709,28 +5709,28 @@
         <v>193.3</v>
       </c>
       <c r="M54">
-        <v>4.841214040000001</v>
+        <v>4.93431431</v>
       </c>
       <c r="N54">
-        <v>188.45878596</v>
+        <v>188.36568569</v>
       </c>
       <c r="O54">
-        <v>35.8071693324</v>
+        <v>35.7894802811</v>
       </c>
       <c r="P54">
-        <v>152.6516166276</v>
+        <v>152.5762054089</v>
       </c>
       <c r="Q54">
-        <v>265.5516166276</v>
+        <v>265.4762054089</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1569175214941034</v>
+        <v>0.1590424705551715</v>
       </c>
       <c r="T54">
-        <v>2.035156429026211</v>
+        <v>2.074075617330959</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>39.92800120029396</v>
+        <v>39.17464268708088</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09634375116093059</v>
+        <v>0.09618073200469157</v>
       </c>
       <c r="C55">
-        <v>83.12898376134066</v>
+        <v>81.19048143810708</v>
       </c>
       <c r="D55">
-        <v>-27.07331623865934</v>
+        <v>-27.16091856189291</v>
       </c>
       <c r="E55">
-        <v>90.40770000000001</v>
+        <v>92.25860000000002</v>
       </c>
       <c r="F55">
-        <v>98.0977</v>
+        <v>99.94860000000001</v>
       </c>
       <c r="G55">
         <v>208.3</v>
@@ -5791,28 +5791,28 @@
         <v>193.3</v>
       </c>
       <c r="M55">
-        <v>4.93431431</v>
+        <v>5.02741458</v>
       </c>
       <c r="N55">
-        <v>188.36568569</v>
+        <v>188.27258542</v>
       </c>
       <c r="O55">
-        <v>35.7894802811</v>
+        <v>35.7717912298</v>
       </c>
       <c r="P55">
-        <v>152.5762054089</v>
+        <v>152.5007941902</v>
       </c>
       <c r="Q55">
-        <v>265.4762054089</v>
+        <v>265.4007941902</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1590424705551715</v>
+        <v>0.1612598087058512</v>
       </c>
       <c r="T55">
-        <v>2.074075617330959</v>
+        <v>2.114686944257653</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>39.17464268708088</v>
+        <v>38.44918634102382</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09618073200469157</v>
+        <v>0.09601771284845251</v>
       </c>
       <c r="C56">
-        <v>81.19048143810708</v>
+        <v>79.25141035711819</v>
       </c>
       <c r="D56">
-        <v>-27.16091856189291</v>
+        <v>-27.2490896428818</v>
       </c>
       <c r="E56">
-        <v>92.25860000000002</v>
+        <v>94.10950000000001</v>
       </c>
       <c r="F56">
-        <v>99.94860000000001</v>
+        <v>101.7995</v>
       </c>
       <c r="G56">
         <v>208.3</v>
@@ -5873,28 +5873,28 @@
         <v>193.3</v>
       </c>
       <c r="M56">
-        <v>5.02741458</v>
+        <v>5.12051485</v>
       </c>
       <c r="N56">
-        <v>188.27258542</v>
+        <v>188.17948515</v>
       </c>
       <c r="O56">
-        <v>35.7717912298</v>
+        <v>35.7541021785</v>
       </c>
       <c r="P56">
-        <v>152.5007941902</v>
+        <v>152.4253829715</v>
       </c>
       <c r="Q56">
-        <v>265.4007941902</v>
+        <v>265.3253829714999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1612598087058512</v>
+        <v>0.1635756952187834</v>
       </c>
       <c r="T56">
-        <v>2.114686944257653</v>
+        <v>2.157103219047755</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>38.44918634102382</v>
+        <v>37.75011022573248</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09601771284845251</v>
+        <v>0.09585469369221349</v>
       </c>
       <c r="C57">
-        <v>79.25141035711819</v>
+        <v>77.31176496134815</v>
       </c>
       <c r="D57">
-        <v>-27.2490896428818</v>
+        <v>-27.33783503865185</v>
       </c>
       <c r="E57">
-        <v>94.10950000000001</v>
+        <v>95.96040000000001</v>
       </c>
       <c r="F57">
-        <v>101.7995</v>
+        <v>103.6504</v>
       </c>
       <c r="G57">
         <v>208.3</v>
@@ -5955,28 +5955,28 @@
         <v>193.3</v>
       </c>
       <c r="M57">
-        <v>5.12051485</v>
+        <v>5.21361512</v>
       </c>
       <c r="N57">
-        <v>188.17948515</v>
+        <v>188.08638488</v>
       </c>
       <c r="O57">
-        <v>35.7541021785</v>
+        <v>35.7364131272</v>
       </c>
       <c r="P57">
-        <v>152.4253829715</v>
+        <v>152.3499717528</v>
       </c>
       <c r="Q57">
-        <v>265.3253829714999</v>
+        <v>265.2499717528</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1635756952187834</v>
+        <v>0.1659968493004852</v>
       </c>
       <c r="T57">
-        <v>2.157103219047755</v>
+        <v>2.201447506328317</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>37.75011022573248</v>
+        <v>37.07600111455869</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09585469369221349</v>
+        <v>0.09569167453597444</v>
       </c>
       <c r="C58">
-        <v>77.31176496134815</v>
+        <v>75.37153962114155</v>
       </c>
       <c r="D58">
-        <v>-27.33783503865185</v>
+        <v>-27.42716037885845</v>
       </c>
       <c r="E58">
-        <v>95.96040000000001</v>
+        <v>97.81130000000002</v>
       </c>
       <c r="F58">
-        <v>103.6504</v>
+        <v>105.5013</v>
       </c>
       <c r="G58">
         <v>208.3</v>
@@ -6037,28 +6037,28 @@
         <v>193.3</v>
       </c>
       <c r="M58">
-        <v>5.21361512</v>
+        <v>5.306715390000001</v>
       </c>
       <c r="N58">
-        <v>188.08638488</v>
+        <v>187.99328461</v>
       </c>
       <c r="O58">
-        <v>35.7364131272</v>
+        <v>35.71872407590001</v>
       </c>
       <c r="P58">
-        <v>152.3499717528</v>
+        <v>152.2745605341</v>
       </c>
       <c r="Q58">
-        <v>265.2499717528</v>
+        <v>265.1745605341</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1659968493004852</v>
+        <v>0.1685306151999406</v>
       </c>
       <c r="T58">
-        <v>2.201447506328317</v>
+        <v>2.247854318598671</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>37.07600111455869</v>
+        <v>36.42554495465414</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09569167453597444</v>
+        <v>0.09552865537973541</v>
       </c>
       <c r="C59">
-        <v>75.37153962114155</v>
+        <v>73.43072863302311</v>
       </c>
       <c r="D59">
-        <v>-27.42716037885845</v>
+        <v>-27.5170713669769</v>
       </c>
       <c r="E59">
-        <v>97.81130000000002</v>
+        <v>99.66220000000001</v>
       </c>
       <c r="F59">
-        <v>105.5013</v>
+        <v>107.3522</v>
       </c>
       <c r="G59">
         <v>208.3</v>
@@ -6119,28 +6119,28 @@
         <v>193.3</v>
       </c>
       <c r="M59">
-        <v>5.306715390000001</v>
+        <v>5.399815660000001</v>
       </c>
       <c r="N59">
-        <v>187.99328461</v>
+        <v>187.90018434</v>
       </c>
       <c r="O59">
-        <v>35.71872407590001</v>
+        <v>35.7010350246</v>
       </c>
       <c r="P59">
-        <v>152.2745605341</v>
+        <v>152.1991493154</v>
       </c>
       <c r="Q59">
-        <v>265.1745605341</v>
+        <v>265.0991493154</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1685306151999406</v>
+        <v>0.1711850366184177</v>
       </c>
       <c r="T59">
-        <v>2.247854318598671</v>
+        <v>2.296470979072377</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>36.42554495465414</v>
+        <v>35.79751831750493</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0955286553797354</v>
+        <v>0.09536563622349638</v>
       </c>
       <c r="C60">
-        <v>73.43072863302309</v>
+        <v>71.48932621848358</v>
       </c>
       <c r="D60">
-        <v>-27.51707136697691</v>
+        <v>-27.60757378151643</v>
       </c>
       <c r="E60">
-        <v>99.6622</v>
+        <v>101.5131</v>
       </c>
       <c r="F60">
-        <v>107.3522</v>
+        <v>109.2031</v>
       </c>
       <c r="G60">
         <v>208.3</v>
@@ -6201,28 +6201,28 @@
         <v>193.3</v>
       </c>
       <c r="M60">
-        <v>5.39981566</v>
+        <v>5.49291593</v>
       </c>
       <c r="N60">
-        <v>187.90018434</v>
+        <v>187.80708407</v>
       </c>
       <c r="O60">
-        <v>35.7010350246</v>
+        <v>35.6833459733</v>
       </c>
       <c r="P60">
-        <v>152.1991493154</v>
+        <v>152.1237380967</v>
       </c>
       <c r="Q60">
-        <v>265.0991493154</v>
+        <v>265.0237380967</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1711850366184176</v>
+        <v>0.1739689420085277</v>
       </c>
       <c r="T60">
-        <v>2.296470979072376</v>
+        <v>2.347459183959433</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>35.79751831750494</v>
+        <v>35.19078071890316</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09536563622349638</v>
+        <v>0.09520261706725733</v>
       </c>
       <c r="C61">
-        <v>71.48932621848358</v>
+        <v>69.54732652274191</v>
       </c>
       <c r="D61">
-        <v>-27.60757378151643</v>
+        <v>-27.69867347725811</v>
       </c>
       <c r="E61">
-        <v>101.5131</v>
+        <v>103.364</v>
       </c>
       <c r="F61">
-        <v>109.2031</v>
+        <v>111.054</v>
       </c>
       <c r="G61">
         <v>208.3</v>
@@ -6283,28 +6283,28 @@
         <v>193.3</v>
       </c>
       <c r="M61">
-        <v>5.49291593</v>
+        <v>5.5860162</v>
       </c>
       <c r="N61">
-        <v>187.80708407</v>
+        <v>187.7139838</v>
       </c>
       <c r="O61">
-        <v>35.6833459733</v>
+        <v>35.665656922</v>
       </c>
       <c r="P61">
-        <v>152.1237380967</v>
+        <v>152.048326878</v>
       </c>
       <c r="Q61">
-        <v>265.0237380967</v>
+        <v>264.948326878</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1739689420085277</v>
+        <v>0.1768920426681433</v>
       </c>
       <c r="T61">
-        <v>2.347459183959433</v>
+        <v>2.400996799090842</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>35.19078071890316</v>
+        <v>34.60426770692144</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09520261706725733</v>
+        <v>0.09503959791101831</v>
       </c>
       <c r="C62">
-        <v>69.54732652274191</v>
+        <v>67.60472361348252</v>
       </c>
       <c r="D62">
-        <v>-27.69867347725811</v>
+        <v>-27.7903763865175</v>
       </c>
       <c r="E62">
-        <v>103.364</v>
+        <v>105.2149</v>
       </c>
       <c r="F62">
-        <v>111.054</v>
+        <v>112.9049</v>
       </c>
       <c r="G62">
         <v>208.3</v>
@@ -6365,28 +6365,28 @@
         <v>193.3</v>
       </c>
       <c r="M62">
-        <v>5.5860162</v>
+        <v>5.679116469999999</v>
       </c>
       <c r="N62">
-        <v>187.7139838</v>
+        <v>187.62088353</v>
       </c>
       <c r="O62">
-        <v>35.665656922</v>
+        <v>35.6479678707</v>
       </c>
       <c r="P62">
-        <v>152.048326878</v>
+        <v>151.9729156593</v>
       </c>
       <c r="Q62">
-        <v>264.948326878</v>
+        <v>264.8729156593</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1768920426681433</v>
+        <v>0.1799650459256879</v>
       </c>
       <c r="T62">
-        <v>2.400996799090842</v>
+        <v>2.45727993294694</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>34.60426770692144</v>
+        <v>34.0369846297588</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09503959791101831</v>
+        <v>0.09487657875477926</v>
       </c>
       <c r="C63">
-        <v>67.60472361348252</v>
+        <v>65.66151147956761</v>
       </c>
       <c r="D63">
-        <v>-27.7903763865175</v>
+        <v>-27.88268852043239</v>
       </c>
       <c r="E63">
-        <v>105.2149</v>
+        <v>107.0658</v>
       </c>
       <c r="F63">
-        <v>112.9049</v>
+        <v>114.7558</v>
       </c>
       <c r="G63">
         <v>208.3</v>
@@ -6447,28 +6447,28 @@
         <v>193.3</v>
       </c>
       <c r="M63">
-        <v>5.679116469999999</v>
+        <v>5.77221674</v>
       </c>
       <c r="N63">
-        <v>187.62088353</v>
+        <v>187.52778326</v>
       </c>
       <c r="O63">
-        <v>35.6479678707</v>
+        <v>35.6302788194</v>
       </c>
       <c r="P63">
-        <v>151.9729156593</v>
+        <v>151.8975044406</v>
       </c>
       <c r="Q63">
-        <v>264.8729156593</v>
+        <v>264.7975044406</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1799650459256879</v>
+        <v>0.1831997861967875</v>
       </c>
       <c r="T63">
-        <v>2.45727993294694</v>
+        <v>2.516525337005989</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>34.0369846297588</v>
+        <v>33.48800100669816</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09487657875477926</v>
+        <v>0.09471355959854021</v>
       </c>
       <c r="C64">
-        <v>65.66151147956761</v>
+        <v>63.71768402972377</v>
       </c>
       <c r="D64">
-        <v>-27.88268852043239</v>
+        <v>-27.97561597027623</v>
       </c>
       <c r="E64">
-        <v>107.0658</v>
+        <v>108.9167</v>
       </c>
       <c r="F64">
-        <v>114.7558</v>
+        <v>116.6067</v>
       </c>
       <c r="G64">
         <v>208.3</v>
@@ -6529,28 +6529,28 @@
         <v>193.3</v>
       </c>
       <c r="M64">
-        <v>5.77221674</v>
+        <v>5.86531701</v>
       </c>
       <c r="N64">
-        <v>187.52778326</v>
+        <v>187.43468299</v>
       </c>
       <c r="O64">
-        <v>35.6302788194</v>
+        <v>35.6125897681</v>
       </c>
       <c r="P64">
-        <v>151.8975044406</v>
+        <v>151.8220932219</v>
       </c>
       <c r="Q64">
-        <v>264.7975044406</v>
+        <v>264.7220932219</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1831997861967875</v>
+        <v>0.1866093772933519</v>
       </c>
       <c r="T64">
-        <v>2.516525337005989</v>
+        <v>2.578973195338501</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>33.48800100669816</v>
+        <v>32.95644543516327</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09471355959854021</v>
+        <v>0.09455054044230117</v>
       </c>
       <c r="C65">
-        <v>63.71768402972377</v>
+        <v>61.77323509120198</v>
       </c>
       <c r="D65">
-        <v>-27.97561597027623</v>
+        <v>-28.06916490879804</v>
       </c>
       <c r="E65">
-        <v>108.9167</v>
+        <v>110.7676</v>
       </c>
       <c r="F65">
-        <v>116.6067</v>
+        <v>118.4576</v>
       </c>
       <c r="G65">
         <v>208.3</v>
@@ -6611,28 +6611,28 @@
         <v>193.3</v>
       </c>
       <c r="M65">
-        <v>5.86531701</v>
+        <v>5.95841728</v>
       </c>
       <c r="N65">
-        <v>187.43468299</v>
+        <v>187.34158272</v>
       </c>
       <c r="O65">
-        <v>35.6125897681</v>
+        <v>35.59490071680001</v>
       </c>
       <c r="P65">
-        <v>151.8220932219</v>
+        <v>151.7466820032</v>
       </c>
       <c r="Q65">
-        <v>264.7220932219</v>
+        <v>264.6466820032</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1866093772933519</v>
+        <v>0.1902083901175033</v>
       </c>
       <c r="T65">
-        <v>2.578973195338501</v>
+        <v>2.644890379133931</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>32.95644543516327</v>
+        <v>32.44150097523885</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09455054044230117</v>
+        <v>0.09438752128606213</v>
       </c>
       <c r="C66">
-        <v>61.77323509120198</v>
+        <v>59.82815840841081</v>
       </c>
       <c r="D66">
-        <v>-28.06916490879804</v>
+        <v>-28.1633415915892</v>
       </c>
       <c r="E66">
-        <v>110.7676</v>
+        <v>112.6185</v>
       </c>
       <c r="F66">
-        <v>118.4576</v>
+        <v>120.3085</v>
       </c>
       <c r="G66">
         <v>208.3</v>
@@ -6693,28 +6693,28 @@
         <v>193.3</v>
       </c>
       <c r="M66">
-        <v>5.95841728</v>
+        <v>6.05151755</v>
       </c>
       <c r="N66">
-        <v>187.34158272</v>
+        <v>187.24848245</v>
       </c>
       <c r="O66">
-        <v>35.59490071680001</v>
+        <v>35.5772116655</v>
       </c>
       <c r="P66">
-        <v>151.7466820032</v>
+        <v>151.6712707845</v>
       </c>
       <c r="Q66">
-        <v>264.6466820032</v>
+        <v>264.5712707845</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1902083901175033</v>
+        <v>0.1940130608173204</v>
       </c>
       <c r="T66">
-        <v>2.644890379133931</v>
+        <v>2.714574259146241</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>32.44150097523885</v>
+        <v>31.94240096023518</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09438752128606213</v>
+        <v>0.0942245021298231</v>
       </c>
       <c r="C67">
-        <v>59.82815840841081</v>
+        <v>57.88244764152211</v>
       </c>
       <c r="D67">
-        <v>-28.1633415915892</v>
+        <v>-28.25815235847791</v>
       </c>
       <c r="E67">
-        <v>112.6185</v>
+        <v>114.4694</v>
       </c>
       <c r="F67">
-        <v>120.3085</v>
+        <v>122.1594</v>
       </c>
       <c r="G67">
         <v>208.3</v>
@@ -6775,28 +6775,28 @@
         <v>193.3</v>
       </c>
       <c r="M67">
-        <v>6.05151755</v>
+        <v>6.14461782</v>
       </c>
       <c r="N67">
-        <v>187.24848245</v>
+        <v>187.15538218</v>
       </c>
       <c r="O67">
-        <v>35.5772116655</v>
+        <v>35.5595226142</v>
       </c>
       <c r="P67">
-        <v>151.6712707845</v>
+        <v>151.5958595658</v>
       </c>
       <c r="Q67">
-        <v>264.5712707845</v>
+        <v>264.4958595657999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1940130608173204</v>
+        <v>0.1980415356759503</v>
       </c>
       <c r="T67">
-        <v>2.714574259146241</v>
+        <v>2.788357190923982</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>31.94240096023518</v>
+        <v>31.4584251881104</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0942245021298231</v>
+        <v>0.09406148297358406</v>
       </c>
       <c r="C68">
-        <v>57.88244764152211</v>
+        <v>55.93609636504816</v>
       </c>
       <c r="D68">
-        <v>-28.25815235847791</v>
+        <v>-28.35360363495184</v>
       </c>
       <c r="E68">
-        <v>114.4694</v>
+        <v>116.3203</v>
       </c>
       <c r="F68">
-        <v>122.1594</v>
+        <v>124.0103</v>
       </c>
       <c r="G68">
         <v>208.3</v>
@@ -6857,28 +6857,28 @@
         <v>193.3</v>
       </c>
       <c r="M68">
-        <v>6.14461782</v>
+        <v>6.23771809</v>
       </c>
       <c r="N68">
-        <v>187.15538218</v>
+        <v>187.06228191</v>
       </c>
       <c r="O68">
-        <v>35.5595226142</v>
+        <v>35.5418335629</v>
       </c>
       <c r="P68">
-        <v>151.5958595658</v>
+        <v>151.5204483471</v>
       </c>
       <c r="Q68">
-        <v>264.4958595657999</v>
+        <v>264.4204483471</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1980415356759503</v>
+        <v>0.2023141605260123</v>
       </c>
       <c r="T68">
-        <v>2.788357190923982</v>
+        <v>2.866611815536738</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>31.4584251881104</v>
+        <v>30.9888964539595</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09406148297358406</v>
+        <v>0.09389846381734501</v>
       </c>
       <c r="C69">
-        <v>55.93609636504816</v>
+        <v>53.98909806639024</v>
       </c>
       <c r="D69">
-        <v>-28.35360363495184</v>
+        <v>-28.44970193360976</v>
       </c>
       <c r="E69">
-        <v>116.3203</v>
+        <v>118.1712</v>
       </c>
       <c r="F69">
-        <v>124.0103</v>
+        <v>125.8612</v>
       </c>
       <c r="G69">
         <v>208.3</v>
@@ -6939,28 +6939,28 @@
         <v>193.3</v>
       </c>
       <c r="M69">
-        <v>6.23771809</v>
+        <v>6.33081836</v>
       </c>
       <c r="N69">
-        <v>187.06228191</v>
+        <v>186.96918164</v>
       </c>
       <c r="O69">
-        <v>35.5418335629</v>
+        <v>35.52414451160001</v>
       </c>
       <c r="P69">
-        <v>151.5204483471</v>
+        <v>151.4450371284</v>
       </c>
       <c r="Q69">
-        <v>264.4204483471</v>
+        <v>264.3450371284</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2023141605260123</v>
+        <v>0.2068538244292032</v>
       </c>
       <c r="T69">
-        <v>2.866611815536738</v>
+        <v>2.949757354187791</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>30.9888964539595</v>
+        <v>30.53317738846009</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09389846381734501</v>
+        <v>0.09373544466110598</v>
       </c>
       <c r="C70">
-        <v>53.98909806639024</v>
+        <v>52.04144614435724</v>
       </c>
       <c r="D70">
-        <v>-28.44970193360976</v>
+        <v>-28.54645385564277</v>
       </c>
       <c r="E70">
-        <v>118.1712</v>
+        <v>120.0221</v>
       </c>
       <c r="F70">
-        <v>125.8612</v>
+        <v>127.7121</v>
       </c>
       <c r="G70">
         <v>208.3</v>
@@ -7021,28 +7021,28 @@
         <v>193.3</v>
       </c>
       <c r="M70">
-        <v>6.33081836</v>
+        <v>6.42391863</v>
       </c>
       <c r="N70">
-        <v>186.96918164</v>
+        <v>186.87608137</v>
       </c>
       <c r="O70">
-        <v>35.52414451160001</v>
+        <v>35.5064554603</v>
       </c>
       <c r="P70">
-        <v>151.4450371284</v>
+        <v>151.3696259097</v>
       </c>
       <c r="Q70">
-        <v>264.3450371284</v>
+        <v>264.2696259097</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2068538244292032</v>
+        <v>0.2116863698745354</v>
       </c>
       <c r="T70">
-        <v>2.949757354187791</v>
+        <v>3.038267121138912</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>30.53317738846009</v>
+        <v>30.09066757123603</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09373544466110598</v>
+        <v>0.09357242550486693</v>
       </c>
       <c r="C71">
-        <v>52.04144614435724</v>
+        <v>50.09313390765408</v>
       </c>
       <c r="D71">
-        <v>-28.54645385564277</v>
+        <v>-28.64386609234592</v>
       </c>
       <c r="E71">
-        <v>120.0221</v>
+        <v>121.873</v>
       </c>
       <c r="F71">
-        <v>127.7121</v>
+        <v>129.563</v>
       </c>
       <c r="G71">
         <v>208.3</v>
@@ -7103,28 +7103,28 @@
         <v>193.3</v>
       </c>
       <c r="M71">
-        <v>6.42391863</v>
+        <v>6.517018900000001</v>
       </c>
       <c r="N71">
-        <v>186.87608137</v>
+        <v>186.7829811</v>
       </c>
       <c r="O71">
-        <v>35.5064554603</v>
+        <v>35.488766409</v>
       </c>
       <c r="P71">
-        <v>151.3696259097</v>
+        <v>151.294214691</v>
       </c>
       <c r="Q71">
-        <v>264.2696259097</v>
+        <v>264.194214691</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2116863698745354</v>
+        <v>0.2168410850162231</v>
       </c>
       <c r="T71">
-        <v>3.038267121138912</v>
+        <v>3.132677539220106</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>30.09066757123603</v>
+        <v>29.66080089164694</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09357242550486693</v>
+        <v>0.0934094063486279</v>
       </c>
       <c r="C72">
-        <v>50.09313390765408</v>
+        <v>48.14415457333925</v>
       </c>
       <c r="D72">
-        <v>-28.64386609234592</v>
+        <v>-28.74194542666076</v>
       </c>
       <c r="E72">
-        <v>121.873</v>
+        <v>123.7239</v>
       </c>
       <c r="F72">
-        <v>129.563</v>
+        <v>131.4139</v>
       </c>
       <c r="G72">
         <v>208.3</v>
@@ -7185,28 +7185,28 @@
         <v>193.3</v>
       </c>
       <c r="M72">
-        <v>6.517018900000001</v>
+        <v>6.61011917</v>
       </c>
       <c r="N72">
-        <v>186.7829811</v>
+        <v>186.68988083</v>
       </c>
       <c r="O72">
-        <v>35.488766409</v>
+        <v>35.4710773577</v>
       </c>
       <c r="P72">
-        <v>151.294214691</v>
+        <v>151.2188034723</v>
       </c>
       <c r="Q72">
-        <v>264.194214691</v>
+        <v>264.1188034723</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2168410850162231</v>
+        <v>0.2223512977538894</v>
       </c>
       <c r="T72">
-        <v>3.132677539220106</v>
+        <v>3.233599020617247</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>29.66080089164694</v>
+        <v>29.24304313260967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0934094063486279</v>
+        <v>0.09324638719238887</v>
       </c>
       <c r="C73">
-        <v>48.14415457333928</v>
+        <v>46.19450126525018</v>
       </c>
       <c r="D73">
-        <v>-28.74194542666076</v>
+        <v>-28.84069873474981</v>
       </c>
       <c r="E73">
-        <v>123.7239</v>
+        <v>125.5748</v>
       </c>
       <c r="F73">
-        <v>131.4139</v>
+        <v>133.2648</v>
       </c>
       <c r="G73">
         <v>208.3</v>
@@ -7267,28 +7267,28 @@
         <v>193.3</v>
       </c>
       <c r="M73">
-        <v>6.610119169999999</v>
+        <v>6.70321944</v>
       </c>
       <c r="N73">
-        <v>186.68988083</v>
+        <v>186.59678056</v>
       </c>
       <c r="O73">
-        <v>35.4710773577</v>
+        <v>35.4533883064</v>
       </c>
       <c r="P73">
-        <v>151.2188034723</v>
+        <v>151.1433922536</v>
       </c>
       <c r="Q73">
-        <v>264.1188034723</v>
+        <v>264.0433922536</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2223512977538893</v>
+        <v>0.2282550971156745</v>
       </c>
       <c r="T73">
-        <v>3.233599020617246</v>
+        <v>3.341729179257038</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>29.24304313260967</v>
+        <v>28.83688975576787</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09324638719238887</v>
+        <v>0.09308336803614981</v>
       </c>
       <c r="C74">
-        <v>46.19450126525018</v>
+        <v>44.24416701239642</v>
       </c>
       <c r="D74">
-        <v>-28.84069873474981</v>
+        <v>-28.94013298760358</v>
       </c>
       <c r="E74">
-        <v>125.5748</v>
+        <v>127.4257</v>
       </c>
       <c r="F74">
-        <v>133.2648</v>
+        <v>135.1157</v>
       </c>
       <c r="G74">
         <v>208.3</v>
@@ -7349,28 +7349,28 @@
         <v>193.3</v>
       </c>
       <c r="M74">
-        <v>6.70321944</v>
+        <v>6.79631971</v>
       </c>
       <c r="N74">
-        <v>186.59678056</v>
+        <v>186.50368029</v>
       </c>
       <c r="O74">
-        <v>35.4533883064</v>
+        <v>35.4356992551</v>
       </c>
       <c r="P74">
-        <v>151.1433922536</v>
+        <v>151.0679810349</v>
       </c>
       <c r="Q74">
-        <v>264.0433922536</v>
+        <v>263.9679810349</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2282550971156745</v>
+        <v>0.234596214948703</v>
       </c>
       <c r="T74">
-        <v>3.341729179257038</v>
+        <v>3.457868979277556</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>28.83688975576787</v>
+        <v>28.44186386870255</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09308336803614981</v>
+        <v>0.09292034887991077</v>
       </c>
       <c r="C75">
-        <v>44.24416701239642</v>
+        <v>42.29314474731925</v>
       </c>
       <c r="D75">
-        <v>-28.94013298760358</v>
+        <v>-29.04025525268077</v>
       </c>
       <c r="E75">
-        <v>127.4257</v>
+        <v>129.2766</v>
       </c>
       <c r="F75">
-        <v>135.1157</v>
+        <v>136.9666</v>
       </c>
       <c r="G75">
         <v>208.3</v>
@@ -7431,28 +7431,28 @@
         <v>193.3</v>
       </c>
       <c r="M75">
-        <v>6.79631971</v>
+        <v>6.88941998</v>
       </c>
       <c r="N75">
-        <v>186.50368029</v>
+        <v>186.41058002</v>
       </c>
       <c r="O75">
-        <v>35.4356992551</v>
+        <v>35.4180102038</v>
       </c>
       <c r="P75">
-        <v>151.0679810349</v>
+        <v>150.9925698162</v>
       </c>
       <c r="Q75">
-        <v>263.9679810349</v>
+        <v>263.8925698162</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.234596214948703</v>
+        <v>0.2414251110765799</v>
       </c>
       <c r="T75">
-        <v>3.457868979277556</v>
+        <v>3.582942610068883</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>28.44186386870255</v>
+        <v>28.05751435696333</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09292034887991077</v>
+        <v>0.09275732972367173</v>
       </c>
       <c r="C76">
-        <v>42.29314474731925</v>
+        <v>40.34142730441698</v>
       </c>
       <c r="D76">
-        <v>-29.04025525268077</v>
+        <v>-29.14107269558302</v>
       </c>
       <c r="E76">
-        <v>129.2766</v>
+        <v>131.1275</v>
       </c>
       <c r="F76">
-        <v>136.9666</v>
+        <v>138.8175</v>
       </c>
       <c r="G76">
         <v>208.3</v>
@@ -7513,28 +7513,28 @@
         <v>193.3</v>
       </c>
       <c r="M76">
-        <v>6.88941998</v>
+        <v>6.982520249999999</v>
       </c>
       <c r="N76">
-        <v>186.41058002</v>
+        <v>186.31747975</v>
       </c>
       <c r="O76">
-        <v>35.4180102038</v>
+        <v>35.40032115250001</v>
       </c>
       <c r="P76">
-        <v>150.9925698162</v>
+        <v>150.9171585975</v>
       </c>
       <c r="Q76">
-        <v>263.8925698162</v>
+        <v>263.8171585975</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2414251110765799</v>
+        <v>0.2488003188946869</v>
       </c>
       <c r="T76">
-        <v>3.582942610068883</v>
+        <v>3.718022131323517</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>28.05751435696333</v>
+        <v>27.68341416553715</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09275732972367173</v>
+        <v>0.0925943105674327</v>
       </c>
       <c r="C77">
-        <v>40.34142730441698</v>
+        <v>38.38900741823576</v>
       </c>
       <c r="D77">
-        <v>-29.14107269558302</v>
+        <v>-29.24259258176424</v>
       </c>
       <c r="E77">
-        <v>131.1275</v>
+        <v>132.9784</v>
       </c>
       <c r="F77">
-        <v>138.8175</v>
+        <v>140.6684</v>
       </c>
       <c r="G77">
         <v>208.3</v>
@@ -7595,28 +7595,28 @@
         <v>193.3</v>
       </c>
       <c r="M77">
-        <v>6.982520249999999</v>
+        <v>7.075620519999999</v>
       </c>
       <c r="N77">
-        <v>186.31747975</v>
+        <v>186.22437948</v>
       </c>
       <c r="O77">
-        <v>35.40032115250001</v>
+        <v>35.3826321012</v>
       </c>
       <c r="P77">
-        <v>150.9171585975</v>
+        <v>150.8417473788</v>
       </c>
       <c r="Q77">
-        <v>263.8171585975</v>
+        <v>263.7417473788</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2488003188946869</v>
+        <v>0.2567901273643029</v>
       </c>
       <c r="T77">
-        <v>3.718022131323517</v>
+        <v>3.86435827934937</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>27.68341416553715</v>
+        <v>27.31915871599061</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0925943105674327</v>
+        <v>0.09243129141119366</v>
       </c>
       <c r="C78">
-        <v>38.38900741823576</v>
+        <v>36.43587772172393</v>
       </c>
       <c r="D78">
-        <v>-29.24259258176424</v>
+        <v>-29.34482227827607</v>
       </c>
       <c r="E78">
-        <v>132.9784</v>
+        <v>134.8293</v>
       </c>
       <c r="F78">
-        <v>140.6684</v>
+        <v>142.5193</v>
       </c>
       <c r="G78">
         <v>208.3</v>
@@ -7677,28 +7677,28 @@
         <v>193.3</v>
       </c>
       <c r="M78">
-        <v>7.075620519999999</v>
+        <v>7.16872079</v>
       </c>
       <c r="N78">
-        <v>186.22437948</v>
+        <v>186.13127921</v>
       </c>
       <c r="O78">
-        <v>35.3826321012</v>
+        <v>35.3649430499</v>
       </c>
       <c r="P78">
-        <v>150.8417473788</v>
+        <v>150.7663361601</v>
       </c>
       <c r="Q78">
-        <v>263.7417473788</v>
+        <v>263.6663361600999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2567901273643029</v>
+        <v>0.2654747017877985</v>
       </c>
       <c r="T78">
-        <v>3.86435827934937</v>
+        <v>4.023419309812254</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>27.31915871599061</v>
+        <v>26.96436444695177</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09243129141119366</v>
+        <v>0.09226827225495463</v>
       </c>
       <c r="C79">
-        <v>36.43587772172393</v>
+        <v>34.48203074445001</v>
       </c>
       <c r="D79">
-        <v>-29.34482227827607</v>
+        <v>-29.44776925554999</v>
       </c>
       <c r="E79">
-        <v>134.8293</v>
+        <v>136.6802</v>
       </c>
       <c r="F79">
-        <v>142.5193</v>
+        <v>144.3702</v>
       </c>
       <c r="G79">
         <v>208.3</v>
@@ -7759,28 +7759,28 @@
         <v>193.3</v>
       </c>
       <c r="M79">
-        <v>7.16872079</v>
+        <v>7.26182106</v>
       </c>
       <c r="N79">
-        <v>186.13127921</v>
+        <v>186.03817894</v>
       </c>
       <c r="O79">
-        <v>35.3649430499</v>
+        <v>35.3472539986</v>
       </c>
       <c r="P79">
-        <v>150.7663361601</v>
+        <v>150.6909249414</v>
       </c>
       <c r="Q79">
-        <v>263.6663361600999</v>
+        <v>263.5909249414</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2654747017877985</v>
+        <v>0.2749487829770665</v>
       </c>
       <c r="T79">
-        <v>4.023419309812254</v>
+        <v>4.196940433953581</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>26.96436444695177</v>
+        <v>26.61866746686265</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09226827225495463</v>
+        <v>0.09210525309871559</v>
       </c>
       <c r="C80">
-        <v>34.48203074445001</v>
+        <v>32.52745891078294</v>
       </c>
       <c r="D80">
-        <v>-29.44776925554999</v>
+        <v>-29.55144108921706</v>
       </c>
       <c r="E80">
-        <v>136.6802</v>
+        <v>138.5311</v>
       </c>
       <c r="F80">
-        <v>144.3702</v>
+        <v>146.2211</v>
       </c>
       <c r="G80">
         <v>208.3</v>
@@ -7841,28 +7841,28 @@
         <v>193.3</v>
       </c>
       <c r="M80">
-        <v>7.26182106</v>
+        <v>7.35492133</v>
       </c>
       <c r="N80">
-        <v>186.03817894</v>
+        <v>185.94507867</v>
       </c>
       <c r="O80">
-        <v>35.3472539986</v>
+        <v>35.3295649473</v>
       </c>
       <c r="P80">
-        <v>150.6909249414</v>
+        <v>150.6155137227</v>
       </c>
       <c r="Q80">
-        <v>263.5909249414</v>
+        <v>263.5155137227</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2749487829770665</v>
+        <v>0.2853251576129314</v>
       </c>
       <c r="T80">
-        <v>4.196940433953581</v>
+        <v>4.386987379441702</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>26.61866746686265</v>
+        <v>26.28172230905426</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09210525309871559</v>
+        <v>0.09194223394247654</v>
       </c>
       <c r="C81">
-        <v>32.52745891078294</v>
+        <v>30.57215453803371</v>
       </c>
       <c r="D81">
-        <v>-29.55144108921706</v>
+        <v>-29.65584546196628</v>
       </c>
       <c r="E81">
-        <v>138.5311</v>
+        <v>140.382</v>
       </c>
       <c r="F81">
-        <v>146.2211</v>
+        <v>148.072</v>
       </c>
       <c r="G81">
         <v>208.3</v>
@@ -7923,28 +7923,28 @@
         <v>193.3</v>
       </c>
       <c r="M81">
-        <v>7.35492133</v>
+        <v>7.4480216</v>
       </c>
       <c r="N81">
-        <v>185.94507867</v>
+        <v>185.8519784</v>
       </c>
       <c r="O81">
-        <v>35.3295649473</v>
+        <v>35.311875896</v>
       </c>
       <c r="P81">
-        <v>150.6155137227</v>
+        <v>150.540102504</v>
       </c>
       <c r="Q81">
-        <v>263.5155137227</v>
+        <v>263.440102504</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2853251576129314</v>
+        <v>0.2967391697123827</v>
       </c>
       <c r="T81">
-        <v>4.386987379441702</v>
+        <v>4.596039019478634</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>26.28172230905426</v>
+        <v>25.95320078019108</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09194223394247654</v>
+        <v>0.09177921478623752</v>
       </c>
       <c r="C82">
-        <v>30.57215453803371</v>
+        <v>28.61610983455759</v>
       </c>
       <c r="D82">
-        <v>-29.65584546196628</v>
+        <v>-29.76099016544242</v>
       </c>
       <c r="E82">
-        <v>140.382</v>
+        <v>142.2329</v>
       </c>
       <c r="F82">
-        <v>148.072</v>
+        <v>149.9229</v>
       </c>
       <c r="G82">
         <v>208.3</v>
@@ -8005,28 +8005,28 @@
         <v>193.3</v>
       </c>
       <c r="M82">
-        <v>7.4480216</v>
+        <v>7.54112187</v>
       </c>
       <c r="N82">
-        <v>185.8519784</v>
+        <v>185.75887813</v>
       </c>
       <c r="O82">
-        <v>35.311875896</v>
+        <v>35.2941868447</v>
       </c>
       <c r="P82">
-        <v>150.540102504</v>
+        <v>150.4646912853</v>
       </c>
       <c r="Q82">
-        <v>263.440102504</v>
+        <v>263.3646912853</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2967391697123827</v>
+        <v>0.3093546567696712</v>
       </c>
       <c r="T82">
-        <v>4.596039019478634</v>
+        <v>4.827096095308929</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>25.95320078019108</v>
+        <v>25.63279089401588</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09177921478623752</v>
+        <v>0.09161619562999845</v>
       </c>
       <c r="C83">
-        <v>28.61610983455759</v>
+        <v>26.6593168978155</v>
       </c>
       <c r="D83">
-        <v>-29.76099016544242</v>
+        <v>-29.86688310218448</v>
       </c>
       <c r="E83">
-        <v>142.2329</v>
+        <v>144.0838</v>
       </c>
       <c r="F83">
-        <v>149.9229</v>
+        <v>151.7738</v>
       </c>
       <c r="G83">
         <v>208.3</v>
@@ -8087,28 +8087,28 @@
         <v>193.3</v>
       </c>
       <c r="M83">
-        <v>7.54112187</v>
+        <v>7.63422214</v>
       </c>
       <c r="N83">
-        <v>185.75887813</v>
+        <v>185.66577786</v>
       </c>
       <c r="O83">
-        <v>35.2941868447</v>
+        <v>35.2764977934</v>
       </c>
       <c r="P83">
-        <v>150.4646912853</v>
+        <v>150.3892800666</v>
       </c>
       <c r="Q83">
-        <v>263.3646912853</v>
+        <v>263.2892800666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3093546567696712</v>
+        <v>0.3233718646111026</v>
       </c>
       <c r="T83">
-        <v>4.827096095308929</v>
+        <v>5.08382617956481</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>25.63279089401588</v>
+        <v>25.32019588311325</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09161619562999845</v>
+        <v>0.09145317647375942</v>
       </c>
       <c r="C84">
-        <v>26.6593168978155</v>
+        <v>24.70176771239448</v>
       </c>
       <c r="D84">
-        <v>-29.86688310218448</v>
+        <v>-29.97353228760549</v>
       </c>
       <c r="E84">
-        <v>144.0838</v>
+        <v>145.9347</v>
       </c>
       <c r="F84">
-        <v>151.7738</v>
+        <v>153.6247</v>
       </c>
       <c r="G84">
         <v>208.3</v>
@@ -8169,28 +8169,28 @@
         <v>193.3</v>
       </c>
       <c r="M84">
-        <v>7.63422214</v>
+        <v>7.72732241</v>
       </c>
       <c r="N84">
-        <v>185.66577786</v>
+        <v>185.57267759</v>
       </c>
       <c r="O84">
-        <v>35.2764977934</v>
+        <v>35.2588087421</v>
       </c>
       <c r="P84">
-        <v>150.3892800666</v>
+        <v>150.3138688479</v>
       </c>
       <c r="Q84">
-        <v>263.2892800666</v>
+        <v>263.2138688479</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3233718646111026</v>
+        <v>0.3390381557279967</v>
       </c>
       <c r="T84">
-        <v>5.08382617956481</v>
+        <v>5.370759803144915</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>25.32019588311325</v>
+        <v>25.01513328211188</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09145317647375942</v>
+        <v>0.09129015731752038</v>
       </c>
       <c r="C85">
-        <v>24.70176771239448</v>
+        <v>22.74345414798489</v>
       </c>
       <c r="D85">
-        <v>-29.97353228760549</v>
+        <v>-30.08094585201511</v>
       </c>
       <c r="E85">
-        <v>145.9347</v>
+        <v>147.7856</v>
       </c>
       <c r="F85">
-        <v>153.6247</v>
+        <v>155.4756</v>
       </c>
       <c r="G85">
         <v>208.3</v>
@@ -8251,28 +8251,28 @@
         <v>193.3</v>
       </c>
       <c r="M85">
-        <v>7.72732241</v>
+        <v>7.82042268</v>
       </c>
       <c r="N85">
-        <v>185.57267759</v>
+        <v>185.47957732</v>
       </c>
       <c r="O85">
-        <v>35.2588087421</v>
+        <v>35.2411196908</v>
       </c>
       <c r="P85">
-        <v>150.3138688479</v>
+        <v>150.2384576292</v>
       </c>
       <c r="Q85">
-        <v>263.2138688479</v>
+        <v>263.1384576292</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3390381557279967</v>
+        <v>0.3566627332345025</v>
       </c>
       <c r="T85">
-        <v>5.370759803144915</v>
+        <v>5.693560129672531</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>25.01513328211188</v>
+        <v>24.71733407637246</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09129015731752038</v>
+        <v>0.09112713816128135</v>
       </c>
       <c r="C86">
-        <v>22.74345414798492</v>
+        <v>20.78436795731432</v>
       </c>
       <c r="D86">
-        <v>-30.08094585201511</v>
+        <v>-30.18913204268567</v>
       </c>
       <c r="E86">
-        <v>147.7856</v>
+        <v>149.6365</v>
       </c>
       <c r="F86">
-        <v>155.4756</v>
+        <v>157.3265</v>
       </c>
       <c r="G86">
         <v>208.3</v>
@@ -8333,28 +8333,28 @@
         <v>193.3</v>
       </c>
       <c r="M86">
-        <v>7.820422679999999</v>
+        <v>7.91352295</v>
       </c>
       <c r="N86">
-        <v>185.47957732</v>
+        <v>185.38647705</v>
       </c>
       <c r="O86">
-        <v>35.2411196908</v>
+        <v>35.2234306395</v>
       </c>
       <c r="P86">
-        <v>150.2384576292</v>
+        <v>150.1630464105</v>
       </c>
       <c r="Q86">
-        <v>263.1384576292</v>
+        <v>263.0630464105</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3566627332345023</v>
+        <v>0.3766372544085422</v>
       </c>
       <c r="T86">
-        <v>5.693560129672528</v>
+        <v>6.059400499737159</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>24.71733407637246</v>
+        <v>24.42654191076808</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09112713816128135</v>
+        <v>0.09096411900504231</v>
       </c>
       <c r="C87">
-        <v>20.78436795731432</v>
+        <v>18.82450077403686</v>
       </c>
       <c r="D87">
-        <v>-30.18913204268567</v>
+        <v>-30.29809922596313</v>
       </c>
       <c r="E87">
-        <v>149.6365</v>
+        <v>151.4874</v>
       </c>
       <c r="F87">
-        <v>157.3265</v>
+        <v>159.1774</v>
       </c>
       <c r="G87">
         <v>208.3</v>
@@ -8415,28 +8415,28 @@
         <v>193.3</v>
       </c>
       <c r="M87">
-        <v>7.91352295</v>
+        <v>8.00662322</v>
       </c>
       <c r="N87">
-        <v>185.38647705</v>
+        <v>185.29337678</v>
       </c>
       <c r="O87">
-        <v>35.2234306395</v>
+        <v>35.20574158820001</v>
       </c>
       <c r="P87">
-        <v>150.1630464105</v>
+        <v>150.0876351918</v>
       </c>
       <c r="Q87">
-        <v>263.0630464105</v>
+        <v>262.9876351918</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3766372544085422</v>
+        <v>0.399465278607445</v>
       </c>
       <c r="T87">
-        <v>6.059400499737159</v>
+        <v>6.477503779811025</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>24.42654191076808</v>
+        <v>24.14251235366612</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09096411900504231</v>
+        <v>0.09080109984880325</v>
       </c>
       <c r="C88">
-        <v>18.82450077403686</v>
+        <v>16.86384411057622</v>
       </c>
       <c r="D88">
-        <v>-30.29809922596313</v>
+        <v>-30.40785588942378</v>
       </c>
       <c r="E88">
-        <v>151.4874</v>
+        <v>153.3383</v>
       </c>
       <c r="F88">
-        <v>159.1774</v>
+        <v>161.0283</v>
       </c>
       <c r="G88">
         <v>208.3</v>
@@ -8497,28 +8497,28 @@
         <v>193.3</v>
       </c>
       <c r="M88">
-        <v>8.00662322</v>
+        <v>8.099723489999999</v>
       </c>
       <c r="N88">
-        <v>185.29337678</v>
+        <v>185.20027651</v>
       </c>
       <c r="O88">
-        <v>35.20574158820001</v>
+        <v>35.1880525369</v>
       </c>
       <c r="P88">
-        <v>150.0876351918</v>
+        <v>150.0122239731</v>
       </c>
       <c r="Q88">
-        <v>262.9876351918</v>
+        <v>262.9122239731</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.399465278607445</v>
+        <v>0.4258053065292558</v>
       </c>
       <c r="T88">
-        <v>6.477503779811025</v>
+        <v>6.959930641434714</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>24.14251235366612</v>
+        <v>23.86501221166996</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09080109984880325</v>
+        <v>0.09063808069256424</v>
       </c>
       <c r="C89">
-        <v>16.86384411057622</v>
+        <v>14.90238935592205</v>
       </c>
       <c r="D89">
-        <v>-30.40785588942378</v>
+        <v>-30.51841064407797</v>
       </c>
       <c r="E89">
-        <v>153.3383</v>
+        <v>155.1892</v>
       </c>
       <c r="F89">
-        <v>161.0283</v>
+        <v>162.8792</v>
       </c>
       <c r="G89">
         <v>208.3</v>
@@ -8579,28 +8579,28 @@
         <v>193.3</v>
       </c>
       <c r="M89">
-        <v>8.099723489999999</v>
+        <v>8.19282376</v>
       </c>
       <c r="N89">
-        <v>185.20027651</v>
+        <v>185.10717624</v>
       </c>
       <c r="O89">
-        <v>35.1880525369</v>
+        <v>35.1703634856</v>
       </c>
       <c r="P89">
-        <v>150.0122239731</v>
+        <v>149.9368127544</v>
       </c>
       <c r="Q89">
-        <v>262.9122239731</v>
+        <v>262.8368127543999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4258053065292558</v>
+        <v>0.4565353391047019</v>
       </c>
       <c r="T89">
-        <v>6.959930641434714</v>
+        <v>7.522761979995688</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>23.86501221166996</v>
+        <v>23.5938188910828</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09063808069256424</v>
+        <v>0.09047506153632517</v>
       </c>
       <c r="C90">
-        <v>14.90238935592205</v>
+        <v>12.94012777337761</v>
       </c>
       <c r="D90">
-        <v>-30.51841064407797</v>
+        <v>-30.6297722266224</v>
       </c>
       <c r="E90">
-        <v>155.1892</v>
+        <v>157.0401</v>
       </c>
       <c r="F90">
-        <v>162.8792</v>
+        <v>164.7301</v>
       </c>
       <c r="G90">
         <v>208.3</v>
@@ -8661,28 +8661,28 @@
         <v>193.3</v>
       </c>
       <c r="M90">
-        <v>8.19282376</v>
+        <v>8.285924029999999</v>
       </c>
       <c r="N90">
-        <v>185.10717624</v>
+        <v>185.01407597</v>
       </c>
       <c r="O90">
-        <v>35.1703634856</v>
+        <v>35.1526744343</v>
       </c>
       <c r="P90">
-        <v>149.9368127544</v>
+        <v>149.8614015357</v>
       </c>
       <c r="Q90">
-        <v>262.8368127543999</v>
+        <v>262.7614015357</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4565353391047019</v>
+        <v>0.4928526503302289</v>
       </c>
       <c r="T90">
-        <v>7.522761979995688</v>
+        <v>8.187926289204109</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>23.5938188910828</v>
+        <v>23.32871980241895</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09047506153632517</v>
+        <v>0.09031204238008614</v>
       </c>
       <c r="C91">
-        <v>12.94012777337761</v>
+        <v>10.97705049825862</v>
       </c>
       <c r="D91">
-        <v>-30.6297722266224</v>
+        <v>-30.74194950174136</v>
       </c>
       <c r="E91">
-        <v>157.0401</v>
+        <v>158.891</v>
       </c>
       <c r="F91">
-        <v>164.7301</v>
+        <v>166.581</v>
       </c>
       <c r="G91">
         <v>208.3</v>
@@ -8743,28 +8743,28 @@
         <v>193.3</v>
       </c>
       <c r="M91">
-        <v>8.285924029999999</v>
+        <v>8.379024300000001</v>
       </c>
       <c r="N91">
-        <v>185.01407597</v>
+        <v>184.9209757</v>
       </c>
       <c r="O91">
-        <v>35.1526744343</v>
+        <v>35.134985383</v>
       </c>
       <c r="P91">
-        <v>149.8614015357</v>
+        <v>149.785990317</v>
       </c>
       <c r="Q91">
-        <v>262.7614015357</v>
+        <v>262.685990317</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4928526503302289</v>
+        <v>0.5364334238008615</v>
       </c>
       <c r="T91">
-        <v>8.187926289204109</v>
+        <v>8.986123460254216</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>23.32871980241895</v>
+        <v>23.06951180461429</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09031204238008614</v>
+        <v>0.0901490232238471</v>
       </c>
       <c r="C92">
-        <v>10.97705049825862</v>
+        <v>9.013148535540722</v>
       </c>
       <c r="D92">
-        <v>-30.74194950174136</v>
+        <v>-30.85495146445927</v>
       </c>
       <c r="E92">
-        <v>158.891</v>
+        <v>160.7419</v>
       </c>
       <c r="F92">
-        <v>166.581</v>
+        <v>168.4319</v>
       </c>
       <c r="G92">
         <v>208.3</v>
@@ -8825,28 +8825,28 @@
         <v>193.3</v>
       </c>
       <c r="M92">
-        <v>8.379024300000001</v>
+        <v>8.47212457</v>
       </c>
       <c r="N92">
-        <v>184.9209757</v>
+        <v>184.82787543</v>
       </c>
       <c r="O92">
-        <v>35.134985383</v>
+        <v>35.1172963317</v>
       </c>
       <c r="P92">
-        <v>149.785990317</v>
+        <v>149.7105790983</v>
       </c>
       <c r="Q92">
-        <v>262.685990317</v>
+        <v>262.6105790983</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5364334238008615</v>
+        <v>0.5896988135983012</v>
       </c>
       <c r="T92">
-        <v>8.986123460254216</v>
+        <v>9.961697780426569</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>23.06951180461429</v>
+        <v>22.81600068588227</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0901490232238471</v>
+        <v>0.08998600406760807</v>
       </c>
       <c r="C93">
-        <v>9.013148535540722</v>
+        <v>7.048412757455054</v>
       </c>
       <c r="D93">
-        <v>-30.85495146445927</v>
+        <v>-30.96878724254494</v>
       </c>
       <c r="E93">
-        <v>160.7419</v>
+        <v>162.5928</v>
       </c>
       <c r="F93">
-        <v>168.4319</v>
+        <v>170.2828</v>
       </c>
       <c r="G93">
         <v>208.3</v>
@@ -8907,28 +8907,28 @@
         <v>193.3</v>
       </c>
       <c r="M93">
-        <v>8.47212457</v>
+        <v>8.565224840000001</v>
       </c>
       <c r="N93">
-        <v>184.82787543</v>
+        <v>184.73477516</v>
       </c>
       <c r="O93">
-        <v>35.1172963317</v>
+        <v>35.0996072804</v>
       </c>
       <c r="P93">
-        <v>149.7105790983</v>
+        <v>149.6351678796</v>
       </c>
       <c r="Q93">
-        <v>262.6105790983</v>
+        <v>262.5351678796</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5896988135983012</v>
+        <v>0.6562805508451012</v>
       </c>
       <c r="T93">
-        <v>9.961697780426569</v>
+        <v>11.18116568064201</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>22.81600068588227</v>
+        <v>22.56800067842702</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08998600406760807</v>
+        <v>0.08982298491136903</v>
       </c>
       <c r="C94">
-        <v>7.048412757455054</v>
+        <v>5.082833901030625</v>
       </c>
       <c r="D94">
-        <v>-30.96878724254494</v>
+        <v>-31.08346609896937</v>
       </c>
       <c r="E94">
-        <v>162.5928</v>
+        <v>164.4437</v>
       </c>
       <c r="F94">
-        <v>170.2828</v>
+        <v>172.1337</v>
       </c>
       <c r="G94">
         <v>208.3</v>
@@ -8989,28 +8989,28 @@
         <v>193.3</v>
       </c>
       <c r="M94">
-        <v>8.565224840000001</v>
+        <v>8.65832511</v>
       </c>
       <c r="N94">
-        <v>184.73477516</v>
+        <v>184.64167489</v>
       </c>
       <c r="O94">
-        <v>35.0996072804</v>
+        <v>35.0819182291</v>
       </c>
       <c r="P94">
-        <v>149.6351678796</v>
+        <v>149.5597566609</v>
       </c>
       <c r="Q94">
-        <v>262.5351678796</v>
+        <v>262.4597566609</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6562805508451012</v>
+        <v>0.7418856415909865</v>
       </c>
       <c r="T94">
-        <v>11.18116568064201</v>
+        <v>12.74905298091901</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>22.56800067842702</v>
+        <v>22.32533400446545</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08982298491136903</v>
+        <v>0.08965996575512999</v>
       </c>
       <c r="C95">
-        <v>5.082833901030625</v>
+        <v>3.116402565581609</v>
       </c>
       <c r="D95">
-        <v>-31.08346609896937</v>
+        <v>-31.19899743441839</v>
       </c>
       <c r="E95">
-        <v>164.4437</v>
+        <v>166.2946</v>
       </c>
       <c r="F95">
-        <v>172.1337</v>
+        <v>173.9846</v>
       </c>
       <c r="G95">
         <v>208.3</v>
@@ -9071,28 +9071,28 @@
         <v>193.3</v>
       </c>
       <c r="M95">
-        <v>8.65832511</v>
+        <v>8.751425379999999</v>
       </c>
       <c r="N95">
-        <v>184.64167489</v>
+        <v>184.54857462</v>
       </c>
       <c r="O95">
-        <v>35.0819182291</v>
+        <v>35.0642291778</v>
       </c>
       <c r="P95">
-        <v>149.5597566609</v>
+        <v>149.4843454422</v>
       </c>
       <c r="Q95">
-        <v>262.4597566609</v>
+        <v>262.3843454422</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7418856415909865</v>
+        <v>0.8560257625855004</v>
       </c>
       <c r="T95">
-        <v>12.74905298091901</v>
+        <v>14.83956938128834</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>22.32533400446545</v>
+        <v>22.08783045122645</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08965996575512999</v>
+        <v>0.08949694659889094</v>
       </c>
       <c r="C96">
-        <v>3.116402565581609</v>
+        <v>1.149109210138477</v>
       </c>
       <c r="D96">
-        <v>-31.19899743441839</v>
+        <v>-31.3153907898615</v>
       </c>
       <c r="E96">
-        <v>166.2946</v>
+        <v>168.1455</v>
       </c>
       <c r="F96">
-        <v>173.9846</v>
+        <v>175.8355</v>
       </c>
       <c r="G96">
         <v>208.3</v>
@@ -9153,28 +9153,28 @@
         <v>193.3</v>
       </c>
       <c r="M96">
-        <v>8.751425379999999</v>
+        <v>8.844525650000001</v>
       </c>
       <c r="N96">
-        <v>184.54857462</v>
+        <v>184.45547435</v>
       </c>
       <c r="O96">
-        <v>35.0642291778</v>
+        <v>35.0465401265</v>
       </c>
       <c r="P96">
-        <v>149.4843454422</v>
+        <v>149.4089342235</v>
       </c>
       <c r="Q96">
-        <v>262.3843454422</v>
+        <v>262.3089342235</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8560257625855004</v>
+        <v>1.01582193197782</v>
       </c>
       <c r="T96">
-        <v>14.83956938128834</v>
+        <v>17.7662923418054</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>22.08783045122645</v>
+        <v>21.85532697279248</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08949694659889094</v>
+        <v>0.08933392744265192</v>
       </c>
       <c r="C97">
-        <v>1.149109210138477</v>
+        <v>-0.819055849178369</v>
       </c>
       <c r="D97">
-        <v>-31.3153907898615</v>
+        <v>-31.43265584917836</v>
       </c>
       <c r="E97">
-        <v>168.1455</v>
+        <v>169.9964</v>
       </c>
       <c r="F97">
-        <v>175.8355</v>
+        <v>177.6864</v>
       </c>
       <c r="G97">
         <v>208.3</v>
@@ -9235,28 +9235,28 @@
         <v>193.3</v>
       </c>
       <c r="M97">
-        <v>8.844525650000001</v>
+        <v>8.93762592</v>
       </c>
       <c r="N97">
-        <v>184.45547435</v>
+        <v>184.36237408</v>
       </c>
       <c r="O97">
-        <v>35.0465401265</v>
+        <v>35.0288510752</v>
       </c>
       <c r="P97">
-        <v>149.4089342235</v>
+        <v>149.3335230048</v>
       </c>
       <c r="Q97">
-        <v>262.3089342235</v>
+        <v>262.2335230048</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.01582193197782</v>
+        <v>1.2555161860663</v>
       </c>
       <c r="T97">
-        <v>17.7662923418054</v>
+        <v>22.156376782581</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>21.85532697279248</v>
+        <v>21.6276673168259</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08933392744265191</v>
+        <v>0.08917090828641287</v>
       </c>
       <c r="C98">
-        <v>-0.819055849178369</v>
+        <v>-2.7881024418447</v>
       </c>
       <c r="D98">
-        <v>-31.43265584917837</v>
+        <v>-31.55080244184473</v>
       </c>
       <c r="E98">
-        <v>169.9964</v>
+        <v>171.8473</v>
       </c>
       <c r="F98">
-        <v>177.6864</v>
+        <v>179.5373</v>
       </c>
       <c r="G98">
         <v>208.3</v>
@@ -9317,28 +9317,28 @@
         <v>193.3</v>
       </c>
       <c r="M98">
-        <v>8.937625919999999</v>
+        <v>9.030726189999999</v>
       </c>
       <c r="N98">
-        <v>184.36237408</v>
+        <v>184.26927381</v>
       </c>
       <c r="O98">
-        <v>35.0288510752</v>
+        <v>35.01116202390001</v>
       </c>
       <c r="P98">
-        <v>149.3335230048</v>
+        <v>149.2581117861</v>
       </c>
       <c r="Q98">
-        <v>262.2335230048</v>
+        <v>262.1581117861</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.255516186066297</v>
+        <v>1.655006609547094</v>
       </c>
       <c r="T98">
-        <v>22.15637678258094</v>
+        <v>29.47318418387357</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>21.6276673168259</v>
+        <v>21.4047016743844</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08917090828641287</v>
+        <v>0.08900788913017382</v>
       </c>
       <c r="C99">
-        <v>-2.7881024418447</v>
+        <v>-4.758040545678938</v>
       </c>
       <c r="D99">
-        <v>-31.55080244184473</v>
+        <v>-31.66984054567894</v>
       </c>
       <c r="E99">
-        <v>171.8473</v>
+        <v>173.6982</v>
       </c>
       <c r="F99">
-        <v>179.5373</v>
+        <v>181.3882</v>
       </c>
       <c r="G99">
         <v>208.3</v>
@@ -9399,28 +9399,28 @@
         <v>193.3</v>
       </c>
       <c r="M99">
-        <v>9.030726189999999</v>
+        <v>9.12382646</v>
       </c>
       <c r="N99">
-        <v>184.26927381</v>
+        <v>184.17617354</v>
       </c>
       <c r="O99">
-        <v>35.01116202390001</v>
+        <v>34.9934729726</v>
       </c>
       <c r="P99">
-        <v>149.2581117861</v>
+        <v>149.1827005674</v>
       </c>
       <c r="Q99">
-        <v>262.1581117861</v>
+        <v>262.0827005674</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.655006609547094</v>
+        <v>2.453987456508689</v>
       </c>
       <c r="T99">
-        <v>29.47318418387357</v>
+        <v>44.10679898645883</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>21.4047016743844</v>
+        <v>21.18628635117639</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08900788913017382</v>
+        <v>0.08884486997393479</v>
       </c>
       <c r="C100">
-        <v>-4.758040545678938</v>
+        <v>-6.728880289650931</v>
       </c>
       <c r="D100">
-        <v>-31.66984054567894</v>
+        <v>-31.78978028965093</v>
       </c>
       <c r="E100">
-        <v>173.6982</v>
+        <v>175.5491</v>
       </c>
       <c r="F100">
-        <v>181.3882</v>
+        <v>183.2391</v>
       </c>
       <c r="G100">
         <v>208.3</v>
@@ -9481,28 +9481,28 @@
         <v>193.3</v>
       </c>
       <c r="M100">
-        <v>9.12382646</v>
+        <v>9.216926729999999</v>
       </c>
       <c r="N100">
-        <v>184.17617354</v>
+        <v>184.08307327</v>
       </c>
       <c r="O100">
-        <v>34.9934729726</v>
+        <v>34.9757839213</v>
       </c>
       <c r="P100">
-        <v>149.1827005674</v>
+        <v>149.1072893487</v>
       </c>
       <c r="Q100">
-        <v>262.0827005674</v>
+        <v>262.0072893486999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.453987456508689</v>
+        <v>4.850929997393475</v>
       </c>
       <c r="T100">
-        <v>44.10679898645883</v>
+        <v>88.00764339421461</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>21.18628635117639</v>
+        <v>20.97228345874027</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08884486997393479</v>
-      </c>
-      <c r="C101">
-        <v>-6.728880289650931</v>
-      </c>
-      <c r="D101">
-        <v>-31.78978028965093</v>
-      </c>
-      <c r="E101">
-        <v>175.5491</v>
-      </c>
-      <c r="F101">
-        <v>183.2391</v>
-      </c>
-      <c r="G101">
-        <v>208.3</v>
-      </c>
-      <c r="H101">
-        <v>177.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>306.2</v>
-      </c>
-      <c r="K101">
-        <v>112.9</v>
-      </c>
-      <c r="L101">
-        <v>193.3</v>
-      </c>
-      <c r="M101">
-        <v>9.216926729999999</v>
-      </c>
-      <c r="N101">
-        <v>184.08307327</v>
-      </c>
-      <c r="O101">
-        <v>34.9757839213</v>
-      </c>
-      <c r="P101">
-        <v>149.1072893487</v>
-      </c>
-      <c r="Q101">
-        <v>262.0072893486999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.850929997393475</v>
-      </c>
-      <c r="T101">
-        <v>88.00764339421461</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.040743</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>20.97228345874027</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
